--- a/AAII_Financials/Quarterly/TIMB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TIMB_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>TIMB</t>
   </si>
@@ -656,302 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1245200</v>
+        <v>1257700</v>
       </c>
       <c r="E8" s="3">
-        <v>1205700</v>
+        <v>1213600</v>
       </c>
       <c r="F8" s="3">
-        <v>1159800</v>
+        <v>1175100</v>
       </c>
       <c r="G8" s="3">
-        <v>1197700</v>
+        <v>1130400</v>
       </c>
       <c r="H8" s="3">
-        <v>1153800</v>
+        <v>1167300</v>
       </c>
       <c r="I8" s="3">
-        <v>1103800</v>
+        <v>1124600</v>
       </c>
       <c r="J8" s="3">
+        <v>1075900</v>
+      </c>
+      <c r="K8" s="3">
         <v>972100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>968700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>908700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>853300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>811900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>915500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>854600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1616400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>752500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>847100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>813600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>754800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>784200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>834100</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>734000</v>
+        <v>734500</v>
       </c>
       <c r="E9" s="3">
-        <v>753400</v>
+        <v>715400</v>
       </c>
       <c r="F9" s="3">
-        <v>747300</v>
+        <v>734300</v>
       </c>
       <c r="G9" s="3">
-        <v>753200</v>
+        <v>728400</v>
       </c>
       <c r="H9" s="3">
-        <v>744100</v>
+        <v>734100</v>
       </c>
       <c r="I9" s="3">
-        <v>715100</v>
+        <v>725200</v>
       </c>
       <c r="J9" s="3">
+        <v>697000</v>
+      </c>
+      <c r="K9" s="3">
         <v>611500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>563900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>546100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>522400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>499800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>414300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>399500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1122400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>350200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>307400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>366300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>329200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>366300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>367900</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>511100</v>
+        <v>523100</v>
       </c>
       <c r="E10" s="3">
-        <v>452300</v>
+        <v>498200</v>
       </c>
       <c r="F10" s="3">
-        <v>412500</v>
+        <v>440800</v>
       </c>
       <c r="G10" s="3">
-        <v>444400</v>
+        <v>402000</v>
       </c>
       <c r="H10" s="3">
-        <v>409800</v>
+        <v>433200</v>
       </c>
       <c r="I10" s="3">
-        <v>388700</v>
+        <v>399400</v>
       </c>
       <c r="J10" s="3">
+        <v>378900</v>
+      </c>
+      <c r="K10" s="3">
         <v>360600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>404800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>362500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>331000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>312100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>501200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>455100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>494000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>402400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>539800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>447200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>425600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>417900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>466200</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -975,8 +987,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1040,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,138 +1121,147 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>11900</v>
+        <v>7800</v>
       </c>
       <c r="E14" s="3">
-        <v>9800</v>
+        <v>11600</v>
       </c>
       <c r="F14" s="3">
-        <v>15200</v>
+        <v>9600</v>
       </c>
       <c r="G14" s="3">
-        <v>7900</v>
+        <v>14800</v>
       </c>
       <c r="H14" s="3">
-        <v>7400</v>
+        <v>7700</v>
       </c>
       <c r="I14" s="3">
-        <v>4800</v>
+        <v>7200</v>
       </c>
       <c r="J14" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K14" s="3">
         <v>10000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>13900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>11700</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>38400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>11800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>10700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>17400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>40300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>16500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>39200</v>
+        <v>38300</v>
       </c>
       <c r="E15" s="3">
-        <v>38500</v>
+        <v>38200</v>
       </c>
       <c r="F15" s="3">
-        <v>36700</v>
+        <v>37500</v>
       </c>
       <c r="G15" s="3">
+        <v>35800</v>
+      </c>
+      <c r="H15" s="3">
+        <v>36600</v>
+      </c>
+      <c r="I15" s="3">
+        <v>37700</v>
+      </c>
+      <c r="J15" s="3">
         <v>37500</v>
       </c>
-      <c r="H15" s="3">
-        <v>38700</v>
-      </c>
-      <c r="I15" s="3">
-        <v>38500</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>40200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>41000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>42200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>40700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>41400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>43800</v>
       </c>
-      <c r="P15" s="3" t="s">
+      <c r="Q15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>48900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>44300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>43900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>48900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>44800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>45900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>994500</v>
+        <v>920900</v>
       </c>
       <c r="E17" s="3">
-        <v>992000</v>
+        <v>969300</v>
       </c>
       <c r="F17" s="3">
-        <v>999500</v>
+        <v>966900</v>
       </c>
       <c r="G17" s="3">
-        <v>998000</v>
+        <v>974200</v>
       </c>
       <c r="H17" s="3">
-        <v>997200</v>
+        <v>972700</v>
       </c>
       <c r="I17" s="3">
-        <v>953300</v>
+        <v>971900</v>
       </c>
       <c r="J17" s="3">
+        <v>929100</v>
+      </c>
+      <c r="K17" s="3">
         <v>829200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>616500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>756600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>724900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>701100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>724800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>721600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1388200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>660600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>616100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>690200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>372700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>700300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>683600</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>250600</v>
+        <v>336700</v>
       </c>
       <c r="E18" s="3">
-        <v>213600</v>
+        <v>244300</v>
       </c>
       <c r="F18" s="3">
-        <v>160300</v>
+        <v>208200</v>
       </c>
       <c r="G18" s="3">
-        <v>199700</v>
+        <v>156200</v>
       </c>
       <c r="H18" s="3">
-        <v>156700</v>
+        <v>194600</v>
       </c>
       <c r="I18" s="3">
-        <v>150600</v>
+        <v>152700</v>
       </c>
       <c r="J18" s="3">
+        <v>146800</v>
+      </c>
+      <c r="K18" s="3">
         <v>142900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>352200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>152100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>128400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>110900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>190700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>133000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>228100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>92000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>231000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>123400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>382100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>84000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>150500</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,333 +1444,349 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-28400</v>
+        <v>-6100</v>
       </c>
       <c r="E20" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="H20" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I20" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="K20" s="3">
+        <v>7400</v>
+      </c>
+      <c r="L20" s="3">
+        <v>20300</v>
+      </c>
+      <c r="M20" s="3">
+        <v>5400</v>
+      </c>
+      <c r="N20" s="3">
+        <v>36500</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="P20" s="3">
+        <v>29500</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-47500</v>
+      </c>
+      <c r="R20" s="3">
+        <v>-56900</v>
+      </c>
+      <c r="S20" s="3">
         <v>-9700</v>
       </c>
-      <c r="F20" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>5300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>3100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-20600</v>
-      </c>
-      <c r="J20" s="3">
-        <v>7400</v>
-      </c>
-      <c r="K20" s="3">
-        <v>20300</v>
-      </c>
-      <c r="L20" s="3">
-        <v>5400</v>
-      </c>
-      <c r="M20" s="3">
-        <v>36500</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="T20" s="3">
+        <v>600</v>
+      </c>
+      <c r="U20" s="3">
         <v>-4600</v>
       </c>
-      <c r="O20" s="3">
-        <v>29500</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-47500</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-56900</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="S20" s="3">
-        <v>600</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>179600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-6300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>583200</v>
+        <v>681300</v>
       </c>
       <c r="E21" s="3">
-        <v>581200</v>
+        <v>568400</v>
       </c>
       <c r="F21" s="3">
-        <v>517500</v>
+        <v>566400</v>
       </c>
       <c r="G21" s="3">
-        <v>587000</v>
+        <v>504400</v>
       </c>
       <c r="H21" s="3">
-        <v>546400</v>
+        <v>572200</v>
       </c>
       <c r="I21" s="3">
-        <v>477300</v>
+        <v>532600</v>
       </c>
       <c r="J21" s="3">
+        <v>465200</v>
+      </c>
+      <c r="K21" s="3">
         <v>438000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>662400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>440200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>440600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>373400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>490000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>356300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>714700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>333700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>427400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>388300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>791500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>327300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>344400</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>55100</v>
+        <v>89600</v>
       </c>
       <c r="E22" s="3">
-        <v>77900</v>
+        <v>53700</v>
       </c>
       <c r="F22" s="3">
-        <v>37800</v>
+        <v>75900</v>
       </c>
       <c r="G22" s="3">
-        <v>77200</v>
+        <v>36800</v>
       </c>
       <c r="H22" s="3">
-        <v>85800</v>
+        <v>75300</v>
       </c>
       <c r="I22" s="3">
-        <v>69600</v>
+        <v>83600</v>
       </c>
       <c r="J22" s="3">
+        <v>67900</v>
+      </c>
+      <c r="K22" s="3">
         <v>58300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>56700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>47900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>43500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>37600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>38200</v>
       </c>
-      <c r="P22" s="3" t="s">
+      <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>45400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>35700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>44100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>45500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>40300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>42800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>167100</v>
+        <v>241000</v>
       </c>
       <c r="E23" s="3">
-        <v>126100</v>
+        <v>162900</v>
       </c>
       <c r="F23" s="3">
-        <v>114400</v>
+        <v>122900</v>
       </c>
       <c r="G23" s="3">
-        <v>127700</v>
+        <v>111500</v>
       </c>
       <c r="H23" s="3">
-        <v>74000</v>
+        <v>124400</v>
       </c>
       <c r="I23" s="3">
-        <v>60300</v>
+        <v>72100</v>
       </c>
       <c r="J23" s="3">
+        <v>58800</v>
+      </c>
+      <c r="K23" s="3">
         <v>91900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>315800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>109600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>121400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>68700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>182000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>85500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>125800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>46500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>187500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>73300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>521300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>34800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>19900</v>
+        <v>24000</v>
       </c>
       <c r="E24" s="3">
-        <v>-2800</v>
+        <v>19400</v>
       </c>
       <c r="F24" s="3">
-        <v>29500</v>
+        <v>-2700</v>
       </c>
       <c r="G24" s="3">
-        <v>17000</v>
+        <v>28800</v>
       </c>
       <c r="H24" s="3">
-        <v>-18100</v>
+        <v>16600</v>
       </c>
       <c r="I24" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="J24" s="3">
         <v>2800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>110900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-90300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-8800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>16900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-16300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>39000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>17600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>17800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-32100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>163300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>12400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>147200</v>
+        <v>217000</v>
       </c>
       <c r="E26" s="3">
-        <v>128800</v>
+        <v>143500</v>
       </c>
       <c r="F26" s="3">
-        <v>84800</v>
+        <v>125600</v>
       </c>
       <c r="G26" s="3">
-        <v>110700</v>
+        <v>82700</v>
       </c>
       <c r="H26" s="3">
-        <v>92100</v>
+        <v>107900</v>
       </c>
       <c r="I26" s="3">
-        <v>57500</v>
+        <v>89700</v>
       </c>
       <c r="J26" s="3">
+        <v>56000</v>
+      </c>
+      <c r="K26" s="3">
         <v>83400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>204900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>199900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>130200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>51800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>198300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>76000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>86800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>28900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>169600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>105400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>358100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>22500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>147200</v>
+        <v>217000</v>
       </c>
       <c r="E27" s="3">
-        <v>128800</v>
+        <v>143500</v>
       </c>
       <c r="F27" s="3">
-        <v>84800</v>
+        <v>125600</v>
       </c>
       <c r="G27" s="3">
-        <v>110700</v>
+        <v>82700</v>
       </c>
       <c r="H27" s="3">
-        <v>92100</v>
+        <v>107900</v>
       </c>
       <c r="I27" s="3">
-        <v>57500</v>
+        <v>89700</v>
       </c>
       <c r="J27" s="3">
+        <v>56000</v>
+      </c>
+      <c r="K27" s="3">
         <v>83400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>204900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>199900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>130200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>51800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>198300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>76000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>86800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>28900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>169600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>105400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>358100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>22500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2062,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>28400</v>
+        <v>6100</v>
       </c>
       <c r="E32" s="3">
+        <v>27700</v>
+      </c>
+      <c r="F32" s="3">
+        <v>9500</v>
+      </c>
+      <c r="G32" s="3">
+        <v>8000</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>20100</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-36500</v>
+      </c>
+      <c r="O32" s="3">
+        <v>4600</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>47500</v>
+      </c>
+      <c r="R32" s="3">
+        <v>56900</v>
+      </c>
+      <c r="S32" s="3">
         <v>9700</v>
       </c>
-      <c r="F32" s="3">
-        <v>8200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>20600</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-20300</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-36500</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="T32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U32" s="3">
         <v>4600</v>
       </c>
-      <c r="O32" s="3">
-        <v>-29500</v>
-      </c>
-      <c r="P32" s="3">
-        <v>47500</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>56900</v>
-      </c>
-      <c r="R32" s="3">
-        <v>9700</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="T32" s="3">
-        <v>4600</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-179600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>6300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>147200</v>
+        <v>217000</v>
       </c>
       <c r="E33" s="3">
-        <v>128800</v>
+        <v>143500</v>
       </c>
       <c r="F33" s="3">
-        <v>84800</v>
+        <v>125600</v>
       </c>
       <c r="G33" s="3">
-        <v>110700</v>
+        <v>82700</v>
       </c>
       <c r="H33" s="3">
-        <v>92100</v>
+        <v>107900</v>
       </c>
       <c r="I33" s="3">
-        <v>57500</v>
+        <v>89700</v>
       </c>
       <c r="J33" s="3">
+        <v>56000</v>
+      </c>
+      <c r="K33" s="3">
         <v>83400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>204900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>199900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>130200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>51800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>198300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>76000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>86800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>28900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>169600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>105400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>358100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>22500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>147200</v>
+        <v>217000</v>
       </c>
       <c r="E35" s="3">
-        <v>128800</v>
+        <v>143500</v>
       </c>
       <c r="F35" s="3">
-        <v>84800</v>
+        <v>125600</v>
       </c>
       <c r="G35" s="3">
-        <v>110700</v>
+        <v>82700</v>
       </c>
       <c r="H35" s="3">
-        <v>92100</v>
+        <v>107900</v>
       </c>
       <c r="I35" s="3">
-        <v>57500</v>
+        <v>89700</v>
       </c>
       <c r="J35" s="3">
+        <v>56000</v>
+      </c>
+      <c r="K35" s="3">
         <v>83400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>204900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>199900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>130200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>51800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>198300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>76000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>86800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>28900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>169600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>105400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>358100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>22500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,593 +2657,621 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>742100</v>
+        <v>616900</v>
       </c>
       <c r="E41" s="3">
-        <v>630700</v>
+        <v>723300</v>
       </c>
       <c r="F41" s="3">
-        <v>731000</v>
+        <v>614700</v>
       </c>
       <c r="G41" s="3">
-        <v>524100</v>
+        <v>712500</v>
       </c>
       <c r="H41" s="3">
-        <v>472000</v>
+        <v>510800</v>
       </c>
       <c r="I41" s="3">
-        <v>246500</v>
+        <v>460100</v>
       </c>
       <c r="J41" s="3">
+        <v>240200</v>
+      </c>
+      <c r="K41" s="3">
         <v>823100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1055300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>819200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>726000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>508200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>504000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>413900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>605800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>284000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>422000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>164300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>118100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>171200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>201300</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>172200</v>
+        <v>392500</v>
       </c>
       <c r="E42" s="3">
-        <v>55900</v>
+        <v>167800</v>
       </c>
       <c r="F42" s="3">
-        <v>66900</v>
+        <v>54400</v>
       </c>
       <c r="G42" s="3">
-        <v>450500</v>
+        <v>65200</v>
       </c>
       <c r="H42" s="3">
-        <v>289400</v>
+        <v>439000</v>
       </c>
       <c r="I42" s="3">
-        <v>223700</v>
+        <v>282100</v>
       </c>
       <c r="J42" s="3">
+        <v>218000</v>
+      </c>
+      <c r="K42" s="3">
         <v>837500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>922000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>665600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>653600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>299700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>405200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>294700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>50300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>7000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>120900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>146700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>87400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>140900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>146900</v>
       </c>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1024600</v>
+        <v>1031700</v>
       </c>
       <c r="E43" s="3">
-        <v>921900</v>
+        <v>998600</v>
       </c>
       <c r="F43" s="3">
-        <v>940700</v>
+        <v>898500</v>
       </c>
       <c r="G43" s="3">
-        <v>948800</v>
+        <v>916900</v>
       </c>
       <c r="H43" s="3">
-        <v>908400</v>
+        <v>924800</v>
       </c>
       <c r="I43" s="3">
-        <v>983800</v>
+        <v>885300</v>
       </c>
       <c r="J43" s="3">
+        <v>958900</v>
+      </c>
+      <c r="K43" s="3">
         <v>898400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>955400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>875900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>867400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>843400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>948600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>956400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>849600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>835500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>923500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>785800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>661200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>670700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>648700</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>85400</v>
+        <v>66500</v>
       </c>
       <c r="E44" s="3">
-        <v>77000</v>
+        <v>83200</v>
       </c>
       <c r="F44" s="3">
-        <v>61900</v>
+        <v>75000</v>
       </c>
       <c r="G44" s="3">
-        <v>48600</v>
+        <v>60400</v>
       </c>
       <c r="H44" s="3">
-        <v>57200</v>
+        <v>47300</v>
       </c>
       <c r="I44" s="3">
-        <v>57600</v>
+        <v>55700</v>
       </c>
       <c r="J44" s="3">
+        <v>56100</v>
+      </c>
+      <c r="K44" s="3">
         <v>45700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>40900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>46600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>43700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>56300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>48300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>40300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>40100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>47900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>37500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>39600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>37800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>40200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>34300</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>204100</v>
+        <v>178000</v>
       </c>
       <c r="E45" s="3">
-        <v>223000</v>
+        <v>198900</v>
       </c>
       <c r="F45" s="3">
-        <v>235800</v>
+        <v>217400</v>
       </c>
       <c r="G45" s="3">
-        <v>159300</v>
+        <v>229800</v>
       </c>
       <c r="H45" s="3">
-        <v>193900</v>
+        <v>155300</v>
       </c>
       <c r="I45" s="3">
-        <v>286900</v>
+        <v>189000</v>
       </c>
       <c r="J45" s="3">
+        <v>279700</v>
+      </c>
+      <c r="K45" s="3">
         <v>192100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>134300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>132600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>170200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>172100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>131600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>164900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>101300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>108500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>57500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>121800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>152000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>206800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>91300</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2228400</v>
+        <v>2285600</v>
       </c>
       <c r="E46" s="3">
-        <v>1908400</v>
+        <v>2171900</v>
       </c>
       <c r="F46" s="3">
-        <v>2036400</v>
+        <v>1860100</v>
       </c>
       <c r="G46" s="3">
-        <v>2131200</v>
+        <v>1984800</v>
       </c>
       <c r="H46" s="3">
-        <v>1920800</v>
+        <v>2077200</v>
       </c>
       <c r="I46" s="3">
-        <v>1798500</v>
+        <v>1872100</v>
       </c>
       <c r="J46" s="3">
+        <v>1752900</v>
+      </c>
+      <c r="K46" s="3">
         <v>2796900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3107900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2539900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2460900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1879800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2037500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1870100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1647200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1283000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1561500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1258200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1056500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1229800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1122400</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>590700</v>
+        <v>552400</v>
       </c>
       <c r="E47" s="3">
-        <v>737800</v>
+        <v>575700</v>
       </c>
       <c r="F47" s="3">
-        <v>663400</v>
+        <v>719100</v>
       </c>
       <c r="G47" s="3">
-        <v>659000</v>
+        <v>646600</v>
       </c>
       <c r="H47" s="3">
-        <v>710000</v>
+        <v>642300</v>
       </c>
       <c r="I47" s="3">
-        <v>701400</v>
+        <v>692000</v>
       </c>
       <c r="J47" s="3">
+        <v>683700</v>
+      </c>
+      <c r="K47" s="3">
         <v>698500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>693400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>411600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>334300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>367500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>444200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>410400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>665000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>603700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>609100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>786100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>766800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>294700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4652700</v>
+        <v>4491800</v>
       </c>
       <c r="E48" s="3">
-        <v>4746900</v>
+        <v>4534800</v>
       </c>
       <c r="F48" s="3">
-        <v>4796800</v>
+        <v>4626700</v>
       </c>
       <c r="G48" s="3">
-        <v>4659800</v>
+        <v>4675200</v>
       </c>
       <c r="H48" s="3">
-        <v>4750400</v>
+        <v>4541700</v>
       </c>
       <c r="I48" s="3">
-        <v>4862500</v>
+        <v>4630100</v>
       </c>
       <c r="J48" s="3">
+        <v>4739300</v>
+      </c>
+      <c r="K48" s="3">
         <v>3963300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3695400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3515000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3373600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3450400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3542300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3380900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3415200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3190900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3253000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3129600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2907800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2970000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2096500</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3243400</v>
+        <v>3131600</v>
       </c>
       <c r="E49" s="3">
-        <v>3300400</v>
+        <v>3161200</v>
       </c>
       <c r="F49" s="3">
-        <v>3359200</v>
+        <v>3216800</v>
       </c>
       <c r="G49" s="3">
-        <v>3375700</v>
+        <v>3274100</v>
       </c>
       <c r="H49" s="3">
-        <v>3279700</v>
+        <v>3290200</v>
       </c>
       <c r="I49" s="3">
-        <v>3237600</v>
+        <v>3196600</v>
       </c>
       <c r="J49" s="3">
+        <v>3155600</v>
+      </c>
+      <c r="K49" s="3">
         <v>2179800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2136500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1459200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1444800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1650300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1766600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1755400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1826000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1703000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1785700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1846400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1791600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1947200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1998900</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,73 +3403,79 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>794600</v>
+        <v>613800</v>
       </c>
       <c r="E52" s="3">
-        <v>761400</v>
+        <v>774500</v>
       </c>
       <c r="F52" s="3">
-        <v>781400</v>
+        <v>742100</v>
       </c>
       <c r="G52" s="3">
-        <v>773400</v>
+        <v>761600</v>
       </c>
       <c r="H52" s="3">
-        <v>584600</v>
+        <v>753800</v>
       </c>
       <c r="I52" s="3">
-        <v>567000</v>
+        <v>569800</v>
       </c>
       <c r="J52" s="3">
+        <v>552700</v>
+      </c>
+      <c r="K52" s="3">
         <v>442800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>422300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>931700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>878600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>344500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>361100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>333500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>295600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>270900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>243100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>278500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>276200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>448900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>461900</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>11509700</v>
+        <v>11075200</v>
       </c>
       <c r="E54" s="3">
-        <v>11455000</v>
+        <v>11218100</v>
       </c>
       <c r="F54" s="3">
-        <v>11637200</v>
+        <v>11164700</v>
       </c>
       <c r="G54" s="3">
-        <v>11599300</v>
+        <v>11342300</v>
       </c>
       <c r="H54" s="3">
-        <v>11245500</v>
+        <v>11305400</v>
       </c>
       <c r="I54" s="3">
-        <v>11167100</v>
+        <v>10960500</v>
       </c>
       <c r="J54" s="3">
+        <v>10884200</v>
+      </c>
+      <c r="K54" s="3">
         <v>10081300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10055500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8857300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8492200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7692600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8151800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7750300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7849100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7051500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7452400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7298800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6798900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6890500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5980300</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,398 +3661,417 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>792500</v>
+        <v>924400</v>
       </c>
       <c r="E57" s="3">
-        <v>750700</v>
+        <v>772400</v>
       </c>
       <c r="F57" s="3">
-        <v>794400</v>
+        <v>731700</v>
       </c>
       <c r="G57" s="3">
-        <v>871300</v>
+        <v>774300</v>
       </c>
       <c r="H57" s="3">
-        <v>852800</v>
+        <v>849200</v>
       </c>
       <c r="I57" s="3">
-        <v>839700</v>
+        <v>831200</v>
       </c>
       <c r="J57" s="3">
+        <v>818400</v>
+      </c>
+      <c r="K57" s="3">
         <v>618900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>659500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>534400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>501500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>497900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>612300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>423900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>407700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>470400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>724600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>548300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>512000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>707700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>809000</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>861600</v>
+        <v>616500</v>
       </c>
       <c r="E58" s="3">
-        <v>879400</v>
+        <v>839800</v>
       </c>
       <c r="F58" s="3">
-        <v>799100</v>
+        <v>857200</v>
       </c>
       <c r="G58" s="3">
-        <v>724300</v>
+        <v>778900</v>
       </c>
       <c r="H58" s="3">
-        <v>411500</v>
+        <v>705900</v>
       </c>
       <c r="I58" s="3">
-        <v>400200</v>
+        <v>401100</v>
       </c>
       <c r="J58" s="3">
+        <v>390000</v>
+      </c>
+      <c r="K58" s="3">
         <v>277400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>365000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>359000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>509600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>630200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>537000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>543200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>513900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>363300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>416900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>432400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>233000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>249900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1166900</v>
+        <v>1041200</v>
       </c>
       <c r="E59" s="3">
-        <v>1096700</v>
+        <v>1137400</v>
       </c>
       <c r="F59" s="3">
-        <v>1155500</v>
+        <v>1068900</v>
       </c>
       <c r="G59" s="3">
-        <v>1101900</v>
+        <v>1126200</v>
       </c>
       <c r="H59" s="3">
-        <v>859100</v>
+        <v>1074000</v>
       </c>
       <c r="I59" s="3">
-        <v>749500</v>
+        <v>837300</v>
       </c>
       <c r="J59" s="3">
+        <v>730500</v>
+      </c>
+      <c r="K59" s="3">
         <v>900400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1117300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>482200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>462100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>350500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>475400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>332200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>307800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>229800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>357800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>383300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>256100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>261700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>345900</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2821000</v>
+        <v>2582000</v>
       </c>
       <c r="E60" s="3">
-        <v>2726900</v>
+        <v>2749500</v>
       </c>
       <c r="F60" s="3">
-        <v>2749000</v>
+        <v>2657800</v>
       </c>
       <c r="G60" s="3">
-        <v>2697500</v>
+        <v>2679300</v>
       </c>
       <c r="H60" s="3">
-        <v>2123400</v>
+        <v>2629100</v>
       </c>
       <c r="I60" s="3">
-        <v>1989300</v>
+        <v>2069600</v>
       </c>
       <c r="J60" s="3">
+        <v>1938900</v>
+      </c>
+      <c r="K60" s="3">
         <v>1796700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2141800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1375500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1473300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1478600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1624700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1299200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1229400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1063500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1499300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1364000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1001100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1219300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1324000</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2725200</v>
+        <v>2595800</v>
       </c>
       <c r="E61" s="3">
-        <v>2799500</v>
+        <v>2656100</v>
       </c>
       <c r="F61" s="3">
-        <v>2932500</v>
+        <v>2728600</v>
       </c>
       <c r="G61" s="3">
-        <v>2936300</v>
+        <v>2858200</v>
       </c>
       <c r="H61" s="3">
-        <v>3169400</v>
+        <v>2861900</v>
       </c>
       <c r="I61" s="3">
-        <v>3197100</v>
+        <v>3089100</v>
       </c>
       <c r="J61" s="3">
+        <v>3116100</v>
+      </c>
+      <c r="K61" s="3">
         <v>2431100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2240600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2043100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1939900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1417100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1561600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1494800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1638000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1534300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1395000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1393500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1461300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1503800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>505100</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>704800</v>
+        <v>683300</v>
       </c>
       <c r="E62" s="3">
-        <v>720500</v>
+        <v>686900</v>
       </c>
       <c r="F62" s="3">
-        <v>770600</v>
+        <v>702300</v>
       </c>
       <c r="G62" s="3">
-        <v>743000</v>
+        <v>751100</v>
       </c>
       <c r="H62" s="3">
-        <v>751000</v>
+        <v>724200</v>
       </c>
       <c r="I62" s="3">
-        <v>771800</v>
+        <v>732000</v>
       </c>
       <c r="J62" s="3">
+        <v>752300</v>
+      </c>
+      <c r="K62" s="3">
         <v>643300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>605500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>475800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>475600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>407100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>428600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>427700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>479400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>421400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>415000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>459000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>451600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>440000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>446900</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,73 +4271,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6250900</v>
+        <v>5861100</v>
       </c>
       <c r="E66" s="3">
-        <v>6246900</v>
+        <v>6092500</v>
       </c>
       <c r="F66" s="3">
-        <v>6452100</v>
+        <v>6088700</v>
       </c>
       <c r="G66" s="3">
-        <v>6376800</v>
+        <v>6288600</v>
       </c>
       <c r="H66" s="3">
-        <v>6043900</v>
+        <v>6215200</v>
       </c>
       <c r="I66" s="3">
-        <v>5958200</v>
+        <v>5890800</v>
       </c>
       <c r="J66" s="3">
+        <v>5807300</v>
+      </c>
+      <c r="K66" s="3">
         <v>4871000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4987900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3894400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3888700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3302800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3614900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3221800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3346700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3019200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3309300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3216600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2914000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3163100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2276100</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4402,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2416000</v>
+        <v>2443300</v>
       </c>
       <c r="E72" s="3">
-        <v>2364700</v>
+        <v>2354800</v>
       </c>
       <c r="F72" s="3">
-        <v>2341700</v>
+        <v>2304700</v>
       </c>
       <c r="G72" s="3">
-        <v>2379100</v>
+        <v>2282400</v>
       </c>
       <c r="H72" s="3">
-        <v>2358600</v>
+        <v>2318800</v>
       </c>
       <c r="I72" s="3">
-        <v>2371800</v>
+        <v>2298900</v>
       </c>
       <c r="J72" s="3">
+        <v>2311700</v>
+      </c>
+      <c r="K72" s="3">
         <v>2368000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2277700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2179300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1930100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1803500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1831900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1835100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2161300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2204900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2251400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2160900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2071600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1811200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1788100</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5258800</v>
+        <v>5214100</v>
       </c>
       <c r="E76" s="3">
-        <v>5208000</v>
+        <v>5125600</v>
       </c>
       <c r="F76" s="3">
-        <v>5185100</v>
+        <v>5076100</v>
       </c>
       <c r="G76" s="3">
-        <v>5222500</v>
+        <v>5053700</v>
       </c>
       <c r="H76" s="3">
-        <v>5201600</v>
+        <v>5090100</v>
       </c>
       <c r="I76" s="3">
-        <v>5208900</v>
+        <v>5069800</v>
       </c>
       <c r="J76" s="3">
+        <v>5076900</v>
+      </c>
+      <c r="K76" s="3">
         <v>5210200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5067600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4962900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4603400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4389800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4536900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4528500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4502400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4032300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4143200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4082200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3884900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3727500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3704200</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>147200</v>
+        <v>217000</v>
       </c>
       <c r="E81" s="3">
-        <v>128800</v>
+        <v>143500</v>
       </c>
       <c r="F81" s="3">
-        <v>84800</v>
+        <v>125600</v>
       </c>
       <c r="G81" s="3">
-        <v>110700</v>
+        <v>82700</v>
       </c>
       <c r="H81" s="3">
-        <v>92100</v>
+        <v>107900</v>
       </c>
       <c r="I81" s="3">
-        <v>57500</v>
+        <v>89700</v>
       </c>
       <c r="J81" s="3">
+        <v>56000</v>
+      </c>
+      <c r="K81" s="3">
         <v>83400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>204900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>199900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>130200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>51800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>198300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>76000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>86800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>28900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>169600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>105400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>358100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>22500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,73 +5214,77 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>361000</v>
+        <v>350700</v>
       </c>
       <c r="E83" s="3">
-        <v>377200</v>
+        <v>351800</v>
       </c>
       <c r="F83" s="3">
-        <v>365400</v>
+        <v>367700</v>
       </c>
       <c r="G83" s="3">
-        <v>382100</v>
+        <v>356200</v>
       </c>
       <c r="H83" s="3">
-        <v>386600</v>
+        <v>372400</v>
       </c>
       <c r="I83" s="3">
-        <v>347400</v>
+        <v>376800</v>
       </c>
       <c r="J83" s="3">
+        <v>338600</v>
+      </c>
+      <c r="K83" s="3">
         <v>287700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>289800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>282800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>275700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>267100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>269800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>270800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>543500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>251500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>195800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>269500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>229800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>249700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>190500</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>716500</v>
+        <v>971800</v>
       </c>
       <c r="E89" s="3">
-        <v>434300</v>
+        <v>698300</v>
       </c>
       <c r="F89" s="3">
-        <v>406200</v>
+        <v>423300</v>
       </c>
       <c r="G89" s="3">
-        <v>720100</v>
+        <v>395900</v>
       </c>
       <c r="H89" s="3">
-        <v>714100</v>
+        <v>701900</v>
       </c>
       <c r="I89" s="3">
-        <v>274500</v>
+        <v>696000</v>
       </c>
       <c r="J89" s="3">
+        <v>267500</v>
+      </c>
+      <c r="K89" s="3">
         <v>230200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>630400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>558400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>432300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>364700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>723800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>426300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>549100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>87000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>666100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>394600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>187500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>55400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>546400</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,73 +5716,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1291900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-998200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-925700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1288500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1375200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-977600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1049600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1328000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2157400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-896500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-175400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-247700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-286500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-165600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-310800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-161400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-246500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-173300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-167300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-121700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-256800</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-317600</v>
+        <v>-578300</v>
       </c>
       <c r="E94" s="3">
-        <v>-172100</v>
+        <v>-309500</v>
       </c>
       <c r="F94" s="3">
-        <v>119900</v>
+        <v>-167700</v>
       </c>
       <c r="G94" s="3">
-        <v>-453500</v>
+        <v>116800</v>
       </c>
       <c r="H94" s="3">
-        <v>-298600</v>
+        <v>-442000</v>
       </c>
       <c r="I94" s="3">
-        <v>-849600</v>
+        <v>-291000</v>
       </c>
       <c r="J94" s="3">
+        <v>-828100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-170900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-470600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-166300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-518500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-159800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-395400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-408500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-231700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-50600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-222900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-226400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-121600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-114600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-291500</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,73 +6014,77 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-58700</v>
+        <v>-83900</v>
       </c>
       <c r="E96" s="3">
-        <v>-167800</v>
+        <v>-57200</v>
       </c>
       <c r="F96" s="3">
-        <v>-134700</v>
+        <v>-163500</v>
       </c>
       <c r="G96" s="3">
-        <v>-54700</v>
+        <v>-131200</v>
       </c>
       <c r="H96" s="3">
-        <v>-54700</v>
+        <v>-53300</v>
       </c>
       <c r="I96" s="3">
-        <v>-39500</v>
+        <v>-53400</v>
       </c>
       <c r="J96" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="K96" s="3">
         <v>-97700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-42700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-59800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-9300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-91000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-108700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-112000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-101300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-67300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-11800</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-64200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,73 +6284,79 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-287500</v>
+        <v>-500000</v>
       </c>
       <c r="E100" s="3">
-        <v>-362600</v>
+        <v>-280200</v>
       </c>
       <c r="F100" s="3">
-        <v>-319100</v>
+        <v>-353400</v>
       </c>
       <c r="G100" s="3">
-        <v>-214600</v>
+        <v>-311000</v>
       </c>
       <c r="H100" s="3">
-        <v>-223000</v>
+        <v>-209200</v>
       </c>
       <c r="I100" s="3">
-        <v>31500</v>
+        <v>-217400</v>
       </c>
       <c r="J100" s="3">
+        <v>30700</v>
+      </c>
+      <c r="K100" s="3">
         <v>-311300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>74500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-328000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>286200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-178500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-240200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-202700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-161800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-160300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-183000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-129100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-109800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>29200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-175900</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6172,69 +6420,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>111400</v>
+        <v>-106400</v>
       </c>
       <c r="E102" s="3">
-        <v>-100400</v>
+        <v>108600</v>
       </c>
       <c r="F102" s="3">
-        <v>206900</v>
+        <v>-97800</v>
       </c>
       <c r="G102" s="3">
-        <v>52100</v>
+        <v>201700</v>
       </c>
       <c r="H102" s="3">
-        <v>225600</v>
+        <v>50700</v>
       </c>
       <c r="I102" s="3">
-        <v>-576600</v>
+        <v>219900</v>
       </c>
       <c r="J102" s="3">
+        <v>-562000</v>
+      </c>
+      <c r="K102" s="3">
         <v>-252000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>234300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>64100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>199900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>26400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>88200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-184800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>155600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-123900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>260200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>39200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-43900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-30000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>79000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TIMB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TIMB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>TIMB</t>
   </si>
@@ -656,314 +656,327 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1257700</v>
+        <v>1126200</v>
       </c>
       <c r="E8" s="3">
-        <v>1213600</v>
+        <v>1159400</v>
       </c>
       <c r="F8" s="3">
-        <v>1175100</v>
+        <v>1118800</v>
       </c>
       <c r="G8" s="3">
-        <v>1130400</v>
+        <v>1083300</v>
       </c>
       <c r="H8" s="3">
-        <v>1167300</v>
+        <v>1042100</v>
       </c>
       <c r="I8" s="3">
-        <v>1124600</v>
+        <v>1076100</v>
       </c>
       <c r="J8" s="3">
+        <v>1036700</v>
+      </c>
+      <c r="K8" s="3">
         <v>1075900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>972100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>968700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>908700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>853300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>811900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>915500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>854600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1616400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>752500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>847100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>813600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>754800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>784200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>834100</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>734500</v>
+        <v>680100</v>
       </c>
       <c r="E9" s="3">
-        <v>715400</v>
+        <v>677100</v>
       </c>
       <c r="F9" s="3">
-        <v>734300</v>
+        <v>659500</v>
       </c>
       <c r="G9" s="3">
-        <v>728400</v>
+        <v>676900</v>
       </c>
       <c r="H9" s="3">
-        <v>734100</v>
+        <v>671500</v>
       </c>
       <c r="I9" s="3">
-        <v>725200</v>
+        <v>676800</v>
       </c>
       <c r="J9" s="3">
+        <v>668500</v>
+      </c>
+      <c r="K9" s="3">
         <v>697000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>611500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>563900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>546100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>522400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>499800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>414300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>399500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1122400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>350200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>307400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>366300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>329200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>366300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>367900</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>523100</v>
+        <v>446100</v>
       </c>
       <c r="E10" s="3">
-        <v>498200</v>
+        <v>482300</v>
       </c>
       <c r="F10" s="3">
-        <v>440800</v>
+        <v>459200</v>
       </c>
       <c r="G10" s="3">
-        <v>402000</v>
+        <v>406400</v>
       </c>
       <c r="H10" s="3">
-        <v>433200</v>
+        <v>370600</v>
       </c>
       <c r="I10" s="3">
-        <v>399400</v>
+        <v>399300</v>
       </c>
       <c r="J10" s="3">
+        <v>368200</v>
+      </c>
+      <c r="K10" s="3">
         <v>378900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>360600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>404800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>362500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>331000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>312100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>501200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>455100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>494000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>402400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>539800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>447200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>425600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>417900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>466200</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -988,8 +1001,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1056,8 +1070,11 @@
       <c r="X12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,144 +1141,153 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>7800</v>
+        <v>11200</v>
       </c>
       <c r="E14" s="3">
-        <v>11600</v>
+        <v>7200</v>
       </c>
       <c r="F14" s="3">
-        <v>9600</v>
+        <v>10700</v>
       </c>
       <c r="G14" s="3">
-        <v>14800</v>
+        <v>8800</v>
       </c>
       <c r="H14" s="3">
-        <v>7700</v>
+        <v>13700</v>
       </c>
       <c r="I14" s="3">
-        <v>7200</v>
+        <v>7100</v>
       </c>
       <c r="J14" s="3">
+        <v>6700</v>
+      </c>
+      <c r="K14" s="3">
         <v>4600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>10000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>7000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>13900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>9400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>11700</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>38400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>11800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>10700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>17400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>40300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>16500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>38300</v>
+        <v>36200</v>
       </c>
       <c r="E15" s="3">
-        <v>38200</v>
+        <v>35300</v>
       </c>
       <c r="F15" s="3">
+        <v>35200</v>
+      </c>
+      <c r="G15" s="3">
+        <v>34600</v>
+      </c>
+      <c r="H15" s="3">
+        <v>33000</v>
+      </c>
+      <c r="I15" s="3">
+        <v>33700</v>
+      </c>
+      <c r="J15" s="3">
+        <v>34700</v>
+      </c>
+      <c r="K15" s="3">
         <v>37500</v>
       </c>
-      <c r="G15" s="3">
-        <v>35800</v>
-      </c>
-      <c r="H15" s="3">
-        <v>36600</v>
-      </c>
-      <c r="I15" s="3">
-        <v>37700</v>
-      </c>
-      <c r="J15" s="3">
-        <v>37500</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>40200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>41000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>42200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>40700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>41400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>43800</v>
       </c>
-      <c r="Q15" s="3" t="s">
+      <c r="R15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>48900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>44300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>43900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>48900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>44800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>45900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>920900</v>
+        <v>920600</v>
       </c>
       <c r="E17" s="3">
-        <v>969300</v>
+        <v>849000</v>
       </c>
       <c r="F17" s="3">
-        <v>966900</v>
+        <v>893600</v>
       </c>
       <c r="G17" s="3">
-        <v>974200</v>
+        <v>891400</v>
       </c>
       <c r="H17" s="3">
-        <v>972700</v>
+        <v>898100</v>
       </c>
       <c r="I17" s="3">
-        <v>971900</v>
+        <v>896700</v>
       </c>
       <c r="J17" s="3">
+        <v>896000</v>
+      </c>
+      <c r="K17" s="3">
         <v>929100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>829200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>616500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>756600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>724900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>701100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>724800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>721600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1388200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>660600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>616100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>690200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>372700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>700300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>683600</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>336700</v>
+        <v>205600</v>
       </c>
       <c r="E18" s="3">
-        <v>244300</v>
+        <v>310400</v>
       </c>
       <c r="F18" s="3">
-        <v>208200</v>
+        <v>225200</v>
       </c>
       <c r="G18" s="3">
-        <v>156200</v>
+        <v>191900</v>
       </c>
       <c r="H18" s="3">
-        <v>194600</v>
+        <v>144000</v>
       </c>
       <c r="I18" s="3">
-        <v>152700</v>
+        <v>179400</v>
       </c>
       <c r="J18" s="3">
+        <v>140800</v>
+      </c>
+      <c r="K18" s="3">
         <v>146800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>142900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>352200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>152100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>128400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>110900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>190700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>133000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>228100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>92000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>231000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>123400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>382100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>84000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>150500</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,348 +1478,364 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-6100</v>
+        <v>-18200</v>
       </c>
       <c r="E20" s="3">
-        <v>-27700</v>
+        <v>-5600</v>
       </c>
       <c r="F20" s="3">
-        <v>-9500</v>
+        <v>-25500</v>
       </c>
       <c r="G20" s="3">
-        <v>-8000</v>
+        <v>-8700</v>
       </c>
       <c r="H20" s="3">
-        <v>5100</v>
+        <v>-7400</v>
       </c>
       <c r="I20" s="3">
-        <v>3100</v>
+        <v>4700</v>
       </c>
       <c r="J20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K20" s="3">
         <v>-20100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>7400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>20300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>36500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>29500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-47500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-56900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-9700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>179600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-6300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>681300</v>
+        <v>511600</v>
       </c>
       <c r="E21" s="3">
-        <v>568400</v>
+        <v>628100</v>
       </c>
       <c r="F21" s="3">
-        <v>566400</v>
+        <v>524000</v>
       </c>
       <c r="G21" s="3">
-        <v>504400</v>
+        <v>522200</v>
       </c>
       <c r="H21" s="3">
-        <v>572200</v>
+        <v>465000</v>
       </c>
       <c r="I21" s="3">
-        <v>532600</v>
+        <v>527400</v>
       </c>
       <c r="J21" s="3">
+        <v>491000</v>
+      </c>
+      <c r="K21" s="3">
         <v>465200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>438000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>662400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>440200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>440600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>373400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>490000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>356300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>714700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>333700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>427400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>388300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>791500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>327300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>344400</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>89600</v>
+        <v>78700</v>
       </c>
       <c r="E22" s="3">
-        <v>53700</v>
+        <v>82600</v>
       </c>
       <c r="F22" s="3">
-        <v>75900</v>
+        <v>49500</v>
       </c>
       <c r="G22" s="3">
-        <v>36800</v>
+        <v>70000</v>
       </c>
       <c r="H22" s="3">
-        <v>75300</v>
+        <v>33900</v>
       </c>
       <c r="I22" s="3">
-        <v>83600</v>
+        <v>69400</v>
       </c>
       <c r="J22" s="3">
+        <v>77100</v>
+      </c>
+      <c r="K22" s="3">
         <v>67900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>58300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>56700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>47900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>43500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>37600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>38200</v>
       </c>
-      <c r="Q22" s="3" t="s">
+      <c r="R22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>45400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>35700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>44100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>45500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>40300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>42800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>241000</v>
+        <v>108600</v>
       </c>
       <c r="E23" s="3">
-        <v>162900</v>
+        <v>222100</v>
       </c>
       <c r="F23" s="3">
-        <v>122900</v>
+        <v>150100</v>
       </c>
       <c r="G23" s="3">
-        <v>111500</v>
+        <v>113300</v>
       </c>
       <c r="H23" s="3">
-        <v>124400</v>
+        <v>102800</v>
       </c>
       <c r="I23" s="3">
-        <v>72100</v>
+        <v>114700</v>
       </c>
       <c r="J23" s="3">
+        <v>66500</v>
+      </c>
+      <c r="K23" s="3">
         <v>58800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>91900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>315800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>109600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>121400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>68700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>182000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>85500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>125800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>46500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>187500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>73300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>521300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>34800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>24000</v>
+        <v>12700</v>
       </c>
       <c r="E24" s="3">
-        <v>19400</v>
+        <v>22100</v>
       </c>
       <c r="F24" s="3">
-        <v>-2700</v>
+        <v>17800</v>
       </c>
       <c r="G24" s="3">
-        <v>28800</v>
+        <v>-2500</v>
       </c>
       <c r="H24" s="3">
-        <v>16600</v>
+        <v>26500</v>
       </c>
       <c r="I24" s="3">
-        <v>-17600</v>
+        <v>15300</v>
       </c>
       <c r="J24" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="K24" s="3">
         <v>2800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>8500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>110900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-90300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-8800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>16900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>39000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>17600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>17800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-32100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>163300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>12400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>217000</v>
+        <v>96000</v>
       </c>
       <c r="E26" s="3">
-        <v>143500</v>
+        <v>200000</v>
       </c>
       <c r="F26" s="3">
-        <v>125600</v>
+        <v>132300</v>
       </c>
       <c r="G26" s="3">
+        <v>115700</v>
+      </c>
+      <c r="H26" s="3">
+        <v>76200</v>
+      </c>
+      <c r="I26" s="3">
+        <v>99400</v>
+      </c>
+      <c r="J26" s="3">
         <v>82700</v>
       </c>
-      <c r="H26" s="3">
-        <v>107900</v>
-      </c>
-      <c r="I26" s="3">
-        <v>89700</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>56000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>83400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>204900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>199900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>130200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>51800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>198300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>76000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>86800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>28900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>169600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>105400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>358100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>22500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>217000</v>
+        <v>96000</v>
       </c>
       <c r="E27" s="3">
-        <v>143500</v>
+        <v>200000</v>
       </c>
       <c r="F27" s="3">
-        <v>125600</v>
+        <v>132300</v>
       </c>
       <c r="G27" s="3">
+        <v>115700</v>
+      </c>
+      <c r="H27" s="3">
+        <v>76200</v>
+      </c>
+      <c r="I27" s="3">
+        <v>99400</v>
+      </c>
+      <c r="J27" s="3">
         <v>82700</v>
       </c>
-      <c r="H27" s="3">
-        <v>107900</v>
-      </c>
-      <c r="I27" s="3">
-        <v>89700</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>56000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>83400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>204900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>199900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>130200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>51800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>198300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>76000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>86800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>28900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>169600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>105400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>358100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>22500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,144 +2328,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>6100</v>
+        <v>18200</v>
       </c>
       <c r="E32" s="3">
-        <v>27700</v>
+        <v>5600</v>
       </c>
       <c r="F32" s="3">
-        <v>9500</v>
+        <v>25500</v>
       </c>
       <c r="G32" s="3">
-        <v>8000</v>
+        <v>8700</v>
       </c>
       <c r="H32" s="3">
-        <v>-5100</v>
+        <v>7400</v>
       </c>
       <c r="I32" s="3">
-        <v>-3100</v>
+        <v>-4700</v>
       </c>
       <c r="J32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="K32" s="3">
         <v>20100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-7400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-20300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-36500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-29500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>47500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>56900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>9700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-179600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>6300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>217000</v>
+        <v>96000</v>
       </c>
       <c r="E33" s="3">
-        <v>143500</v>
+        <v>200000</v>
       </c>
       <c r="F33" s="3">
-        <v>125600</v>
+        <v>132300</v>
       </c>
       <c r="G33" s="3">
+        <v>115700</v>
+      </c>
+      <c r="H33" s="3">
+        <v>76200</v>
+      </c>
+      <c r="I33" s="3">
+        <v>99400</v>
+      </c>
+      <c r="J33" s="3">
         <v>82700</v>
       </c>
-      <c r="H33" s="3">
-        <v>107900</v>
-      </c>
-      <c r="I33" s="3">
-        <v>89700</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>56000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>83400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>204900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>199900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>130200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>51800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>198300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>76000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>86800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>28900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>169600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>105400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>358100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>22500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>217000</v>
+        <v>96000</v>
       </c>
       <c r="E35" s="3">
-        <v>143500</v>
+        <v>200000</v>
       </c>
       <c r="F35" s="3">
-        <v>125600</v>
+        <v>132300</v>
       </c>
       <c r="G35" s="3">
+        <v>115700</v>
+      </c>
+      <c r="H35" s="3">
+        <v>76200</v>
+      </c>
+      <c r="I35" s="3">
+        <v>99400</v>
+      </c>
+      <c r="J35" s="3">
         <v>82700</v>
       </c>
-      <c r="H35" s="3">
-        <v>107900</v>
-      </c>
-      <c r="I35" s="3">
-        <v>89700</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>56000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>83400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>204900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>199900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>130200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>51800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>198300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>76000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>86800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>28900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>169600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>105400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>358100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>22500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,620 +2744,648 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>616900</v>
+        <v>366700</v>
       </c>
       <c r="E41" s="3">
-        <v>723300</v>
+        <v>568700</v>
       </c>
       <c r="F41" s="3">
-        <v>614700</v>
+        <v>666800</v>
       </c>
       <c r="G41" s="3">
-        <v>712500</v>
+        <v>566700</v>
       </c>
       <c r="H41" s="3">
-        <v>510800</v>
+        <v>656800</v>
       </c>
       <c r="I41" s="3">
-        <v>460100</v>
+        <v>470900</v>
       </c>
       <c r="J41" s="3">
+        <v>424100</v>
+      </c>
+      <c r="K41" s="3">
         <v>240200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>823100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1055300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>819200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>726000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>508200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>504000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>413900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>605800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>284000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>422000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>164300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>118100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>171200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>201300</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>392500</v>
+        <v>256100</v>
       </c>
       <c r="E42" s="3">
-        <v>167800</v>
+        <v>361900</v>
       </c>
       <c r="F42" s="3">
-        <v>54400</v>
+        <v>154700</v>
       </c>
       <c r="G42" s="3">
-        <v>65200</v>
+        <v>50200</v>
       </c>
       <c r="H42" s="3">
-        <v>439000</v>
+        <v>60100</v>
       </c>
       <c r="I42" s="3">
-        <v>282100</v>
+        <v>404700</v>
       </c>
       <c r="J42" s="3">
+        <v>260000</v>
+      </c>
+      <c r="K42" s="3">
         <v>218000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>837500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>922000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>665600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>653600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>299700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>405200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>294700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>50300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>7000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>120900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>146700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>87400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>140900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>146900</v>
       </c>
     </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1031700</v>
+        <v>976000</v>
       </c>
       <c r="E43" s="3">
-        <v>998600</v>
+        <v>951100</v>
       </c>
       <c r="F43" s="3">
-        <v>898500</v>
+        <v>920600</v>
       </c>
       <c r="G43" s="3">
-        <v>916900</v>
+        <v>828300</v>
       </c>
       <c r="H43" s="3">
-        <v>924800</v>
+        <v>845200</v>
       </c>
       <c r="I43" s="3">
-        <v>885300</v>
+        <v>852500</v>
       </c>
       <c r="J43" s="3">
+        <v>816200</v>
+      </c>
+      <c r="K43" s="3">
         <v>958900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>898400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>955400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>875900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>867400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>843400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>948600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>956400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>849600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>835500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>923500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>785800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>661200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>670700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>648700</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>66500</v>
+        <v>74800</v>
       </c>
       <c r="E44" s="3">
-        <v>83200</v>
+        <v>61300</v>
       </c>
       <c r="F44" s="3">
-        <v>75000</v>
+        <v>76700</v>
       </c>
       <c r="G44" s="3">
-        <v>60400</v>
+        <v>69200</v>
       </c>
       <c r="H44" s="3">
-        <v>47300</v>
+        <v>55600</v>
       </c>
       <c r="I44" s="3">
-        <v>55700</v>
+        <v>43600</v>
       </c>
       <c r="J44" s="3">
+        <v>51400</v>
+      </c>
+      <c r="K44" s="3">
         <v>56100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>45700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>40900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>46600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>43700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>56300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>48300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>40300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>40100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>47900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>37500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>39600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>37800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>40200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>34300</v>
       </c>
     </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>178000</v>
+        <v>235800</v>
       </c>
       <c r="E45" s="3">
-        <v>198900</v>
+        <v>164100</v>
       </c>
       <c r="F45" s="3">
-        <v>217400</v>
+        <v>183400</v>
       </c>
       <c r="G45" s="3">
-        <v>229800</v>
+        <v>200400</v>
       </c>
       <c r="H45" s="3">
-        <v>155300</v>
+        <v>211900</v>
       </c>
       <c r="I45" s="3">
-        <v>189000</v>
+        <v>143200</v>
       </c>
       <c r="J45" s="3">
+        <v>174200</v>
+      </c>
+      <c r="K45" s="3">
         <v>279700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>192100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>134300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>132600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>170200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>172100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>131600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>164900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>101300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>108500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>57500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>121800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>152000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>206800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>91300</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2285600</v>
+        <v>1909400</v>
       </c>
       <c r="E46" s="3">
-        <v>2171900</v>
+        <v>2107100</v>
       </c>
       <c r="F46" s="3">
-        <v>1860100</v>
+        <v>2002200</v>
       </c>
       <c r="G46" s="3">
-        <v>1984800</v>
+        <v>1714700</v>
       </c>
       <c r="H46" s="3">
-        <v>2077200</v>
+        <v>1829700</v>
       </c>
       <c r="I46" s="3">
-        <v>1872100</v>
+        <v>1914900</v>
       </c>
       <c r="J46" s="3">
+        <v>1725900</v>
+      </c>
+      <c r="K46" s="3">
         <v>1752900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2796900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3107900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2539900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2460900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1879800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2037500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1870100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1647200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1283000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1561500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1258200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1056500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1229800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1122400</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>552400</v>
+        <v>507000</v>
       </c>
       <c r="E47" s="3">
-        <v>575700</v>
+        <v>509200</v>
       </c>
       <c r="F47" s="3">
-        <v>719100</v>
+        <v>530700</v>
       </c>
       <c r="G47" s="3">
-        <v>646600</v>
+        <v>662900</v>
       </c>
       <c r="H47" s="3">
-        <v>642300</v>
+        <v>596000</v>
       </c>
       <c r="I47" s="3">
-        <v>692000</v>
+        <v>592200</v>
       </c>
       <c r="J47" s="3">
+        <v>637900</v>
+      </c>
+      <c r="K47" s="3">
         <v>683700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>698500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>693400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>411600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>334300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>367500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>444200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>410400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>665000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>603700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>609100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>786100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>766800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>294700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4491800</v>
+        <v>4192100</v>
       </c>
       <c r="E48" s="3">
-        <v>4534800</v>
+        <v>4140800</v>
       </c>
       <c r="F48" s="3">
-        <v>4626700</v>
+        <v>4180400</v>
       </c>
       <c r="G48" s="3">
-        <v>4675200</v>
+        <v>4265200</v>
       </c>
       <c r="H48" s="3">
-        <v>4541700</v>
+        <v>4309900</v>
       </c>
       <c r="I48" s="3">
-        <v>4630100</v>
+        <v>4186900</v>
       </c>
       <c r="J48" s="3">
+        <v>4268300</v>
+      </c>
+      <c r="K48" s="3">
         <v>4739300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3963300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3695400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3515000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3373600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3450400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3542300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3380900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3415200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3190900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3253000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3129600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2907800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2970000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2096500</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3131600</v>
+        <v>2855000</v>
       </c>
       <c r="E49" s="3">
-        <v>3161200</v>
+        <v>2886900</v>
       </c>
       <c r="F49" s="3">
-        <v>3216800</v>
+        <v>2914200</v>
       </c>
       <c r="G49" s="3">
-        <v>3274100</v>
+        <v>2965400</v>
       </c>
       <c r="H49" s="3">
-        <v>3290200</v>
+        <v>3018300</v>
       </c>
       <c r="I49" s="3">
-        <v>3196600</v>
+        <v>3033100</v>
       </c>
       <c r="J49" s="3">
+        <v>2946800</v>
+      </c>
+      <c r="K49" s="3">
         <v>3155600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2179800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2136500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1459200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1444800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1650300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1766600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1755400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1826000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1703000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1785700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1846400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1791600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1947200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1998900</v>
       </c>
     </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,76 +3523,82 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>613800</v>
+        <v>575400</v>
       </c>
       <c r="E52" s="3">
-        <v>774500</v>
+        <v>565900</v>
       </c>
       <c r="F52" s="3">
-        <v>742100</v>
+        <v>714000</v>
       </c>
       <c r="G52" s="3">
-        <v>761600</v>
+        <v>684100</v>
       </c>
       <c r="H52" s="3">
-        <v>753800</v>
+        <v>702100</v>
       </c>
       <c r="I52" s="3">
-        <v>569800</v>
+        <v>694900</v>
       </c>
       <c r="J52" s="3">
+        <v>525300</v>
+      </c>
+      <c r="K52" s="3">
         <v>552700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>442800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>422300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>931700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>878600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>344500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>361100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>333500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>295600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>270900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>243100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>278500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>276200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>448900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>461900</v>
       </c>
     </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,76 +3665,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>11075200</v>
+        <v>10038800</v>
       </c>
       <c r="E54" s="3">
-        <v>11218100</v>
+        <v>10209900</v>
       </c>
       <c r="F54" s="3">
-        <v>11164700</v>
+        <v>10341600</v>
       </c>
       <c r="G54" s="3">
-        <v>11342300</v>
+        <v>10292400</v>
       </c>
       <c r="H54" s="3">
-        <v>11305400</v>
+        <v>10456100</v>
       </c>
       <c r="I54" s="3">
-        <v>10960500</v>
+        <v>10422000</v>
       </c>
       <c r="J54" s="3">
+        <v>10104100</v>
+      </c>
+      <c r="K54" s="3">
         <v>10884200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10081300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10055500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8857300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8492200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7692600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8151800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7750300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7849100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7051500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7452400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7298800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6798900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6890500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5980300</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,416 +3792,435 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>924400</v>
+        <v>722800</v>
       </c>
       <c r="E57" s="3">
-        <v>772400</v>
+        <v>852100</v>
       </c>
       <c r="F57" s="3">
-        <v>731700</v>
+        <v>712000</v>
       </c>
       <c r="G57" s="3">
-        <v>774300</v>
+        <v>674500</v>
       </c>
       <c r="H57" s="3">
-        <v>849200</v>
+        <v>713800</v>
       </c>
       <c r="I57" s="3">
-        <v>831200</v>
+        <v>782900</v>
       </c>
       <c r="J57" s="3">
+        <v>766200</v>
+      </c>
+      <c r="K57" s="3">
         <v>818400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>618900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>659500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>534400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>501500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>497900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>612300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>423900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>407700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>470400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>724600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>548300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>512000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>707700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>809000</v>
       </c>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>616500</v>
+        <v>481800</v>
       </c>
       <c r="E58" s="3">
-        <v>839800</v>
+        <v>568300</v>
       </c>
       <c r="F58" s="3">
-        <v>857200</v>
+        <v>774200</v>
       </c>
       <c r="G58" s="3">
-        <v>778900</v>
+        <v>790200</v>
       </c>
       <c r="H58" s="3">
-        <v>705900</v>
+        <v>718000</v>
       </c>
       <c r="I58" s="3">
-        <v>401100</v>
+        <v>650800</v>
       </c>
       <c r="J58" s="3">
+        <v>369800</v>
+      </c>
+      <c r="K58" s="3">
         <v>390000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>277400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>365000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>359000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>509600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>630200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>537000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>543200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>513900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>363300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>416900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>432400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>233000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>249900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1041200</v>
+        <v>1155400</v>
       </c>
       <c r="E59" s="3">
-        <v>1137400</v>
+        <v>959800</v>
       </c>
       <c r="F59" s="3">
-        <v>1068900</v>
+        <v>1048500</v>
       </c>
       <c r="G59" s="3">
-        <v>1126200</v>
+        <v>985400</v>
       </c>
       <c r="H59" s="3">
-        <v>1074000</v>
+        <v>1038200</v>
       </c>
       <c r="I59" s="3">
-        <v>837300</v>
+        <v>990100</v>
       </c>
       <c r="J59" s="3">
+        <v>771900</v>
+      </c>
+      <c r="K59" s="3">
         <v>730500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>900400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1117300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>482200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>462100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>350500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>475400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>332200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>307800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>229800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>357800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>383300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>256100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>261700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>345900</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2582000</v>
+        <v>2359900</v>
       </c>
       <c r="E60" s="3">
-        <v>2749500</v>
+        <v>2380300</v>
       </c>
       <c r="F60" s="3">
-        <v>2657800</v>
+        <v>2534700</v>
       </c>
       <c r="G60" s="3">
-        <v>2679300</v>
+        <v>2450100</v>
       </c>
       <c r="H60" s="3">
-        <v>2629100</v>
+        <v>2470000</v>
       </c>
       <c r="I60" s="3">
-        <v>2069600</v>
+        <v>2423700</v>
       </c>
       <c r="J60" s="3">
+        <v>1907900</v>
+      </c>
+      <c r="K60" s="3">
         <v>1938900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1796700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2141800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1375500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1473300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1478600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1624700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1299200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1229400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1063500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1499300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1364000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1001100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1219300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1324000</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2595800</v>
+        <v>2408100</v>
       </c>
       <c r="E61" s="3">
-        <v>2656100</v>
+        <v>2393000</v>
       </c>
       <c r="F61" s="3">
-        <v>2728600</v>
+        <v>2448600</v>
       </c>
       <c r="G61" s="3">
-        <v>2858200</v>
+        <v>2515400</v>
       </c>
       <c r="H61" s="3">
-        <v>2861900</v>
+        <v>2634900</v>
       </c>
       <c r="I61" s="3">
-        <v>3089100</v>
+        <v>2638300</v>
       </c>
       <c r="J61" s="3">
+        <v>2847800</v>
+      </c>
+      <c r="K61" s="3">
         <v>3116100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2431100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2240600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2043100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1939900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1417100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1561600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1494800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1638000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1534300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1395000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1393500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1461300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1503800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>505100</v>
       </c>
     </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>683300</v>
+        <v>647100</v>
       </c>
       <c r="E62" s="3">
-        <v>686900</v>
+        <v>629900</v>
       </c>
       <c r="F62" s="3">
-        <v>702300</v>
+        <v>633200</v>
       </c>
       <c r="G62" s="3">
-        <v>751100</v>
+        <v>647400</v>
       </c>
       <c r="H62" s="3">
-        <v>724200</v>
+        <v>692400</v>
       </c>
       <c r="I62" s="3">
-        <v>732000</v>
+        <v>667600</v>
       </c>
       <c r="J62" s="3">
+        <v>674800</v>
+      </c>
+      <c r="K62" s="3">
         <v>752300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>643300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>605500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>475800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>475600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>407100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>428600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>427700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>479400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>421400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>415000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>459000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>451600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>440000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>446900</v>
       </c>
     </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,76 +4429,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5861100</v>
+        <v>5415100</v>
       </c>
       <c r="E66" s="3">
-        <v>6092500</v>
+        <v>5403200</v>
       </c>
       <c r="F66" s="3">
-        <v>6088700</v>
+        <v>5616500</v>
       </c>
       <c r="G66" s="3">
-        <v>6288600</v>
+        <v>5612900</v>
       </c>
       <c r="H66" s="3">
-        <v>6215200</v>
+        <v>5797300</v>
       </c>
       <c r="I66" s="3">
-        <v>5890800</v>
+        <v>5729600</v>
       </c>
       <c r="J66" s="3">
+        <v>5430500</v>
+      </c>
+      <c r="K66" s="3">
         <v>5807300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4871000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4987900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3894400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3888700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3302800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3614900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3221800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3346700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3019200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3309300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3216600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2914000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3163100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2276100</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,76 +4811,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2443300</v>
+        <v>2070500</v>
       </c>
       <c r="E72" s="3">
-        <v>2354800</v>
+        <v>2252400</v>
       </c>
       <c r="F72" s="3">
-        <v>2304700</v>
+        <v>2170800</v>
       </c>
       <c r="G72" s="3">
-        <v>2282400</v>
+        <v>2124700</v>
       </c>
       <c r="H72" s="3">
-        <v>2318800</v>
+        <v>2104100</v>
       </c>
       <c r="I72" s="3">
-        <v>2298900</v>
+        <v>2137700</v>
       </c>
       <c r="J72" s="3">
+        <v>2119200</v>
+      </c>
+      <c r="K72" s="3">
         <v>2311700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2368000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2277700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2179300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1930100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1803500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1831900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1835100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2161300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2204900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2251400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2160900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2071600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1811200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1788100</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5095,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5214100</v>
+        <v>4623700</v>
       </c>
       <c r="E76" s="3">
-        <v>5125600</v>
+        <v>4806700</v>
       </c>
       <c r="F76" s="3">
-        <v>5076100</v>
+        <v>4725100</v>
       </c>
       <c r="G76" s="3">
-        <v>5053700</v>
+        <v>4679400</v>
       </c>
       <c r="H76" s="3">
-        <v>5090100</v>
+        <v>4658800</v>
       </c>
       <c r="I76" s="3">
-        <v>5069800</v>
+        <v>4692400</v>
       </c>
       <c r="J76" s="3">
+        <v>4673600</v>
+      </c>
+      <c r="K76" s="3">
         <v>5076900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5210200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5067600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4962900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4603400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4389800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4536900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4528500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4502400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4032300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4143200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4082200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3884900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3727500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3704200</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>217000</v>
+        <v>96000</v>
       </c>
       <c r="E81" s="3">
-        <v>143500</v>
+        <v>200000</v>
       </c>
       <c r="F81" s="3">
-        <v>125600</v>
+        <v>132300</v>
       </c>
       <c r="G81" s="3">
+        <v>115700</v>
+      </c>
+      <c r="H81" s="3">
+        <v>76200</v>
+      </c>
+      <c r="I81" s="3">
+        <v>99400</v>
+      </c>
+      <c r="J81" s="3">
         <v>82700</v>
       </c>
-      <c r="H81" s="3">
-        <v>107900</v>
-      </c>
-      <c r="I81" s="3">
-        <v>89700</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>56000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>83400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>204900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>199900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>130200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>51800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>198300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>76000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>86800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>28900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>169600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>105400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>358100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>22500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,76 +5413,80 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>350700</v>
+        <v>324200</v>
       </c>
       <c r="E83" s="3">
-        <v>351800</v>
+        <v>323300</v>
       </c>
       <c r="F83" s="3">
-        <v>367700</v>
+        <v>324300</v>
       </c>
       <c r="G83" s="3">
-        <v>356200</v>
+        <v>339000</v>
       </c>
       <c r="H83" s="3">
-        <v>372400</v>
+        <v>328300</v>
       </c>
       <c r="I83" s="3">
-        <v>376800</v>
+        <v>343300</v>
       </c>
       <c r="J83" s="3">
+        <v>347400</v>
+      </c>
+      <c r="K83" s="3">
         <v>338600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>287700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>289800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>282800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>275700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>267100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>269800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>270800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>543500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>251500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>195800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>269500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>229800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>249700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>190500</v>
       </c>
     </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5837,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>971800</v>
+        <v>304100</v>
       </c>
       <c r="E89" s="3">
-        <v>698300</v>
+        <v>895900</v>
       </c>
       <c r="F89" s="3">
-        <v>423300</v>
+        <v>643700</v>
       </c>
       <c r="G89" s="3">
-        <v>395900</v>
+        <v>390200</v>
       </c>
       <c r="H89" s="3">
-        <v>701900</v>
+        <v>365000</v>
       </c>
       <c r="I89" s="3">
-        <v>696000</v>
+        <v>647000</v>
       </c>
       <c r="J89" s="3">
+        <v>641600</v>
+      </c>
+      <c r="K89" s="3">
         <v>267500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>230200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>630400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>558400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>432300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>364700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>723800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>426300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>549100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>87000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>666100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>394600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>187500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>55400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>546400</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,76 +5937,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1354500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1291900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-998200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-925700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1288500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1375200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-977600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1049600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1328000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2157400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-896500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-175400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-247700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-286500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-165600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-310800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-161400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-246500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-173300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-167300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-121700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-256800</v>
       </c>
     </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6148,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-578300</v>
+        <v>-135200</v>
       </c>
       <c r="E94" s="3">
-        <v>-309500</v>
+        <v>-533100</v>
       </c>
       <c r="F94" s="3">
-        <v>-167700</v>
+        <v>-285300</v>
       </c>
       <c r="G94" s="3">
-        <v>116800</v>
+        <v>-154600</v>
       </c>
       <c r="H94" s="3">
-        <v>-442000</v>
+        <v>107700</v>
       </c>
       <c r="I94" s="3">
-        <v>-291000</v>
+        <v>-407400</v>
       </c>
       <c r="J94" s="3">
+        <v>-268300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-828100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-170900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-470600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-166300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-518500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-159800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-395400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-408500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-231700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-50600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-222900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-226400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-121600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-114600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-291500</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,76 +6248,80 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-83900</v>
+        <v>-119200</v>
       </c>
       <c r="E96" s="3">
-        <v>-57200</v>
+        <v>-77300</v>
       </c>
       <c r="F96" s="3">
-        <v>-163500</v>
+        <v>-52800</v>
       </c>
       <c r="G96" s="3">
-        <v>-131200</v>
+        <v>-150700</v>
       </c>
       <c r="H96" s="3">
-        <v>-53300</v>
+        <v>-121000</v>
       </c>
       <c r="I96" s="3">
-        <v>-53400</v>
+        <v>-49100</v>
       </c>
       <c r="J96" s="3">
+        <v>-49200</v>
+      </c>
+      <c r="K96" s="3">
         <v>-38500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-97700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-42700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-59800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-9300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-91000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-108700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-5700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-112000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-101300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-67300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-11800</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-64200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,76 +6530,82 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-500000</v>
+        <v>-370800</v>
       </c>
       <c r="E100" s="3">
-        <v>-280200</v>
+        <v>-460900</v>
       </c>
       <c r="F100" s="3">
-        <v>-353400</v>
+        <v>-258300</v>
       </c>
       <c r="G100" s="3">
-        <v>-311000</v>
+        <v>-325800</v>
       </c>
       <c r="H100" s="3">
-        <v>-209200</v>
+        <v>-286700</v>
       </c>
       <c r="I100" s="3">
-        <v>-217400</v>
+        <v>-192800</v>
       </c>
       <c r="J100" s="3">
+        <v>-200400</v>
+      </c>
+      <c r="K100" s="3">
         <v>30700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-311300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>74500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-328000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>286200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-178500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-240200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-202700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-161800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-160300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-183000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-129100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-109800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>29200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-175900</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6423,72 +6672,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-106400</v>
+        <v>-202000</v>
       </c>
       <c r="E102" s="3">
-        <v>108600</v>
+        <v>-98100</v>
       </c>
       <c r="F102" s="3">
-        <v>-97800</v>
+        <v>100100</v>
       </c>
       <c r="G102" s="3">
-        <v>201700</v>
+        <v>-90200</v>
       </c>
       <c r="H102" s="3">
-        <v>50700</v>
+        <v>185900</v>
       </c>
       <c r="I102" s="3">
-        <v>219900</v>
+        <v>46800</v>
       </c>
       <c r="J102" s="3">
+        <v>202700</v>
+      </c>
+      <c r="K102" s="3">
         <v>-562000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-252000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>234300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>64100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>199900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>26400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>88200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-184800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>155600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-123900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>260200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>39200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-43900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-30000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>79000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TIMB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TIMB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>TIMB</t>
   </si>
@@ -656,327 +656,340 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1126200</v>
+        <v>1132700</v>
       </c>
       <c r="E8" s="3">
-        <v>1159400</v>
+        <v>1095500</v>
       </c>
       <c r="F8" s="3">
-        <v>1118800</v>
+        <v>1127800</v>
       </c>
       <c r="G8" s="3">
-        <v>1083300</v>
+        <v>1088300</v>
       </c>
       <c r="H8" s="3">
-        <v>1042100</v>
+        <v>1053800</v>
       </c>
       <c r="I8" s="3">
-        <v>1076100</v>
+        <v>1013700</v>
       </c>
       <c r="J8" s="3">
+        <v>1046800</v>
+      </c>
+      <c r="K8" s="3">
         <v>1036700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1075900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>972100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>968700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>908700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>853300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>811900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>915500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>854600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1616400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>752500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>847100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>813600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>754800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>784200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>834100</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>680100</v>
+        <v>655400</v>
       </c>
       <c r="E9" s="3">
-        <v>677100</v>
+        <v>661600</v>
       </c>
       <c r="F9" s="3">
-        <v>659500</v>
+        <v>658700</v>
       </c>
       <c r="G9" s="3">
-        <v>676900</v>
+        <v>641600</v>
       </c>
       <c r="H9" s="3">
-        <v>671500</v>
+        <v>658500</v>
       </c>
       <c r="I9" s="3">
-        <v>676800</v>
+        <v>653200</v>
       </c>
       <c r="J9" s="3">
+        <v>658400</v>
+      </c>
+      <c r="K9" s="3">
         <v>668500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>697000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>611500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>563900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>546100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>522400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>499800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>414300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>399500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1122400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>350200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>307400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>366300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>329200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>366300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>367900</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>446100</v>
+        <v>477400</v>
       </c>
       <c r="E10" s="3">
-        <v>482300</v>
+        <v>434000</v>
       </c>
       <c r="F10" s="3">
-        <v>459200</v>
+        <v>469100</v>
       </c>
       <c r="G10" s="3">
-        <v>406400</v>
+        <v>446700</v>
       </c>
       <c r="H10" s="3">
-        <v>370600</v>
+        <v>395300</v>
       </c>
       <c r="I10" s="3">
-        <v>399300</v>
+        <v>360500</v>
       </c>
       <c r="J10" s="3">
+        <v>388500</v>
+      </c>
+      <c r="K10" s="3">
         <v>368200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>378900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>360600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>404800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>362500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>331000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>312100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>501200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>455100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>494000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>402400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>539800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>447200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>425600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>417900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>466200</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1002,8 +1015,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1073,8 +1087,11 @@
       <c r="Y12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,150 +1161,159 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>11200</v>
+        <v>2300</v>
       </c>
       <c r="E14" s="3">
-        <v>7200</v>
+        <v>10900</v>
       </c>
       <c r="F14" s="3">
+        <v>7000</v>
+      </c>
+      <c r="G14" s="3">
+        <v>10400</v>
+      </c>
+      <c r="H14" s="3">
+        <v>8600</v>
+      </c>
+      <c r="I14" s="3">
+        <v>13300</v>
+      </c>
+      <c r="J14" s="3">
+        <v>6900</v>
+      </c>
+      <c r="K14" s="3">
+        <v>6700</v>
+      </c>
+      <c r="L14" s="3">
+        <v>4600</v>
+      </c>
+      <c r="M14" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N14" s="3">
+        <v>7000</v>
+      </c>
+      <c r="O14" s="3">
+        <v>6700</v>
+      </c>
+      <c r="P14" s="3">
+        <v>13900</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>9400</v>
+      </c>
+      <c r="R14" s="3">
+        <v>11700</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
+        <v>38400</v>
+      </c>
+      <c r="U14" s="3">
+        <v>11800</v>
+      </c>
+      <c r="V14" s="3">
         <v>10700</v>
       </c>
-      <c r="G14" s="3">
-        <v>8800</v>
-      </c>
-      <c r="H14" s="3">
-        <v>13700</v>
-      </c>
-      <c r="I14" s="3">
-        <v>7100</v>
-      </c>
-      <c r="J14" s="3">
-        <v>6700</v>
-      </c>
-      <c r="K14" s="3">
-        <v>4600</v>
-      </c>
-      <c r="L14" s="3">
-        <v>10000</v>
-      </c>
-      <c r="M14" s="3">
-        <v>7000</v>
-      </c>
-      <c r="N14" s="3">
-        <v>6700</v>
-      </c>
-      <c r="O14" s="3">
-        <v>13900</v>
-      </c>
-      <c r="P14" s="3">
-        <v>9400</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>11700</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3">
-        <v>38400</v>
-      </c>
-      <c r="T14" s="3">
-        <v>11800</v>
-      </c>
-      <c r="U14" s="3">
-        <v>10700</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>17400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>40300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>16500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>36200</v>
+        <v>35700</v>
       </c>
       <c r="E15" s="3">
-        <v>35300</v>
+        <v>35200</v>
       </c>
       <c r="F15" s="3">
-        <v>35200</v>
+        <v>34400</v>
       </c>
       <c r="G15" s="3">
-        <v>34600</v>
+        <v>34300</v>
       </c>
       <c r="H15" s="3">
-        <v>33000</v>
+        <v>33700</v>
       </c>
       <c r="I15" s="3">
-        <v>33700</v>
+        <v>32100</v>
       </c>
       <c r="J15" s="3">
+        <v>32800</v>
+      </c>
+      <c r="K15" s="3">
         <v>34700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>37500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>40200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>41000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>42200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>40700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>41400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>43800</v>
       </c>
-      <c r="R15" s="3" t="s">
+      <c r="S15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>48900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>44300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>43900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>48900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>44800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>45900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1336,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>920600</v>
+        <v>885800</v>
       </c>
       <c r="E17" s="3">
-        <v>849000</v>
+        <v>895500</v>
       </c>
       <c r="F17" s="3">
-        <v>893600</v>
+        <v>825900</v>
       </c>
       <c r="G17" s="3">
-        <v>891400</v>
+        <v>869300</v>
       </c>
       <c r="H17" s="3">
-        <v>898100</v>
+        <v>867100</v>
       </c>
       <c r="I17" s="3">
-        <v>896700</v>
+        <v>873600</v>
       </c>
       <c r="J17" s="3">
+        <v>872300</v>
+      </c>
+      <c r="K17" s="3">
         <v>896000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>929100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>829200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>616500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>756600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>724900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>701100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>724800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>721600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1388200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>660600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>616100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>690200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>372700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>700300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>683600</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>205600</v>
+        <v>247000</v>
       </c>
       <c r="E18" s="3">
-        <v>310400</v>
+        <v>200000</v>
       </c>
       <c r="F18" s="3">
-        <v>225200</v>
+        <v>302000</v>
       </c>
       <c r="G18" s="3">
-        <v>191900</v>
+        <v>219100</v>
       </c>
       <c r="H18" s="3">
-        <v>144000</v>
+        <v>186700</v>
       </c>
       <c r="I18" s="3">
-        <v>179400</v>
+        <v>140100</v>
       </c>
       <c r="J18" s="3">
+        <v>174500</v>
+      </c>
+      <c r="K18" s="3">
         <v>140800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>146800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>142900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>352200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>152100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>128400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>110900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>190700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>133000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>228100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>92000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>231000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>123400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>382100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>84000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>150500</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,363 +1512,379 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-18200</v>
+        <v>-5500</v>
       </c>
       <c r="E20" s="3">
-        <v>-5600</v>
+        <v>-17700</v>
       </c>
       <c r="F20" s="3">
-        <v>-25500</v>
+        <v>-5500</v>
       </c>
       <c r="G20" s="3">
-        <v>-8700</v>
+        <v>-24800</v>
       </c>
       <c r="H20" s="3">
-        <v>-7400</v>
+        <v>-8500</v>
       </c>
       <c r="I20" s="3">
-        <v>4700</v>
+        <v>-7200</v>
       </c>
       <c r="J20" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K20" s="3">
         <v>2800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-20100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>20300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>36500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>29500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-47500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-56900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-9700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>179600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>511600</v>
+        <v>557000</v>
       </c>
       <c r="E21" s="3">
-        <v>628100</v>
+        <v>497700</v>
       </c>
       <c r="F21" s="3">
-        <v>524000</v>
+        <v>611000</v>
       </c>
       <c r="G21" s="3">
-        <v>522200</v>
+        <v>509700</v>
       </c>
       <c r="H21" s="3">
-        <v>465000</v>
+        <v>508000</v>
       </c>
       <c r="I21" s="3">
-        <v>527400</v>
+        <v>452300</v>
       </c>
       <c r="J21" s="3">
+        <v>513100</v>
+      </c>
+      <c r="K21" s="3">
         <v>491000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>465200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>438000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>662400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>440200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>440600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>373400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>490000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>356300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>714700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>333700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>427400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>388300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>791500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>327300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>344400</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>78700</v>
+        <v>75400</v>
       </c>
       <c r="E22" s="3">
-        <v>82600</v>
+        <v>76600</v>
       </c>
       <c r="F22" s="3">
-        <v>49500</v>
+        <v>80400</v>
       </c>
       <c r="G22" s="3">
-        <v>70000</v>
+        <v>48200</v>
       </c>
       <c r="H22" s="3">
-        <v>33900</v>
+        <v>68000</v>
       </c>
       <c r="I22" s="3">
-        <v>69400</v>
+        <v>33000</v>
       </c>
       <c r="J22" s="3">
+        <v>67500</v>
+      </c>
+      <c r="K22" s="3">
         <v>77100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>67900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>58300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>56700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>47900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>43500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>37600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>38200</v>
       </c>
-      <c r="R22" s="3" t="s">
+      <c r="S22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>45400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>35700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>44100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>45500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>40300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>42800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>108600</v>
+        <v>166100</v>
       </c>
       <c r="E23" s="3">
-        <v>222100</v>
+        <v>105700</v>
       </c>
       <c r="F23" s="3">
-        <v>150100</v>
+        <v>216100</v>
       </c>
       <c r="G23" s="3">
-        <v>113300</v>
+        <v>146000</v>
       </c>
       <c r="H23" s="3">
-        <v>102800</v>
+        <v>110200</v>
       </c>
       <c r="I23" s="3">
-        <v>114700</v>
+        <v>100000</v>
       </c>
       <c r="J23" s="3">
+        <v>111600</v>
+      </c>
+      <c r="K23" s="3">
         <v>66500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>58800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>91900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>315800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>109600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>121400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>68700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>182000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>85500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>125800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>46500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>187500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>73300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>521300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>34800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>12700</v>
+        <v>25700</v>
       </c>
       <c r="E24" s="3">
-        <v>22100</v>
+        <v>12300</v>
       </c>
       <c r="F24" s="3">
+        <v>21500</v>
+      </c>
+      <c r="G24" s="3">
+        <v>17400</v>
+      </c>
+      <c r="H24" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="I24" s="3">
+        <v>25800</v>
+      </c>
+      <c r="J24" s="3">
+        <v>14900</v>
+      </c>
+      <c r="K24" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="L24" s="3">
+        <v>2800</v>
+      </c>
+      <c r="M24" s="3">
+        <v>8500</v>
+      </c>
+      <c r="N24" s="3">
+        <v>110900</v>
+      </c>
+      <c r="O24" s="3">
+        <v>-90300</v>
+      </c>
+      <c r="P24" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>16900</v>
+      </c>
+      <c r="R24" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="S24" s="3">
+        <v>9600</v>
+      </c>
+      <c r="T24" s="3">
+        <v>39000</v>
+      </c>
+      <c r="U24" s="3">
+        <v>17600</v>
+      </c>
+      <c r="V24" s="3">
         <v>17800</v>
       </c>
-      <c r="G24" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="H24" s="3">
-        <v>26500</v>
-      </c>
-      <c r="I24" s="3">
-        <v>15300</v>
-      </c>
-      <c r="J24" s="3">
-        <v>-16200</v>
-      </c>
-      <c r="K24" s="3">
-        <v>2800</v>
-      </c>
-      <c r="L24" s="3">
-        <v>8500</v>
-      </c>
-      <c r="M24" s="3">
-        <v>110900</v>
-      </c>
-      <c r="N24" s="3">
-        <v>-90300</v>
-      </c>
-      <c r="O24" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="P24" s="3">
-        <v>16900</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>-16300</v>
-      </c>
-      <c r="R24" s="3">
-        <v>9600</v>
-      </c>
-      <c r="S24" s="3">
-        <v>39000</v>
-      </c>
-      <c r="T24" s="3">
-        <v>17600</v>
-      </c>
-      <c r="U24" s="3">
-        <v>17800</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-32100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>163300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>12400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>96000</v>
+        <v>140400</v>
       </c>
       <c r="E26" s="3">
-        <v>200000</v>
+        <v>93400</v>
       </c>
       <c r="F26" s="3">
-        <v>132300</v>
+        <v>194600</v>
       </c>
       <c r="G26" s="3">
-        <v>115700</v>
+        <v>128700</v>
       </c>
       <c r="H26" s="3">
-        <v>76200</v>
+        <v>112600</v>
       </c>
       <c r="I26" s="3">
-        <v>99400</v>
+        <v>74100</v>
       </c>
       <c r="J26" s="3">
+        <v>96700</v>
+      </c>
+      <c r="K26" s="3">
         <v>82700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>56000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>83400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>204900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>199900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>130200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>51800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>198300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>76000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>86800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>28900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>169600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>105400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>358100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>22500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>96000</v>
+        <v>140400</v>
       </c>
       <c r="E27" s="3">
-        <v>200000</v>
+        <v>93400</v>
       </c>
       <c r="F27" s="3">
-        <v>132300</v>
+        <v>194600</v>
       </c>
       <c r="G27" s="3">
-        <v>115700</v>
+        <v>128700</v>
       </c>
       <c r="H27" s="3">
-        <v>76200</v>
+        <v>112600</v>
       </c>
       <c r="I27" s="3">
-        <v>99400</v>
+        <v>74100</v>
       </c>
       <c r="J27" s="3">
+        <v>96700</v>
+      </c>
+      <c r="K27" s="3">
         <v>82700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>56000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>83400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>204900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>199900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>130200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>51800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>198300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>76000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>86800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>28900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>169600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>105400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>358100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>22500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,150 +2398,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>18200</v>
+        <v>5500</v>
       </c>
       <c r="E32" s="3">
-        <v>5600</v>
+        <v>17700</v>
       </c>
       <c r="F32" s="3">
-        <v>25500</v>
+        <v>5500</v>
       </c>
       <c r="G32" s="3">
-        <v>8700</v>
+        <v>24800</v>
       </c>
       <c r="H32" s="3">
-        <v>7400</v>
+        <v>8500</v>
       </c>
       <c r="I32" s="3">
-        <v>-4700</v>
+        <v>7200</v>
       </c>
       <c r="J32" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>20100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-20300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-36500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-29500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>47500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>56900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>9700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-179600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>6300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>96000</v>
+        <v>140400</v>
       </c>
       <c r="E33" s="3">
-        <v>200000</v>
+        <v>93400</v>
       </c>
       <c r="F33" s="3">
-        <v>132300</v>
+        <v>194600</v>
       </c>
       <c r="G33" s="3">
-        <v>115700</v>
+        <v>128700</v>
       </c>
       <c r="H33" s="3">
-        <v>76200</v>
+        <v>112600</v>
       </c>
       <c r="I33" s="3">
-        <v>99400</v>
+        <v>74100</v>
       </c>
       <c r="J33" s="3">
+        <v>96700</v>
+      </c>
+      <c r="K33" s="3">
         <v>82700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>56000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>83400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>204900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>199900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>130200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>51800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>198300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>76000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>86800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>28900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>169600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>105400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>358100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>22500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>96000</v>
+        <v>140400</v>
       </c>
       <c r="E35" s="3">
-        <v>200000</v>
+        <v>93400</v>
       </c>
       <c r="F35" s="3">
-        <v>132300</v>
+        <v>194600</v>
       </c>
       <c r="G35" s="3">
-        <v>115700</v>
+        <v>128700</v>
       </c>
       <c r="H35" s="3">
-        <v>76200</v>
+        <v>112600</v>
       </c>
       <c r="I35" s="3">
-        <v>99400</v>
+        <v>74100</v>
       </c>
       <c r="J35" s="3">
+        <v>96700</v>
+      </c>
+      <c r="K35" s="3">
         <v>82700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>56000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>83400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>204900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>199900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>130200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>51800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>198300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>76000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>86800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>28900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>169600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>105400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>358100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>22500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,647 +2831,675 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>366700</v>
+        <v>379400</v>
       </c>
       <c r="E41" s="3">
-        <v>568700</v>
+        <v>356700</v>
       </c>
       <c r="F41" s="3">
-        <v>666800</v>
+        <v>553200</v>
       </c>
       <c r="G41" s="3">
-        <v>566700</v>
+        <v>648600</v>
       </c>
       <c r="H41" s="3">
-        <v>656800</v>
+        <v>551200</v>
       </c>
       <c r="I41" s="3">
-        <v>470900</v>
+        <v>639000</v>
       </c>
       <c r="J41" s="3">
+        <v>458100</v>
+      </c>
+      <c r="K41" s="3">
         <v>424100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>240200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>823100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1055300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>819200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>726000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>508200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>504000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>413900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>605800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>284000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>422000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>164300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>118100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>171200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>201300</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>256100</v>
+        <v>215800</v>
       </c>
       <c r="E42" s="3">
-        <v>361900</v>
+        <v>249100</v>
       </c>
       <c r="F42" s="3">
-        <v>154700</v>
+        <v>352000</v>
       </c>
       <c r="G42" s="3">
-        <v>50200</v>
+        <v>150500</v>
       </c>
       <c r="H42" s="3">
-        <v>60100</v>
+        <v>48800</v>
       </c>
       <c r="I42" s="3">
-        <v>404700</v>
+        <v>58500</v>
       </c>
       <c r="J42" s="3">
+        <v>393700</v>
+      </c>
+      <c r="K42" s="3">
         <v>260000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>218000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>837500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>922000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>665600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>653600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>299700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>405200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>294700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>50300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>7000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>120900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>146700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>87400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>140900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>146900</v>
       </c>
     </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>976000</v>
+        <v>984000</v>
       </c>
       <c r="E43" s="3">
-        <v>951100</v>
+        <v>949400</v>
       </c>
       <c r="F43" s="3">
-        <v>920600</v>
+        <v>925200</v>
       </c>
       <c r="G43" s="3">
-        <v>828300</v>
+        <v>895500</v>
       </c>
       <c r="H43" s="3">
-        <v>845200</v>
+        <v>805800</v>
       </c>
       <c r="I43" s="3">
-        <v>852500</v>
+        <v>822200</v>
       </c>
       <c r="J43" s="3">
+        <v>829300</v>
+      </c>
+      <c r="K43" s="3">
         <v>816200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>958900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>898400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>955400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>875900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>867400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>843400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>948600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>956400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>849600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>835500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>923500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>785800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>661200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>670700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>648700</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>74800</v>
+        <v>74700</v>
       </c>
       <c r="E44" s="3">
-        <v>61300</v>
+        <v>72700</v>
       </c>
       <c r="F44" s="3">
-        <v>76700</v>
+        <v>59600</v>
       </c>
       <c r="G44" s="3">
-        <v>69200</v>
+        <v>74700</v>
       </c>
       <c r="H44" s="3">
-        <v>55600</v>
+        <v>67300</v>
       </c>
       <c r="I44" s="3">
-        <v>43600</v>
+        <v>54100</v>
       </c>
       <c r="J44" s="3">
+        <v>42400</v>
+      </c>
+      <c r="K44" s="3">
         <v>51400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>56100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>45700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>40900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>46600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>43700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>56300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>48300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>40300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>40100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>47900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>37500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>39600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>37800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>40200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>34300</v>
       </c>
     </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>235800</v>
+        <v>214700</v>
       </c>
       <c r="E45" s="3">
-        <v>164100</v>
+        <v>229400</v>
       </c>
       <c r="F45" s="3">
-        <v>183400</v>
+        <v>159600</v>
       </c>
       <c r="G45" s="3">
-        <v>200400</v>
+        <v>178400</v>
       </c>
       <c r="H45" s="3">
-        <v>211900</v>
+        <v>194900</v>
       </c>
       <c r="I45" s="3">
-        <v>143200</v>
+        <v>206100</v>
       </c>
       <c r="J45" s="3">
+        <v>139300</v>
+      </c>
+      <c r="K45" s="3">
         <v>174200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>279700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>192100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>134300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>132600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>170200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>172100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>131600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>164900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>101300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>108500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>57500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>121800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>152000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>206800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>91300</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1909400</v>
+        <v>1868700</v>
       </c>
       <c r="E46" s="3">
-        <v>2107100</v>
+        <v>1857400</v>
       </c>
       <c r="F46" s="3">
-        <v>2002200</v>
+        <v>2049700</v>
       </c>
       <c r="G46" s="3">
-        <v>1714700</v>
+        <v>1947700</v>
       </c>
       <c r="H46" s="3">
-        <v>1829700</v>
+        <v>1668000</v>
       </c>
       <c r="I46" s="3">
-        <v>1914900</v>
+        <v>1779900</v>
       </c>
       <c r="J46" s="3">
+        <v>1862800</v>
+      </c>
+      <c r="K46" s="3">
         <v>1725900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1752900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2796900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3107900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2539900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2460900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1879800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2037500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1870100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1647200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1283000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1561500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1258200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1056500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1229800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1122400</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>507000</v>
+        <v>490200</v>
       </c>
       <c r="E47" s="3">
-        <v>509200</v>
+        <v>493200</v>
       </c>
       <c r="F47" s="3">
-        <v>530700</v>
+        <v>495400</v>
       </c>
       <c r="G47" s="3">
-        <v>662900</v>
+        <v>516300</v>
       </c>
       <c r="H47" s="3">
-        <v>596000</v>
+        <v>644800</v>
       </c>
       <c r="I47" s="3">
-        <v>592200</v>
+        <v>579800</v>
       </c>
       <c r="J47" s="3">
+        <v>576000</v>
+      </c>
+      <c r="K47" s="3">
         <v>637900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>683700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>698500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>693400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>411600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>334300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>367500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>444200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>410400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>665000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>603700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>609100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>786100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>766800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>294700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4192100</v>
+        <v>4056800</v>
       </c>
       <c r="E48" s="3">
-        <v>4140800</v>
+        <v>4078000</v>
       </c>
       <c r="F48" s="3">
-        <v>4180400</v>
+        <v>4028100</v>
       </c>
       <c r="G48" s="3">
-        <v>4265200</v>
+        <v>4066600</v>
       </c>
       <c r="H48" s="3">
-        <v>4309900</v>
+        <v>4149000</v>
       </c>
       <c r="I48" s="3">
-        <v>4186900</v>
+        <v>4192600</v>
       </c>
       <c r="J48" s="3">
+        <v>4072900</v>
+      </c>
+      <c r="K48" s="3">
         <v>4268300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4739300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3963300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3695400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3515000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3373600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3450400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3542300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3380900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3415200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3190900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3253000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3129600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2907800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2970000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2096500</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2855000</v>
+        <v>2730900</v>
       </c>
       <c r="E49" s="3">
-        <v>2886900</v>
+        <v>2777200</v>
       </c>
       <c r="F49" s="3">
-        <v>2914200</v>
+        <v>2808300</v>
       </c>
       <c r="G49" s="3">
-        <v>2965400</v>
+        <v>2834900</v>
       </c>
       <c r="H49" s="3">
-        <v>3018300</v>
+        <v>2884700</v>
       </c>
       <c r="I49" s="3">
-        <v>3033100</v>
+        <v>2936100</v>
       </c>
       <c r="J49" s="3">
+        <v>2950500</v>
+      </c>
+      <c r="K49" s="3">
         <v>2946800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3155600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2179800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2136500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1459200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1444800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1650300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1766600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1755400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1826000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1703000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1785700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1846400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1791600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1947200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1998900</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,79 +3643,85 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>575400</v>
+        <v>565000</v>
       </c>
       <c r="E52" s="3">
-        <v>565900</v>
+        <v>559700</v>
       </c>
       <c r="F52" s="3">
-        <v>714000</v>
+        <v>550500</v>
       </c>
       <c r="G52" s="3">
-        <v>684100</v>
+        <v>694600</v>
       </c>
       <c r="H52" s="3">
-        <v>702100</v>
+        <v>665500</v>
       </c>
       <c r="I52" s="3">
-        <v>694900</v>
+        <v>683000</v>
       </c>
       <c r="J52" s="3">
+        <v>676000</v>
+      </c>
+      <c r="K52" s="3">
         <v>525300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>552700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>442800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>422300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>931700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>878600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>344500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>361100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>333500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>295600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>270900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>243100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>278500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>276200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>448900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>461900</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3791,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>10038800</v>
+        <v>9711600</v>
       </c>
       <c r="E54" s="3">
-        <v>10209900</v>
+        <v>9765500</v>
       </c>
       <c r="F54" s="3">
-        <v>10341600</v>
+        <v>9931900</v>
       </c>
       <c r="G54" s="3">
-        <v>10292400</v>
+        <v>10060000</v>
       </c>
       <c r="H54" s="3">
-        <v>10456100</v>
+        <v>10012100</v>
       </c>
       <c r="I54" s="3">
-        <v>10422000</v>
+        <v>10171400</v>
       </c>
       <c r="J54" s="3">
+        <v>10138300</v>
+      </c>
+      <c r="K54" s="3">
         <v>10104100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10884200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10081300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10055500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8857300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8492200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7692600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8151800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7750300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7849100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7051500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7452400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7298800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6798900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6890500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5980300</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,434 +3923,453 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>722800</v>
+        <v>655800</v>
       </c>
       <c r="E57" s="3">
-        <v>852100</v>
+        <v>703100</v>
       </c>
       <c r="F57" s="3">
-        <v>712000</v>
+        <v>828900</v>
       </c>
       <c r="G57" s="3">
-        <v>674500</v>
+        <v>692600</v>
       </c>
       <c r="H57" s="3">
-        <v>713800</v>
+        <v>656200</v>
       </c>
       <c r="I57" s="3">
-        <v>782900</v>
+        <v>694300</v>
       </c>
       <c r="J57" s="3">
+        <v>761600</v>
+      </c>
+      <c r="K57" s="3">
         <v>766200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>818400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>618900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>659500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>534400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>501500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>497900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>612300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>423900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>407700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>470400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>724600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>548300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>512000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>707700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>809000</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>481800</v>
+        <v>401500</v>
       </c>
       <c r="E58" s="3">
-        <v>568300</v>
+        <v>468700</v>
       </c>
       <c r="F58" s="3">
-        <v>774200</v>
+        <v>552800</v>
       </c>
       <c r="G58" s="3">
-        <v>790200</v>
+        <v>753100</v>
       </c>
       <c r="H58" s="3">
-        <v>718000</v>
+        <v>768700</v>
       </c>
       <c r="I58" s="3">
-        <v>650800</v>
+        <v>698500</v>
       </c>
       <c r="J58" s="3">
+        <v>633000</v>
+      </c>
+      <c r="K58" s="3">
         <v>369800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>390000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>277400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>365000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>359000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>509600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>630200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>537000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>543200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>513900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>363300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>416900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>432400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>233000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>249900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1155400</v>
+        <v>1055900</v>
       </c>
       <c r="E59" s="3">
-        <v>959800</v>
+        <v>1124000</v>
       </c>
       <c r="F59" s="3">
-        <v>1048500</v>
+        <v>933700</v>
       </c>
       <c r="G59" s="3">
-        <v>985400</v>
+        <v>1020000</v>
       </c>
       <c r="H59" s="3">
-        <v>1038200</v>
+        <v>958600</v>
       </c>
       <c r="I59" s="3">
-        <v>990100</v>
+        <v>1009900</v>
       </c>
       <c r="J59" s="3">
+        <v>963100</v>
+      </c>
+      <c r="K59" s="3">
         <v>771900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>730500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>900400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1117300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>482200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>462100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>350500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>475400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>332200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>307800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>229800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>357800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>383300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>256100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>261700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>345900</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2359900</v>
+        <v>2113200</v>
       </c>
       <c r="E60" s="3">
-        <v>2380300</v>
+        <v>2295700</v>
       </c>
       <c r="F60" s="3">
-        <v>2534700</v>
+        <v>2315500</v>
       </c>
       <c r="G60" s="3">
-        <v>2450100</v>
+        <v>2465700</v>
       </c>
       <c r="H60" s="3">
-        <v>2470000</v>
+        <v>2383400</v>
       </c>
       <c r="I60" s="3">
-        <v>2423700</v>
+        <v>2402700</v>
       </c>
       <c r="J60" s="3">
+        <v>2357700</v>
+      </c>
+      <c r="K60" s="3">
         <v>1907900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1938900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1796700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2141800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1375500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1473300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1478600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1624700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1299200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1229400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1063500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1499300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1364000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1001100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1219300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1324000</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2408100</v>
+        <v>2397900</v>
       </c>
       <c r="E61" s="3">
-        <v>2393000</v>
+        <v>2342600</v>
       </c>
       <c r="F61" s="3">
-        <v>2448600</v>
+        <v>2327800</v>
       </c>
       <c r="G61" s="3">
-        <v>2515400</v>
+        <v>2381900</v>
       </c>
       <c r="H61" s="3">
-        <v>2634900</v>
+        <v>2446900</v>
       </c>
       <c r="I61" s="3">
-        <v>2638300</v>
+        <v>2563100</v>
       </c>
       <c r="J61" s="3">
+        <v>2566500</v>
+      </c>
+      <c r="K61" s="3">
         <v>2847800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3116100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2431100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2240600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2043100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1939900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1417100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1561600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1494800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1638000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1534300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1395000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1393500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1461300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1503800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>505100</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>647100</v>
+        <v>621800</v>
       </c>
       <c r="E62" s="3">
-        <v>629900</v>
+        <v>629400</v>
       </c>
       <c r="F62" s="3">
-        <v>633200</v>
+        <v>612800</v>
       </c>
       <c r="G62" s="3">
-        <v>647400</v>
+        <v>616000</v>
       </c>
       <c r="H62" s="3">
-        <v>692400</v>
+        <v>629800</v>
       </c>
       <c r="I62" s="3">
-        <v>667600</v>
+        <v>673500</v>
       </c>
       <c r="J62" s="3">
+        <v>649500</v>
+      </c>
+      <c r="K62" s="3">
         <v>674800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>752300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>643300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>605500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>475800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>475600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>407100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>428600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>427700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>479400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>421400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>415000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>459000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>451600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>440000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>446900</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4587,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5415100</v>
+        <v>5132900</v>
       </c>
       <c r="E66" s="3">
-        <v>5403200</v>
+        <v>5267700</v>
       </c>
       <c r="F66" s="3">
-        <v>5616500</v>
+        <v>5256100</v>
       </c>
       <c r="G66" s="3">
-        <v>5612900</v>
+        <v>5463600</v>
       </c>
       <c r="H66" s="3">
-        <v>5797300</v>
+        <v>5460100</v>
       </c>
       <c r="I66" s="3">
-        <v>5729600</v>
+        <v>5639400</v>
       </c>
       <c r="J66" s="3">
+        <v>5573600</v>
+      </c>
+      <c r="K66" s="3">
         <v>5430500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5807300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4871000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4987900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3894400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3888700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3302800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3614900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3221800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3346700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3019200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3309300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3216600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2914000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3163100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2276100</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,79 +4985,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2070500</v>
+        <v>2102000</v>
       </c>
       <c r="E72" s="3">
-        <v>2252400</v>
+        <v>2014100</v>
       </c>
       <c r="F72" s="3">
-        <v>2170800</v>
+        <v>2191000</v>
       </c>
       <c r="G72" s="3">
-        <v>2124700</v>
+        <v>2111700</v>
       </c>
       <c r="H72" s="3">
-        <v>2104100</v>
+        <v>2066800</v>
       </c>
       <c r="I72" s="3">
-        <v>2137700</v>
+        <v>2046800</v>
       </c>
       <c r="J72" s="3">
+        <v>2079500</v>
+      </c>
+      <c r="K72" s="3">
         <v>2119200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2311700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2368000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2277700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2179300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1930100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1803500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1831900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1835100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2161300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2204900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2251400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2160900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2071600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1811200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1788100</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5281,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4623700</v>
+        <v>4578700</v>
       </c>
       <c r="E76" s="3">
-        <v>4806700</v>
+        <v>4497800</v>
       </c>
       <c r="F76" s="3">
-        <v>4725100</v>
+        <v>4675800</v>
       </c>
       <c r="G76" s="3">
-        <v>4679400</v>
+        <v>4596400</v>
       </c>
       <c r="H76" s="3">
-        <v>4658800</v>
+        <v>4552000</v>
       </c>
       <c r="I76" s="3">
-        <v>4692400</v>
+        <v>4532000</v>
       </c>
       <c r="J76" s="3">
+        <v>4564700</v>
+      </c>
+      <c r="K76" s="3">
         <v>4673600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5076900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5210200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5067600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4962900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4603400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4389800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4536900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4528500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4502400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4032300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4143200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4082200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3884900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3727500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3704200</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>96000</v>
+        <v>140400</v>
       </c>
       <c r="E81" s="3">
-        <v>200000</v>
+        <v>93400</v>
       </c>
       <c r="F81" s="3">
-        <v>132300</v>
+        <v>194600</v>
       </c>
       <c r="G81" s="3">
-        <v>115700</v>
+        <v>128700</v>
       </c>
       <c r="H81" s="3">
-        <v>76200</v>
+        <v>112600</v>
       </c>
       <c r="I81" s="3">
-        <v>99400</v>
+        <v>74100</v>
       </c>
       <c r="J81" s="3">
+        <v>96700</v>
+      </c>
+      <c r="K81" s="3">
         <v>82700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>56000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>83400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>204900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>199900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>130200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>51800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>198300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>76000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>86800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>28900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>169600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>105400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>358100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>22500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,79 +5612,83 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>324200</v>
+        <v>315500</v>
       </c>
       <c r="E83" s="3">
-        <v>323300</v>
+        <v>315400</v>
       </c>
       <c r="F83" s="3">
-        <v>324300</v>
+        <v>314500</v>
       </c>
       <c r="G83" s="3">
-        <v>339000</v>
+        <v>315500</v>
       </c>
       <c r="H83" s="3">
-        <v>328300</v>
+        <v>329700</v>
       </c>
       <c r="I83" s="3">
-        <v>343300</v>
+        <v>319400</v>
       </c>
       <c r="J83" s="3">
+        <v>334000</v>
+      </c>
+      <c r="K83" s="3">
         <v>347400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>338600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>287700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>289800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>282800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>275700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>267100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>269800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>270800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>543500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>251500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>195800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>269500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>229800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>249700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>190500</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6054,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>304100</v>
+        <v>482800</v>
       </c>
       <c r="E89" s="3">
-        <v>895900</v>
+        <v>295800</v>
       </c>
       <c r="F89" s="3">
-        <v>643700</v>
+        <v>871500</v>
       </c>
       <c r="G89" s="3">
-        <v>390200</v>
+        <v>626200</v>
       </c>
       <c r="H89" s="3">
-        <v>365000</v>
+        <v>379600</v>
       </c>
       <c r="I89" s="3">
-        <v>647000</v>
+        <v>355000</v>
       </c>
       <c r="J89" s="3">
+        <v>629400</v>
+      </c>
+      <c r="K89" s="3">
         <v>641600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>267500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>230200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>630400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>558400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>432300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>364700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>723800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>426300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>549100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>87000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>666100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>394600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>187500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>55400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>546400</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,79 +6158,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1002100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1354500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1291900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-998200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-925700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1288500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1375200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-977600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1049600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1328000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2157400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-896500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-175400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-247700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-286500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-165600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-310800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-161400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-246500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-173300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-167300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-121700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-256800</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,79 +6378,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-135200</v>
+        <v>-139500</v>
       </c>
       <c r="E94" s="3">
-        <v>-533100</v>
+        <v>-131600</v>
       </c>
       <c r="F94" s="3">
-        <v>-285300</v>
+        <v>-518600</v>
       </c>
       <c r="G94" s="3">
-        <v>-154600</v>
+        <v>-277600</v>
       </c>
       <c r="H94" s="3">
-        <v>107700</v>
+        <v>-150400</v>
       </c>
       <c r="I94" s="3">
-        <v>-407400</v>
+        <v>104800</v>
       </c>
       <c r="J94" s="3">
+        <v>-396300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-268300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-828100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-170900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-470600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-166300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-518500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-159800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-395400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-408500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-231700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-50600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-222900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-226400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-121600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-114600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-291500</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,79 +6482,83 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-119200</v>
+        <v>-112600</v>
       </c>
       <c r="E96" s="3">
-        <v>-77300</v>
+        <v>-115900</v>
       </c>
       <c r="F96" s="3">
-        <v>-52800</v>
+        <v>-75200</v>
       </c>
       <c r="G96" s="3">
-        <v>-150700</v>
+        <v>-51300</v>
       </c>
       <c r="H96" s="3">
-        <v>-121000</v>
+        <v>-146600</v>
       </c>
       <c r="I96" s="3">
-        <v>-49100</v>
+        <v>-117700</v>
       </c>
       <c r="J96" s="3">
+        <v>-47800</v>
+      </c>
+      <c r="K96" s="3">
         <v>-49200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-38500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-97700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-42700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-59800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-9300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-91000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-108700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-5700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-112000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-101300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-67300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-11800</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-64200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,79 +6776,85 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-370800</v>
+        <v>-320600</v>
       </c>
       <c r="E100" s="3">
-        <v>-460900</v>
+        <v>-360700</v>
       </c>
       <c r="F100" s="3">
-        <v>-258300</v>
+        <v>-448300</v>
       </c>
       <c r="G100" s="3">
-        <v>-325800</v>
+        <v>-251300</v>
       </c>
       <c r="H100" s="3">
-        <v>-286700</v>
+        <v>-316900</v>
       </c>
       <c r="I100" s="3">
-        <v>-192800</v>
+        <v>-278900</v>
       </c>
       <c r="J100" s="3">
+        <v>-187600</v>
+      </c>
+      <c r="K100" s="3">
         <v>-200400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>30700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-311300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>74500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-328000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>286200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-178500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-240200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-202700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-161800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-160300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-183000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-129100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-109800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>29200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-175900</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6675,75 +6924,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-202000</v>
+        <v>22700</v>
       </c>
       <c r="E102" s="3">
-        <v>-98100</v>
+        <v>-196500</v>
       </c>
       <c r="F102" s="3">
-        <v>100100</v>
+        <v>-95400</v>
       </c>
       <c r="G102" s="3">
-        <v>-90200</v>
+        <v>97400</v>
       </c>
       <c r="H102" s="3">
-        <v>185900</v>
+        <v>-87700</v>
       </c>
       <c r="I102" s="3">
-        <v>46800</v>
+        <v>180900</v>
       </c>
       <c r="J102" s="3">
+        <v>45500</v>
+      </c>
+      <c r="K102" s="3">
         <v>202700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-562000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-252000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>234300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>64100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>199900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>26400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>88200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-184800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>155600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-123900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>260200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>39200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-43900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-30000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>79000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TIMB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TIMB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>TIMB</t>
   </si>
@@ -656,340 +656,353 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1132700</v>
+        <v>1178800</v>
       </c>
       <c r="E8" s="3">
-        <v>1095500</v>
+        <v>1135300</v>
       </c>
       <c r="F8" s="3">
-        <v>1127800</v>
+        <v>1215300</v>
       </c>
       <c r="G8" s="3">
-        <v>1088300</v>
+        <v>1293200</v>
       </c>
       <c r="H8" s="3">
-        <v>1053800</v>
+        <v>1212500</v>
       </c>
       <c r="I8" s="3">
-        <v>1013700</v>
+        <v>1216000</v>
       </c>
       <c r="J8" s="3">
+        <v>1113900</v>
+      </c>
+      <c r="K8" s="3">
         <v>1046800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1036700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1075900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>972100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>968700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>908700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>853300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>811900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>915500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>854600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1616400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>752500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>847100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>813600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>754800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>784200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>834100</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>655400</v>
+        <v>543500</v>
       </c>
       <c r="E9" s="3">
-        <v>661600</v>
+        <v>525100</v>
       </c>
       <c r="F9" s="3">
-        <v>658700</v>
+        <v>588800</v>
       </c>
       <c r="G9" s="3">
-        <v>641600</v>
+        <v>600400</v>
       </c>
       <c r="H9" s="3">
-        <v>658500</v>
+        <v>568400</v>
       </c>
       <c r="I9" s="3">
-        <v>653200</v>
+        <v>608200</v>
       </c>
       <c r="J9" s="3">
+        <v>555300</v>
+      </c>
+      <c r="K9" s="3">
         <v>658400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>668500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>697000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>611500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>563900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>546100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>522400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>499800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>414300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>399500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1122400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>350200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>307400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>366300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>329200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>366300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>367900</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>477400</v>
+        <v>635300</v>
       </c>
       <c r="E10" s="3">
-        <v>434000</v>
+        <v>610200</v>
       </c>
       <c r="F10" s="3">
-        <v>469100</v>
+        <v>626600</v>
       </c>
       <c r="G10" s="3">
-        <v>446700</v>
+        <v>692800</v>
       </c>
       <c r="H10" s="3">
-        <v>395300</v>
+        <v>644100</v>
       </c>
       <c r="I10" s="3">
-        <v>360500</v>
+        <v>607800</v>
       </c>
       <c r="J10" s="3">
+        <v>558600</v>
+      </c>
+      <c r="K10" s="3">
         <v>388500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>368200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>378900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>360600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>404800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>362500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>331000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>312100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>501200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>455100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>494000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>402400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>539800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>447200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>425600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>417900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>466200</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1016,8 +1029,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1090,8 +1104,11 @@
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,156 +1181,165 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>2300</v>
-      </c>
-      <c r="E14" s="3">
-        <v>10900</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
+        <v>35100</v>
+      </c>
+      <c r="G14" s="3">
+        <v>14100</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
+        <v>41200</v>
+      </c>
+      <c r="K14" s="3">
+        <v>6900</v>
+      </c>
+      <c r="L14" s="3">
+        <v>6700</v>
+      </c>
+      <c r="M14" s="3">
+        <v>4600</v>
+      </c>
+      <c r="N14" s="3">
+        <v>10000</v>
+      </c>
+      <c r="O14" s="3">
         <v>7000</v>
       </c>
-      <c r="G14" s="3">
-        <v>10400</v>
-      </c>
-      <c r="H14" s="3">
-        <v>8600</v>
-      </c>
-      <c r="I14" s="3">
-        <v>13300</v>
-      </c>
-      <c r="J14" s="3">
-        <v>6900</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="P14" s="3">
         <v>6700</v>
       </c>
-      <c r="L14" s="3">
-        <v>4600</v>
-      </c>
-      <c r="M14" s="3">
-        <v>10000</v>
-      </c>
-      <c r="N14" s="3">
-        <v>7000</v>
-      </c>
-      <c r="O14" s="3">
-        <v>6700</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>13900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>9400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>11700</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>38400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>11800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>10700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>17400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>40300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>16500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>35700</v>
+        <v>208700</v>
       </c>
       <c r="E15" s="3">
-        <v>35200</v>
+        <v>178700</v>
       </c>
       <c r="F15" s="3">
-        <v>34400</v>
+        <v>225000</v>
       </c>
       <c r="G15" s="3">
-        <v>34300</v>
+        <v>182400</v>
       </c>
       <c r="H15" s="3">
-        <v>33700</v>
+        <v>213200</v>
       </c>
       <c r="I15" s="3">
-        <v>32100</v>
+        <v>205800</v>
       </c>
       <c r="J15" s="3">
+        <v>177600</v>
+      </c>
+      <c r="K15" s="3">
         <v>32800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>34700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>37500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>40200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>41000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>42200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>40700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>41400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>43800</v>
       </c>
-      <c r="S15" s="3" t="s">
+      <c r="T15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>48900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>44300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>43900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>48900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>44800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>45900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1363,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>885800</v>
+        <v>913300</v>
       </c>
       <c r="E17" s="3">
-        <v>895500</v>
+        <v>883600</v>
       </c>
       <c r="F17" s="3">
-        <v>825900</v>
+        <v>972300</v>
       </c>
       <c r="G17" s="3">
-        <v>869300</v>
+        <v>994000</v>
       </c>
       <c r="H17" s="3">
-        <v>867100</v>
+        <v>963500</v>
       </c>
       <c r="I17" s="3">
-        <v>873600</v>
+        <v>995800</v>
       </c>
       <c r="J17" s="3">
+        <v>938400</v>
+      </c>
+      <c r="K17" s="3">
         <v>872300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>896000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>929100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>829200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>616500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>756600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>724900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>701100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>724800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>721600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1388200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>660600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>616100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>690200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>372700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>700300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>683600</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>247000</v>
+        <v>265500</v>
       </c>
       <c r="E18" s="3">
-        <v>200000</v>
+        <v>251700</v>
       </c>
       <c r="F18" s="3">
-        <v>302000</v>
+        <v>243100</v>
       </c>
       <c r="G18" s="3">
-        <v>219100</v>
+        <v>299200</v>
       </c>
       <c r="H18" s="3">
-        <v>186700</v>
+        <v>249000</v>
       </c>
       <c r="I18" s="3">
-        <v>140100</v>
+        <v>220200</v>
       </c>
       <c r="J18" s="3">
+        <v>175500</v>
+      </c>
+      <c r="K18" s="3">
         <v>174500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>140800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>146800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>142900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>352200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>152100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>128400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>110900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>190700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>133000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>228100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>92000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>231000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>123400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>382100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>84000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>150500</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,378 +1546,394 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-5500</v>
+        <v>3700</v>
       </c>
       <c r="E20" s="3">
-        <v>-17700</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>-5500</v>
+        <v>8400</v>
       </c>
       <c r="G20" s="3">
-        <v>-24800</v>
+        <v>-38300</v>
       </c>
       <c r="H20" s="3">
-        <v>-8500</v>
+        <v>3700</v>
       </c>
       <c r="I20" s="3">
-        <v>-7200</v>
+        <v>4900</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>4600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-20100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>20300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>36500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>29500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-47500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-56900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-9700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-4600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>179600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-6300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>557000</v>
+        <v>470500</v>
       </c>
       <c r="E21" s="3">
-        <v>497700</v>
+        <v>430400</v>
       </c>
       <c r="F21" s="3">
-        <v>611000</v>
+        <v>459700</v>
       </c>
       <c r="G21" s="3">
-        <v>509700</v>
+        <v>520000</v>
       </c>
       <c r="H21" s="3">
-        <v>508000</v>
+        <v>458500</v>
       </c>
       <c r="I21" s="3">
-        <v>452300</v>
+        <v>421000</v>
       </c>
       <c r="J21" s="3">
+        <v>353100</v>
+      </c>
+      <c r="K21" s="3">
         <v>513100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>491000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>465200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>438000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>662400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>440200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>440600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>373400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>490000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>356300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>714700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>333700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>427400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>388300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>791500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>327300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>344400</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>75400</v>
+        <v>121300</v>
       </c>
       <c r="E22" s="3">
-        <v>76600</v>
+        <v>119100</v>
       </c>
       <c r="F22" s="3">
-        <v>80400</v>
+        <v>122800</v>
       </c>
       <c r="G22" s="3">
-        <v>48200</v>
+        <v>131700</v>
       </c>
       <c r="H22" s="3">
-        <v>68000</v>
+        <v>135000</v>
       </c>
       <c r="I22" s="3">
-        <v>33000</v>
+        <v>153700</v>
       </c>
       <c r="J22" s="3">
+        <v>83200</v>
+      </c>
+      <c r="K22" s="3">
         <v>67500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>77100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>67900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>58300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>56700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>47900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>43500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>37600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>38200</v>
       </c>
-      <c r="S22" s="3" t="s">
+      <c r="T22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>45400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>35700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>44100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>45500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>40300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>42800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>166100</v>
+        <v>178500</v>
       </c>
       <c r="E23" s="3">
-        <v>105700</v>
+        <v>166500</v>
       </c>
       <c r="F23" s="3">
-        <v>216100</v>
+        <v>117200</v>
       </c>
       <c r="G23" s="3">
-        <v>146000</v>
+        <v>247800</v>
       </c>
       <c r="H23" s="3">
-        <v>110200</v>
+        <v>162700</v>
       </c>
       <c r="I23" s="3">
-        <v>100000</v>
+        <v>127100</v>
       </c>
       <c r="J23" s="3">
+        <v>109800</v>
+      </c>
+      <c r="K23" s="3">
         <v>111600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>66500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>58800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>91900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>315800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>109600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>121400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>68700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>182000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>85500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>125800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>46500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>187500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>73300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>521300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>34800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>25700</v>
+        <v>30600</v>
       </c>
       <c r="E24" s="3">
-        <v>12300</v>
+        <v>25800</v>
       </c>
       <c r="F24" s="3">
-        <v>21500</v>
+        <v>13700</v>
       </c>
       <c r="G24" s="3">
-        <v>17400</v>
+        <v>24700</v>
       </c>
       <c r="H24" s="3">
-        <v>-2400</v>
+        <v>19300</v>
       </c>
       <c r="I24" s="3">
-        <v>25800</v>
+        <v>-2800</v>
       </c>
       <c r="J24" s="3">
+        <v>28400</v>
+      </c>
+      <c r="K24" s="3">
         <v>14900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-16200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>110900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-90300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>16900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-16300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>9600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>39000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>17600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>17800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-32100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>163300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>12400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2006,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>140400</v>
+        <v>147800</v>
       </c>
       <c r="E26" s="3">
-        <v>93400</v>
+        <v>140700</v>
       </c>
       <c r="F26" s="3">
-        <v>194600</v>
+        <v>103600</v>
       </c>
       <c r="G26" s="3">
-        <v>128700</v>
+        <v>223100</v>
       </c>
       <c r="H26" s="3">
-        <v>112600</v>
+        <v>143400</v>
       </c>
       <c r="I26" s="3">
-        <v>74100</v>
+        <v>129900</v>
       </c>
       <c r="J26" s="3">
+        <v>81500</v>
+      </c>
+      <c r="K26" s="3">
         <v>96700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>82700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>56000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>83400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>204900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>199900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>130200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>51800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>198300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>76000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>86800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>28900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>169600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>105400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>358100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>22500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>140400</v>
+        <v>147800</v>
       </c>
       <c r="E27" s="3">
-        <v>93400</v>
+        <v>140700</v>
       </c>
       <c r="F27" s="3">
-        <v>194600</v>
+        <v>103600</v>
       </c>
       <c r="G27" s="3">
-        <v>128700</v>
+        <v>223100</v>
       </c>
       <c r="H27" s="3">
-        <v>112600</v>
+        <v>143400</v>
       </c>
       <c r="I27" s="3">
-        <v>74100</v>
+        <v>129900</v>
       </c>
       <c r="J27" s="3">
+        <v>81500</v>
+      </c>
+      <c r="K27" s="3">
         <v>96700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>82700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>56000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>83400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>204900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>199900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>130200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>51800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>198300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>76000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>86800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>28900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>169600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>105400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>358100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>22500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2237,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2314,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2391,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,156 +2468,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>5500</v>
+        <v>-3700</v>
       </c>
       <c r="E32" s="3">
-        <v>17700</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>5500</v>
+        <v>-8400</v>
       </c>
       <c r="G32" s="3">
-        <v>24800</v>
+        <v>38300</v>
       </c>
       <c r="H32" s="3">
-        <v>8500</v>
+        <v>-3700</v>
       </c>
       <c r="I32" s="3">
-        <v>7200</v>
+        <v>-4900</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-4600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>20100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-20300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-36500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-29500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>47500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>56900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>9700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>4600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-179600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>6300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>140400</v>
+        <v>147800</v>
       </c>
       <c r="E33" s="3">
-        <v>93400</v>
+        <v>140700</v>
       </c>
       <c r="F33" s="3">
-        <v>194600</v>
+        <v>103600</v>
       </c>
       <c r="G33" s="3">
-        <v>128700</v>
+        <v>223100</v>
       </c>
       <c r="H33" s="3">
-        <v>112600</v>
+        <v>143400</v>
       </c>
       <c r="I33" s="3">
-        <v>74100</v>
+        <v>129900</v>
       </c>
       <c r="J33" s="3">
+        <v>81500</v>
+      </c>
+      <c r="K33" s="3">
         <v>96700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>82700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>56000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>83400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>204900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>199900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>130200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>51800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>198300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>76000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>86800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>28900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>169600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>105400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>358100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>22500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2699,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>140400</v>
+        <v>147800</v>
       </c>
       <c r="E35" s="3">
-        <v>93400</v>
+        <v>140700</v>
       </c>
       <c r="F35" s="3">
-        <v>194600</v>
+        <v>103600</v>
       </c>
       <c r="G35" s="3">
-        <v>128700</v>
+        <v>223100</v>
       </c>
       <c r="H35" s="3">
-        <v>112600</v>
+        <v>143400</v>
       </c>
       <c r="I35" s="3">
-        <v>74100</v>
+        <v>129900</v>
       </c>
       <c r="J35" s="3">
+        <v>81500</v>
+      </c>
+      <c r="K35" s="3">
         <v>96700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>82700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>56000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>83400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>204900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>199900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>130200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>51800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>198300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>76000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>86800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>28900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>169600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>105400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>358100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>22500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2889,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,674 +2918,702 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>379400</v>
+        <v>420100</v>
       </c>
       <c r="E41" s="3">
-        <v>356700</v>
+        <v>380300</v>
       </c>
       <c r="F41" s="3">
-        <v>553200</v>
+        <v>395700</v>
       </c>
       <c r="G41" s="3">
-        <v>648600</v>
+        <v>634300</v>
       </c>
       <c r="H41" s="3">
-        <v>551200</v>
+        <v>722600</v>
       </c>
       <c r="I41" s="3">
-        <v>639000</v>
+        <v>636100</v>
       </c>
       <c r="J41" s="3">
+        <v>702100</v>
+      </c>
+      <c r="K41" s="3">
         <v>458100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>424100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>240200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>823100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1055300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>819200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>726000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>508200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>504000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>413900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>605800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>284000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>422000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>164300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>118100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>171200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>201300</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>215800</v>
+        <v>375600</v>
       </c>
       <c r="E42" s="3">
-        <v>249100</v>
+        <v>216300</v>
       </c>
       <c r="F42" s="3">
-        <v>352000</v>
+        <v>276400</v>
       </c>
       <c r="G42" s="3">
-        <v>150500</v>
+        <v>403600</v>
       </c>
       <c r="H42" s="3">
-        <v>48800</v>
+        <v>167700</v>
       </c>
       <c r="I42" s="3">
-        <v>58500</v>
+        <v>56300</v>
       </c>
       <c r="J42" s="3">
+        <v>64300</v>
+      </c>
+      <c r="K42" s="3">
         <v>393700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>260000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>218000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>837500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>922000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>665600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>653600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>299700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>405200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>294700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>50300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>7000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>120900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>146700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>87400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>140900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>146900</v>
       </c>
     </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>984000</v>
+        <v>1020200</v>
       </c>
       <c r="E43" s="3">
-        <v>949400</v>
+        <v>1001700</v>
       </c>
       <c r="F43" s="3">
-        <v>925200</v>
+        <v>1073200</v>
       </c>
       <c r="G43" s="3">
-        <v>895500</v>
+        <v>1083800</v>
       </c>
       <c r="H43" s="3">
-        <v>805800</v>
+        <v>1020000</v>
       </c>
       <c r="I43" s="3">
-        <v>822200</v>
+        <v>952500</v>
       </c>
       <c r="J43" s="3">
+        <v>915100</v>
+      </c>
+      <c r="K43" s="3">
         <v>829300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>816200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>958900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>898400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>955400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>875900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>867400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>843400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>948600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>956400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>849600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>835500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>923500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>785800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>661200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>670700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>648700</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>74700</v>
+        <v>70200</v>
       </c>
       <c r="E44" s="3">
-        <v>72700</v>
+        <v>74900</v>
       </c>
       <c r="F44" s="3">
-        <v>59600</v>
+        <v>80700</v>
       </c>
       <c r="G44" s="3">
-        <v>74700</v>
+        <v>68400</v>
       </c>
       <c r="H44" s="3">
-        <v>67300</v>
+        <v>83200</v>
       </c>
       <c r="I44" s="3">
-        <v>54100</v>
+        <v>77700</v>
       </c>
       <c r="J44" s="3">
+        <v>59500</v>
+      </c>
+      <c r="K44" s="3">
         <v>42400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>51400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>56100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>45700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>40900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>46600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>43700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>56300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>48300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>40300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>40100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>47900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>37500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>39600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>37800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>40200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>34300</v>
       </c>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>214700</v>
+        <v>105700</v>
       </c>
       <c r="E45" s="3">
-        <v>229400</v>
+        <v>110600</v>
       </c>
       <c r="F45" s="3">
-        <v>159600</v>
+        <v>112600</v>
       </c>
       <c r="G45" s="3">
-        <v>178400</v>
+        <v>111100</v>
       </c>
       <c r="H45" s="3">
-        <v>194900</v>
+        <v>103300</v>
       </c>
       <c r="I45" s="3">
-        <v>206100</v>
+        <v>102500</v>
       </c>
       <c r="J45" s="3">
+        <v>91300</v>
+      </c>
+      <c r="K45" s="3">
         <v>139300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>174200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>279700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>192100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>134300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>132600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>170200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>172100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>131600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>164900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>101300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>108500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>57500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>121800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>152000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>206800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>91300</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1868700</v>
+        <v>2066300</v>
       </c>
       <c r="E46" s="3">
-        <v>1857400</v>
+        <v>1872900</v>
       </c>
       <c r="F46" s="3">
-        <v>2049700</v>
+        <v>2060500</v>
       </c>
       <c r="G46" s="3">
-        <v>1947700</v>
+        <v>2350300</v>
       </c>
       <c r="H46" s="3">
-        <v>1668000</v>
+        <v>2169900</v>
       </c>
       <c r="I46" s="3">
-        <v>1779900</v>
+        <v>1924800</v>
       </c>
       <c r="J46" s="3">
+        <v>1955800</v>
+      </c>
+      <c r="K46" s="3">
         <v>1862800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1725900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1752900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2796900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3107900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2539900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2460900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1879800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2037500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1870100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1647200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1283000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1561500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1258200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1056500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1229800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1122400</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>490200</v>
+        <v>292800</v>
       </c>
       <c r="E47" s="3">
-        <v>493200</v>
+        <v>281000</v>
       </c>
       <c r="F47" s="3">
-        <v>495400</v>
+        <v>330100</v>
       </c>
       <c r="G47" s="3">
-        <v>516300</v>
+        <v>346300</v>
       </c>
       <c r="H47" s="3">
-        <v>644800</v>
+        <v>330900</v>
       </c>
       <c r="I47" s="3">
-        <v>579800</v>
+        <v>347400</v>
       </c>
       <c r="J47" s="3">
+        <v>303100</v>
+      </c>
+      <c r="K47" s="3">
         <v>576000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>637900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>683700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>698500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>693400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>411600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>334300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>367500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>444200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>410400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>665000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>603700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>609100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>786100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>766800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>294700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4056800</v>
+        <v>4145800</v>
       </c>
       <c r="E48" s="3">
-        <v>4078000</v>
+        <v>4085600</v>
       </c>
       <c r="F48" s="3">
-        <v>4028100</v>
+        <v>4545300</v>
       </c>
       <c r="G48" s="3">
-        <v>4066600</v>
+        <v>4641600</v>
       </c>
       <c r="H48" s="3">
-        <v>4149000</v>
+        <v>4553300</v>
       </c>
       <c r="I48" s="3">
-        <v>4192600</v>
+        <v>4811700</v>
       </c>
       <c r="J48" s="3">
+        <v>4629200</v>
+      </c>
+      <c r="K48" s="3">
         <v>4072900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4268300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4739300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3963300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3695400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3515000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3373600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3450400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3542300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3380900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3415200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3190900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3253000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3129600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2907800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2970000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2096500</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2730900</v>
+        <v>2720700</v>
       </c>
       <c r="E49" s="3">
-        <v>2777200</v>
+        <v>2717100</v>
       </c>
       <c r="F49" s="3">
-        <v>2808300</v>
+        <v>3059400</v>
       </c>
       <c r="G49" s="3">
-        <v>2834900</v>
+        <v>3197400</v>
       </c>
       <c r="H49" s="3">
-        <v>2884700</v>
+        <v>3135700</v>
       </c>
       <c r="I49" s="3">
-        <v>2936100</v>
+        <v>3304700</v>
       </c>
       <c r="J49" s="3">
+        <v>3204000</v>
+      </c>
+      <c r="K49" s="3">
         <v>2950500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2946800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3155600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2179800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2136500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1459200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1444800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1650300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1766600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1755400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1826000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1703000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1785700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1846400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1791600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1947200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1998900</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3686,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,82 +3763,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>565000</v>
+        <v>522500</v>
       </c>
       <c r="E52" s="3">
-        <v>559700</v>
+        <v>498500</v>
       </c>
       <c r="F52" s="3">
-        <v>550500</v>
+        <v>505200</v>
       </c>
       <c r="G52" s="3">
-        <v>694600</v>
+        <v>510200</v>
       </c>
       <c r="H52" s="3">
-        <v>665500</v>
+        <v>651400</v>
       </c>
       <c r="I52" s="3">
-        <v>683000</v>
+        <v>805600</v>
       </c>
       <c r="J52" s="3">
+        <v>728200</v>
+      </c>
+      <c r="K52" s="3">
         <v>676000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>525300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>552700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>442800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>422300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>931700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>878600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>344500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>361100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>333500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>295600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>270900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>243100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>278500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>276200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>448900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>461900</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +3917,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>9711600</v>
+        <v>10015400</v>
       </c>
       <c r="E54" s="3">
-        <v>9765500</v>
+        <v>9733200</v>
       </c>
       <c r="F54" s="3">
-        <v>9931900</v>
+        <v>10833300</v>
       </c>
       <c r="G54" s="3">
-        <v>10060000</v>
+        <v>11388400</v>
       </c>
       <c r="H54" s="3">
-        <v>10012100</v>
+        <v>11207800</v>
       </c>
       <c r="I54" s="3">
-        <v>10171400</v>
+        <v>11553300</v>
       </c>
       <c r="J54" s="3">
+        <v>11176600</v>
+      </c>
+      <c r="K54" s="3">
         <v>10138300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10104100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10884200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10081300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10055500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8857300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8492200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7692600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8151800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7750300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7849100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7051500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7452400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7298800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6798900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6890500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5980300</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4025,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,452 +4054,471 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>655800</v>
+        <v>671000</v>
       </c>
       <c r="E57" s="3">
-        <v>703100</v>
+        <v>657300</v>
       </c>
       <c r="F57" s="3">
-        <v>828900</v>
+        <v>780000</v>
       </c>
       <c r="G57" s="3">
-        <v>692600</v>
+        <v>950500</v>
       </c>
       <c r="H57" s="3">
-        <v>656200</v>
+        <v>771700</v>
       </c>
       <c r="I57" s="3">
-        <v>694300</v>
+        <v>757200</v>
       </c>
       <c r="J57" s="3">
+        <v>762900</v>
+      </c>
+      <c r="K57" s="3">
         <v>761600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>766200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>818400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>618900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>659500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>534400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>501500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>497900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>612300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>423900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>407700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>470400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>724600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>548300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>512000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>707700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>809000</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>401500</v>
+        <v>404800</v>
       </c>
       <c r="E58" s="3">
-        <v>468700</v>
+        <v>402400</v>
       </c>
       <c r="F58" s="3">
-        <v>552800</v>
+        <v>519900</v>
       </c>
       <c r="G58" s="3">
-        <v>753100</v>
+        <v>633900</v>
       </c>
       <c r="H58" s="3">
-        <v>768700</v>
+        <v>839000</v>
       </c>
       <c r="I58" s="3">
-        <v>698500</v>
+        <v>887000</v>
       </c>
       <c r="J58" s="3">
+        <v>767500</v>
+      </c>
+      <c r="K58" s="3">
         <v>633000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>369800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>390000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>277400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>365000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>359000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>509600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>630200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>537000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>543200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>513900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>363300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>416900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>432400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>233000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>249900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1055900</v>
+        <v>324000</v>
       </c>
       <c r="E59" s="3">
-        <v>1124000</v>
+        <v>381700</v>
       </c>
       <c r="F59" s="3">
-        <v>933700</v>
+        <v>533300</v>
       </c>
       <c r="G59" s="3">
-        <v>1020000</v>
+        <v>362800</v>
       </c>
       <c r="H59" s="3">
-        <v>958600</v>
+        <v>506000</v>
       </c>
       <c r="I59" s="3">
-        <v>1009900</v>
+        <v>497600</v>
       </c>
       <c r="J59" s="3">
+        <v>561400</v>
+      </c>
+      <c r="K59" s="3">
         <v>963100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>771900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>730500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>900400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1117300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>482200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>462100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>350500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>475400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>332200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>307800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>229800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>357800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>383300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>256100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>261700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>345900</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2113200</v>
+        <v>2135000</v>
       </c>
       <c r="E60" s="3">
-        <v>2295700</v>
+        <v>2117900</v>
       </c>
       <c r="F60" s="3">
-        <v>2315500</v>
+        <v>2546700</v>
       </c>
       <c r="G60" s="3">
-        <v>2465700</v>
+        <v>2655000</v>
       </c>
       <c r="H60" s="3">
-        <v>2383400</v>
+        <v>2747000</v>
       </c>
       <c r="I60" s="3">
-        <v>2402700</v>
+        <v>2750300</v>
       </c>
       <c r="J60" s="3">
+        <v>2640200</v>
+      </c>
+      <c r="K60" s="3">
         <v>2357700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1907900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1938900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1796700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2141800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1375500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1473300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1478600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1624700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1299200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1229400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1063500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1499300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1364000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1001100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1219300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1324000</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2397900</v>
+        <v>2467900</v>
       </c>
       <c r="E61" s="3">
-        <v>2342600</v>
+        <v>2403200</v>
       </c>
       <c r="F61" s="3">
-        <v>2327800</v>
+        <v>2598700</v>
       </c>
       <c r="G61" s="3">
-        <v>2381900</v>
+        <v>2669200</v>
       </c>
       <c r="H61" s="3">
-        <v>2446900</v>
+        <v>2653700</v>
       </c>
       <c r="I61" s="3">
-        <v>2563100</v>
+        <v>2823500</v>
       </c>
       <c r="J61" s="3">
+        <v>2816500</v>
+      </c>
+      <c r="K61" s="3">
         <v>2566500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2847800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3116100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2431100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2240600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2043100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1939900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1417100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1561600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1494800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1638000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1534300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1395000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1393500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1461300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1503800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>505100</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>621800</v>
+        <v>536300</v>
       </c>
       <c r="E62" s="3">
-        <v>629400</v>
+        <v>516200</v>
       </c>
       <c r="F62" s="3">
-        <v>612800</v>
+        <v>575800</v>
       </c>
       <c r="G62" s="3">
-        <v>616000</v>
+        <v>573500</v>
       </c>
       <c r="H62" s="3">
-        <v>629800</v>
+        <v>559600</v>
       </c>
       <c r="I62" s="3">
-        <v>673500</v>
+        <v>593200</v>
       </c>
       <c r="J62" s="3">
+        <v>610100</v>
+      </c>
+      <c r="K62" s="3">
         <v>649500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>674800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>752300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>643300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>605500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>475800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>475600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>407100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>428600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>427700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>479400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>421400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>415000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>459000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>451600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>440000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>446900</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4591,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4668,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,82 +4745,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5132900</v>
+        <v>5244700</v>
       </c>
       <c r="E66" s="3">
-        <v>5267700</v>
+        <v>5144300</v>
       </c>
       <c r="F66" s="3">
-        <v>5256100</v>
+        <v>5843700</v>
       </c>
       <c r="G66" s="3">
-        <v>5463600</v>
+        <v>6026900</v>
       </c>
       <c r="H66" s="3">
-        <v>5460100</v>
+        <v>6087000</v>
       </c>
       <c r="I66" s="3">
-        <v>5639400</v>
+        <v>6300600</v>
       </c>
       <c r="J66" s="3">
+        <v>6196700</v>
+      </c>
+      <c r="K66" s="3">
         <v>5573600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5430500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5807300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4871000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4987900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3894400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3888700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3302800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3614900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3221800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3346700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3019200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3309300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3216600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2914000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3163100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2276100</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4853,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4928,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5005,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5082,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,82 +5159,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2102000</v>
+        <v>2235000</v>
       </c>
       <c r="E72" s="3">
-        <v>2014100</v>
+        <v>2098600</v>
       </c>
       <c r="F72" s="3">
-        <v>2191000</v>
+        <v>2227000</v>
       </c>
       <c r="G72" s="3">
-        <v>2111700</v>
+        <v>2506000</v>
       </c>
       <c r="H72" s="3">
-        <v>2066800</v>
+        <v>2347700</v>
       </c>
       <c r="I72" s="3">
-        <v>2046800</v>
+        <v>2371300</v>
       </c>
       <c r="J72" s="3">
+        <v>2237100</v>
+      </c>
+      <c r="K72" s="3">
         <v>2079500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2119200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2311700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2368000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2277700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2179300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1930100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1803500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1831900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1835100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2161300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2204900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2251400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2160900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2071600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1811200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1788100</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5313,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5390,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5467,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4578700</v>
+        <v>4770700</v>
       </c>
       <c r="E76" s="3">
-        <v>4497800</v>
+        <v>4588900</v>
       </c>
       <c r="F76" s="3">
-        <v>4675800</v>
+        <v>4989600</v>
       </c>
       <c r="G76" s="3">
-        <v>4596400</v>
+        <v>5361600</v>
       </c>
       <c r="H76" s="3">
-        <v>4552000</v>
+        <v>5120900</v>
       </c>
       <c r="I76" s="3">
-        <v>4532000</v>
+        <v>5252700</v>
       </c>
       <c r="J76" s="3">
+        <v>4979900</v>
+      </c>
+      <c r="K76" s="3">
         <v>4564700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4673600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5076900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5210200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5067600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4962900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4603400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4389800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4536900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4528500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4502400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4032300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4143200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4082200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3884900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3727500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3704200</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5621,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>140400</v>
+        <v>147800</v>
       </c>
       <c r="E81" s="3">
-        <v>93400</v>
+        <v>140700</v>
       </c>
       <c r="F81" s="3">
-        <v>194600</v>
+        <v>103600</v>
       </c>
       <c r="G81" s="3">
-        <v>128700</v>
+        <v>223100</v>
       </c>
       <c r="H81" s="3">
-        <v>112600</v>
+        <v>143400</v>
       </c>
       <c r="I81" s="3">
-        <v>74100</v>
+        <v>129900</v>
       </c>
       <c r="J81" s="3">
+        <v>81500</v>
+      </c>
+      <c r="K81" s="3">
         <v>96700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>82700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>56000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>83400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>204900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>199900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>130200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>51800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>198300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>76000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>86800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>28900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>169600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>105400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>358100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>22500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,82 +5811,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>315500</v>
+        <v>253800</v>
       </c>
       <c r="E83" s="3">
-        <v>315400</v>
+        <v>283000</v>
       </c>
       <c r="F83" s="3">
-        <v>314500</v>
+        <v>255300</v>
       </c>
       <c r="G83" s="3">
-        <v>315500</v>
+        <v>135300</v>
       </c>
       <c r="H83" s="3">
-        <v>329700</v>
+        <v>260700</v>
       </c>
       <c r="I83" s="3">
-        <v>319400</v>
+        <v>233500</v>
       </c>
       <c r="J83" s="3">
+        <v>205100</v>
+      </c>
+      <c r="K83" s="3">
         <v>334000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>347400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>338600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>287700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>289800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>282800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>275700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>267100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>269800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>270800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>543500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>251500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>195800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>269500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>229800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>249700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>190500</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5963,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6040,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6117,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6194,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,82 +6271,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>482800</v>
+        <v>638700</v>
       </c>
       <c r="E89" s="3">
-        <v>295800</v>
+        <v>483900</v>
       </c>
       <c r="F89" s="3">
-        <v>871500</v>
+        <v>328100</v>
       </c>
       <c r="G89" s="3">
-        <v>626200</v>
+        <v>999300</v>
       </c>
       <c r="H89" s="3">
-        <v>379600</v>
+        <v>697700</v>
       </c>
       <c r="I89" s="3">
-        <v>355000</v>
+        <v>441300</v>
       </c>
       <c r="J89" s="3">
+        <v>387000</v>
+      </c>
+      <c r="K89" s="3">
         <v>629400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>641600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>267500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>230200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>630400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>558400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>432300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>364700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>723800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>426300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>549100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>87000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>666100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>394600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>187500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>55400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>546400</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,82 +6379,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1002100</v>
+        <v>-164600</v>
       </c>
       <c r="E91" s="3">
-        <v>-1354500</v>
+        <v>-166600</v>
       </c>
       <c r="F91" s="3">
-        <v>-1291900</v>
+        <v>-270100</v>
       </c>
       <c r="G91" s="3">
-        <v>-998200</v>
+        <v>-266200</v>
       </c>
       <c r="H91" s="3">
-        <v>-925700</v>
+        <v>-199900</v>
       </c>
       <c r="I91" s="3">
-        <v>-1288500</v>
+        <v>-192000</v>
       </c>
       <c r="J91" s="3">
+        <v>-254500</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1375200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-977600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1049600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1328000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2157400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-896500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-175400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-247700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-286500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-165600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-310800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-161400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-246500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-173300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-167300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-121700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-256800</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6531,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,82 +6608,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-139500</v>
+        <v>-321000</v>
       </c>
       <c r="E94" s="3">
-        <v>-131600</v>
+        <v>-139800</v>
       </c>
       <c r="F94" s="3">
-        <v>-518600</v>
+        <v>-145900</v>
       </c>
       <c r="G94" s="3">
-        <v>-277600</v>
+        <v>-594600</v>
       </c>
       <c r="H94" s="3">
-        <v>-150400</v>
+        <v>-309200</v>
       </c>
       <c r="I94" s="3">
-        <v>104800</v>
+        <v>-176900</v>
       </c>
       <c r="J94" s="3">
+        <v>118300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-396300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-268300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-828100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-170900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-470600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-166300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-518500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-159800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-395400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-408500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-231700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-50600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-222900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-226400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-121600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-114600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-291500</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,82 +6716,86 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-112600</v>
+        <v>14800</v>
       </c>
       <c r="E96" s="3">
-        <v>-115900</v>
+        <v>112800</v>
       </c>
       <c r="F96" s="3">
-        <v>-75200</v>
+        <v>128600</v>
       </c>
       <c r="G96" s="3">
-        <v>-51300</v>
+        <v>86300</v>
       </c>
       <c r="H96" s="3">
-        <v>-146600</v>
+        <v>57200</v>
       </c>
       <c r="I96" s="3">
-        <v>-117700</v>
+        <v>169200</v>
       </c>
       <c r="J96" s="3">
+        <v>129300</v>
+      </c>
+      <c r="K96" s="3">
         <v>-47800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-49200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-38500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-97700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-42700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-59800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-91000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-108700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-5700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-112000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-101300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-67300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-11800</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-64200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6868,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6945,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,105 +7022,111 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-320600</v>
+        <v>-285300</v>
       </c>
       <c r="E100" s="3">
-        <v>-360700</v>
+        <v>-321300</v>
       </c>
       <c r="F100" s="3">
-        <v>-448300</v>
+        <v>-400200</v>
       </c>
       <c r="G100" s="3">
-        <v>-251300</v>
+        <v>-514100</v>
       </c>
       <c r="H100" s="3">
-        <v>-316900</v>
+        <v>-279900</v>
       </c>
       <c r="I100" s="3">
-        <v>-278900</v>
+        <v>-365700</v>
       </c>
       <c r="J100" s="3">
+        <v>-306500</v>
+      </c>
+      <c r="K100" s="3">
         <v>-187600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-200400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>30700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-311300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>74500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-328000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>286200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-178500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-240200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-202700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-161800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-160300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-183000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-129100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-109800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>29200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-175900</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6927,78 +7176,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>22700</v>
+        <v>32400</v>
       </c>
       <c r="E102" s="3">
-        <v>-196500</v>
+        <v>22800</v>
       </c>
       <c r="F102" s="3">
-        <v>-95400</v>
+        <v>-218000</v>
       </c>
       <c r="G102" s="3">
-        <v>97400</v>
+        <v>-109400</v>
       </c>
       <c r="H102" s="3">
-        <v>-87700</v>
+        <v>108500</v>
       </c>
       <c r="I102" s="3">
-        <v>180900</v>
+        <v>-101200</v>
       </c>
       <c r="J102" s="3">
+        <v>198800</v>
+      </c>
+      <c r="K102" s="3">
         <v>45500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>202700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-562000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-252000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>234300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>64100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>199900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>26400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>88200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-184800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>155600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-123900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>260200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>39200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-43900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-30000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>79000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TIMB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TIMB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>TIMB</t>
   </si>
@@ -656,353 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1072100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1178800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1135300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1215300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1293200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1212500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1216000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1113900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1046800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1036700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1075900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>972100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>968700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>908700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>853300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>811900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>915500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>854600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1616400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>752500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>847100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>813600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>754800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>784200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>834100</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>495700</v>
+      </c>
+      <c r="E9" s="3">
         <v>543500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>525100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>588800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>600400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>568400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>608200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>555300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>658400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>668500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>697000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>611500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>563900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>546100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>522400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>499800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>414300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>399500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1122400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>350200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>307400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>366300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>329200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>366300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>367900</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>576500</v>
+      </c>
+      <c r="E10" s="3">
         <v>635300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>610200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>626600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>692800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>644100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>607800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>558600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>388500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>368200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>378900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>360600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>404800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>362500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>331000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>312100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>501200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>455100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>494000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>402400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>539800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>447200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>425600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>417900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>466200</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1030,8 +1042,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1107,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,162 +1200,171 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>18500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>35100</v>
       </c>
-      <c r="G14" s="3">
-        <v>14100</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+      <c r="H14" s="3">
+        <v>-36400</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>41200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>10000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>7000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>6700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>13900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>9400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>11700</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>38400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>11800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>10700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>17400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>40300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>16500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>172500</v>
+      </c>
+      <c r="E15" s="3">
         <v>208700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>178700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>225000</v>
       </c>
-      <c r="G15" s="3">
-        <v>182400</v>
-      </c>
       <c r="H15" s="3">
+        <v>194800</v>
+      </c>
+      <c r="I15" s="3">
         <v>213200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>205800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>177600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>32800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>34700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>37500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>40200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>41000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>42200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>40700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>41400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>43800</v>
       </c>
-      <c r="T15" s="3" t="s">
+      <c r="U15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>48900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>44300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>43900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>48900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>44800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>45900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>802800</v>
+      </c>
+      <c r="E17" s="3">
         <v>913300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>883600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>972300</v>
       </c>
-      <c r="G17" s="3">
-        <v>994000</v>
-      </c>
       <c r="H17" s="3">
+        <v>993600</v>
+      </c>
+      <c r="I17" s="3">
         <v>963500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>995800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>938400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>872300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>896000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>929100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>829200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>616500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>756600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>724900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>701100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>724800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>721600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1388200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>660600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>616100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>690200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>372700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>700300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>683600</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>269300</v>
+      </c>
+      <c r="E18" s="3">
         <v>265500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>251700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>243100</v>
       </c>
-      <c r="G18" s="3">
-        <v>299200</v>
-      </c>
       <c r="H18" s="3">
+        <v>299700</v>
+      </c>
+      <c r="I18" s="3">
         <v>249000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>220200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>175500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>174500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>140800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>146800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>142900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>352200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>152100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>128400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>110900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>190700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>133000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>228100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>92000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>231000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>123400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>382100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>84000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>150500</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,393 +1579,409 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E20" s="3">
         <v>3700</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>8400</v>
       </c>
-      <c r="G20" s="3">
-        <v>-38300</v>
-      </c>
       <c r="H20" s="3">
+        <v>22700</v>
+      </c>
+      <c r="I20" s="3">
         <v>3700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4900</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>4600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-20100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>7400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>20300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>5400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>36500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>29500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-47500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-56900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-9700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>179600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-6300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>438200</v>
+      </c>
+      <c r="E21" s="3">
         <v>470500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>430400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>459700</v>
       </c>
-      <c r="G21" s="3">
-        <v>520000</v>
-      </c>
       <c r="H21" s="3">
+        <v>471800</v>
+      </c>
+      <c r="I21" s="3">
         <v>458500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>421000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>353100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>513100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>491000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>465200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>438000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>662400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>440200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>440600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>373400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>490000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>356300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>714700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>333700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>427400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>388300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>791500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>327300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>344400</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>98300</v>
+      </c>
+      <c r="E22" s="3">
         <v>121300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>119100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>122800</v>
       </c>
-      <c r="G22" s="3">
-        <v>131700</v>
-      </c>
       <c r="H22" s="3">
+        <v>121600</v>
+      </c>
+      <c r="I22" s="3">
         <v>135000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>153700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>83200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>67500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>77100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>67900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>58300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>56700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>47900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>43500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>37600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>38200</v>
       </c>
-      <c r="T22" s="3" t="s">
+      <c r="U22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>45400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>35700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>44100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>45500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>40300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>42800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>184100</v>
+      </c>
+      <c r="E23" s="3">
         <v>178500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>166500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>117200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>247800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>162700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>127100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>109800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>111600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>66500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>58800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>91900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>315800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>109600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>121400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>68700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>182000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>85500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>125800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>46500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>187500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>73300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>521300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>34800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E24" s="3">
         <v>30600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>25800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>13700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>24700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>19300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>28400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>14900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-16200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>110900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-90300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-8800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>16900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-16300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>9600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>39000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>17600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>17800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-32100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>163300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>12400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>169500</v>
+      </c>
+      <c r="E26" s="3">
         <v>147800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>140700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>103600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>223100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>143400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>129900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>81500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>96700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>82700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>56000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>83400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>204900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>199900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>130200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>51800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>198300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>76000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>86800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>28900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>169600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>105400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>358100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>22500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>169500</v>
+      </c>
+      <c r="E27" s="3">
         <v>147800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>140700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>103600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>223100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>143400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>129900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>81500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>96700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>82700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>56000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>83400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>204900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>199900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>130200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>51800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>198300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>76000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>86800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>28900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>169600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>105400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>358100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>22500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2317,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,162 +2537,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3700</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-8400</v>
       </c>
-      <c r="G32" s="3">
-        <v>38300</v>
-      </c>
       <c r="H32" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="I32" s="3">
         <v>-3700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4900</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-4600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>20100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-7400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-20300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-36500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-29500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>47500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>56900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>9700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>4600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-179600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>6300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>169500</v>
+      </c>
+      <c r="E33" s="3">
         <v>147800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>140700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>103600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>223100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>143400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>129900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>81500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>96700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>82700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>56000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>83400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>204900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>199900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>130200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>51800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>198300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>76000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>86800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>28900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>169600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>105400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>358100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>22500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>169500</v>
+      </c>
+      <c r="E35" s="3">
         <v>147800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>140700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>103600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>223100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>143400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>129900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>81500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>96700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>82700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>56000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>83400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>204900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>199900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>130200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>51800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>198300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>76000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>86800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>28900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>169600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>105400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>358100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>22500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,701 +3004,729 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>526900</v>
+      </c>
+      <c r="E41" s="3">
         <v>420100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>380300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>395700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>634300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>722600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>636100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>702100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>458100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>424100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>240200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>823100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1055300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>819200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>726000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>508200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>504000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>413900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>605800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>284000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>422000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>164300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>118100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>171200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>201300</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>393600</v>
+      </c>
+      <c r="E42" s="3">
         <v>375600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>216300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>276400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>403600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>167700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>56300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>64300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>393700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>260000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>218000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>837500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>922000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>665600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>653600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>299700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>405200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>294700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>50300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>7000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>120900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>146700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>87400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>140900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>146900</v>
       </c>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>938900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1020200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1001700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1073200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1083800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1020000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>952500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>915100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>829300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>816200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>958900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>898400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>955400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>875900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>867400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>843400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>948600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>956400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>849600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>835500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>923500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>785800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>661200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>670700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>648700</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E44" s="3">
         <v>70200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>74900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>80700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>68400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>83200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>77700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>59500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>42400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>51400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>56100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>45700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>40900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>46600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>43700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>56300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>48300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>40300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>40100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>47900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>37500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>39600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>37800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>40200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>34300</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>95100</v>
+      </c>
+      <c r="E45" s="3">
         <v>105700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>110600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>112600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>111100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>103300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>102500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>91300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>139300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>174200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>279700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>192100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>134300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>132600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>170200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>172100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>131600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>164900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>101300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>108500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>57500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>121800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>152000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>206800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>91300</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2047400</v>
+      </c>
+      <c r="E46" s="3">
         <v>2066300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1872900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2060500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2350300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2169900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1924800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1955800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1862800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1725900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1752900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2796900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3107900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2539900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2460900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1879800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2037500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1870100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1647200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1283000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1561500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1258200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1056500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1229800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1122400</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>312700</v>
+      </c>
+      <c r="E47" s="3">
         <v>292800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>281000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>330100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>346300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>330900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>347400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>303100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>576000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>637900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>683700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>698500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>693400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>411600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>334300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>367500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>444200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>410400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>665000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>603700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>609100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>786100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>766800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>294700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3705800</v>
+      </c>
+      <c r="E48" s="3">
         <v>4145800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4085600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4545300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4641600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4553300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4811700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4629200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4072900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4268300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4739300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3963300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3695400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3515000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3373600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3450400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3542300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3380900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3415200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3190900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3253000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3129600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2907800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2970000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2096500</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2384900</v>
+      </c>
+      <c r="E49" s="3">
         <v>2720700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2717100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3059400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3197400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3135700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3304700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3204000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2950500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2946800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3155600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2179800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2136500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1459200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1444800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1650300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1766600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1755400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1826000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1703000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1785700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1846400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1791600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1947200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1998900</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,85 +3882,91 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>425800</v>
+      </c>
+      <c r="E52" s="3">
         <v>522500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>498500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>505200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>510200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>651400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>805600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>728200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>676000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>525300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>552700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>442800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>422300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>931700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>878600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>344500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>361100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>333500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>295600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>270900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>243100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>278500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>276200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>448900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>461900</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,85 +4042,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9107200</v>
+      </c>
+      <c r="E54" s="3">
         <v>10015400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9733200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10833300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11388400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11207800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11553300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11176600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10138300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10104100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10884200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10081300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10055500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8857300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8492200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7692600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8151800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7750300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7849100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7051500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7452400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7298800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6798900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6890500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5980300</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,470 +4184,489 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>806300</v>
+      </c>
+      <c r="E57" s="3">
         <v>671000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>657300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>780000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>950500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>771700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>757200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>762900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>761600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>766200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>818400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>618900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>659500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>534400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>501500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>497900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>612300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>423900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>407700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>470400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>724600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>548300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>512000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>707700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>809000</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>319800</v>
+      </c>
+      <c r="E58" s="3">
         <v>404800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>402400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>519900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>633900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>839000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>887000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>767500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>633000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>369800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>390000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>277400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>365000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>359000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>509600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>630200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>537000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>543200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>513900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>363300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>416900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>432400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>233000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>249900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>262000</v>
+      </c>
+      <c r="E59" s="3">
         <v>324000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>381700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>533300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>362800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>506000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>497600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>561400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>963100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>771900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>730500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>900400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1117300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>482200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>462100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>350500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>475400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>332200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>307800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>229800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>357800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>383300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>256100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>261700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>345900</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2074000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2135000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2117900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2546700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2655000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2747000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2750300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2640200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2357700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1907900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1938900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1796700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2141800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1375500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1473300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1478600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1624700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1299200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1229400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1063500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1499300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1364000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1001100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1219300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1324000</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2204300</v>
+      </c>
+      <c r="E61" s="3">
         <v>2467900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2403200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2598700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2669200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2653700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2823500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2816500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2566500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2847800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3116100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2431100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2240600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2043100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1939900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1417100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1561600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1494800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1638000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1534300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1395000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1393500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1461300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1503800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>505100</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>468800</v>
+      </c>
+      <c r="E62" s="3">
         <v>536300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>516200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>575800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>573500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>559600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>593200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>610100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>649500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>674800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>752300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>643300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>605500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>475800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>475600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>407100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>428600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>427700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>479400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>421400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>415000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>459000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>451600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>440000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>446900</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,85 +4902,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4838000</v>
+      </c>
+      <c r="E66" s="3">
         <v>5244700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5144300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5843700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6026900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6087000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6300600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6196700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5573600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5430500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5807300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4871000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4987900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3894400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3888700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3302800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3614900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3221800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3346700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3019200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3309300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3216600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2914000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3163100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2276100</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5085,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,85 +5332,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2030700</v>
+      </c>
+      <c r="E72" s="3">
         <v>2235000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2098600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2227000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2506000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2347700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2371300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2237100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2079500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2119200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2311700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2368000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2277700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2179300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1930100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1803500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1831900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1835100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2161300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2204900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2251400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2160900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2071600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1811200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1788100</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,85 +5652,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4269200</v>
+      </c>
+      <c r="E76" s="3">
         <v>4770700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4588900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4989600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5361600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5120900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5252700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4979900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4564700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4673600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5076900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5210200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5067600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4962900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4603400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4389800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4536900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4528500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4502400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4032300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4143200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4082200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3884900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3727500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3704200</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>169500</v>
+      </c>
+      <c r="E81" s="3">
         <v>147800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>140700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>103600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>223100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>143400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>129900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>81500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>96700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>82700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>56000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>83400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>204900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>199900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>130200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>51800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>198300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>76000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>86800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>28900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>169600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>105400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>358100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>22500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,85 +6009,89 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>261100</v>
+      </c>
+      <c r="E83" s="3">
         <v>253800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>283000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>255300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>135300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>260700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>233500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>205100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>334000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>347400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>338600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>287700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>289800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>282800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>275700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>267100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>269800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>270800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>543500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>251500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>195800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>269500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>229800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>249700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>190500</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>731000</v>
+      </c>
+      <c r="E89" s="3">
         <v>638700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>483900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>328100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>999300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>697700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>441300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>387000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>629400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>641600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>267500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>230200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>630400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>558400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>432300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>364700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>723800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>426300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>549100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>87000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>666100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>394600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>187500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>55400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>546400</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,85 +6599,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-222200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-164600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-166600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-270100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-266200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-199900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-192000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-254500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1375200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-977600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1049600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1328000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2157400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-896500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-175400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-247700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-286500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-165600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-310800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-161400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-246500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-173300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-167300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-121700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-256800</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,85 +6837,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-274500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-321000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-139800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-145900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-594600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-309200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-176900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>118300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-396300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-268300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-828100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-170900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-470600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-166300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-518500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-159800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-395400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-408500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-231700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-50600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-222900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-226400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-121600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-114600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-291500</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,85 +6949,89 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>221200</v>
+      </c>
+      <c r="E96" s="3">
         <v>14800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>112800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>128600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>86300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>57200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>169200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>129300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-47800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-49200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-38500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-97700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-42700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-59800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-9300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-91000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-108700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-5700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-112000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-101300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-67300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-11800</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-64200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,85 +7267,91 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-299500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-285300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-321300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-400200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-514100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-279900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-365700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-306500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-187600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-200400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>30700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-311300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>74500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-328000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>286200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-178500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-240200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-202700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-161800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-160300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-183000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-129100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-109800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>29200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-175900</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7128,8 +7376,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7179,81 +7427,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>157100</v>
+      </c>
+      <c r="E102" s="3">
         <v>32400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>22800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-218000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-109400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>108500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-101200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>198800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>45500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>202700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-562000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-252000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>234300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>64100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>199900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>26400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>88200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-184800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>155600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-123900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>260200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>39200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-43900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-30000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>79000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TIMB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TIMB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>TIMB</t>
   </si>
@@ -656,365 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1115100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1072100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1178800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1135300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1215300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1293200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1212500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1216000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1113900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1046800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1036700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1075900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>972100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>968700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>908700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>853300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>811900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>915500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>854600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1616400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>752500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>847100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>813600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>754800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>784200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>834100</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>531000</v>
+      </c>
+      <c r="E9" s="3">
         <v>495700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>543500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>525100</v>
       </c>
-      <c r="G9" s="3">
-        <v>588800</v>
-      </c>
       <c r="H9" s="3">
+        <v>581700</v>
+      </c>
+      <c r="I9" s="3">
         <v>600400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>568400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>608200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>555300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>658400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>668500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>697000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>611500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>563900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>546100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>522400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>499800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>414300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>399500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1122400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>350200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>307400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>366300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>329200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>366300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>367900</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>584100</v>
+      </c>
+      <c r="E10" s="3">
         <v>576500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>635300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>610200</v>
       </c>
-      <c r="G10" s="3">
-        <v>626600</v>
-      </c>
       <c r="H10" s="3">
+        <v>633700</v>
+      </c>
+      <c r="I10" s="3">
         <v>692800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>644100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>607800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>558600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>388500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>368200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>378900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>360600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>404800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>362500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>331000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>312100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>501200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>455100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>494000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>402400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>539800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>447200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>425600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>417900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>466200</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,8 +1056,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1123,8 +1137,11 @@
       <c r="AB12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,168 +1220,177 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E14" s="3">
         <v>18500</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>35100</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3">
+        <v>16700</v>
+      </c>
+      <c r="I14" s="3">
         <v>-36400</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>41200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>10000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>6700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>13900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>9400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>11700</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>38400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>11800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>10700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>17400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>40300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>16500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>191400</v>
+      </c>
+      <c r="E15" s="3">
         <v>172500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>208700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>178700</v>
       </c>
-      <c r="G15" s="3">
-        <v>225000</v>
-      </c>
       <c r="H15" s="3">
+        <v>209000</v>
+      </c>
+      <c r="I15" s="3">
         <v>194800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>213200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>205800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>177600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>32800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>34700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>37500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>40200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>41000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>42200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>40700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>41400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>43800</v>
       </c>
-      <c r="U15" s="3" t="s">
+      <c r="V15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>48900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>44300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>43900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>48900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>44800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>45900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>874800</v>
+      </c>
+      <c r="E17" s="3">
         <v>802800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>913300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>883600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>972300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>993600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>963500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>995800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>938400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>872300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>896000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>929100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>829200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>616500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>756600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>724900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>701100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>724800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>721600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1388200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>660600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>616100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>690200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>372700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>700300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>683600</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>240300</v>
+      </c>
+      <c r="E18" s="3">
         <v>269300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>265500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>251700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>243100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>299700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>249000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>220200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>175500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>174500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>140800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>146800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>142900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>352200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>152100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>128400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>110900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>190700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>133000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>228100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>92000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>231000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>123400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>382100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>84000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>150500</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,408 +1613,424 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E20" s="3">
         <v>3600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3700</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
-        <v>8400</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>32300</v>
+      </c>
+      <c r="I20" s="3">
         <v>22700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4900</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>4600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-20100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>20300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>36500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>29500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-47500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-56900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-9700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>179600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-6300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>385800</v>
+      </c>
+      <c r="E21" s="3">
         <v>438200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>470500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>430400</v>
       </c>
-      <c r="G21" s="3">
-        <v>459700</v>
-      </c>
       <c r="H21" s="3">
+        <v>419700</v>
+      </c>
+      <c r="I21" s="3">
         <v>471800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>458500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>421000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>353100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>513100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>491000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>465200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>438000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>662400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>440200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>440600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>373400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>490000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>356300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>714700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>333700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>427400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>388300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>791500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>327300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>344400</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>110400</v>
+      </c>
+      <c r="E22" s="3">
         <v>98300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>121300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>119100</v>
       </c>
-      <c r="G22" s="3">
-        <v>122800</v>
-      </c>
       <c r="H22" s="3">
+        <v>117200</v>
+      </c>
+      <c r="I22" s="3">
         <v>121600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>135000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>153700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>83200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>67500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>77100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>67900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>58300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>56700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>47900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>43500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>37600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>38200</v>
       </c>
-      <c r="U22" s="3" t="s">
+      <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>45400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>35700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>44100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>45500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>40300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>42800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E23" s="3">
         <v>184100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>178500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>166500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>117200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>247800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>162700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>127100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>109800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>111600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>66500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>58800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>91900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>315800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>109600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>121400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>68700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>182000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>85500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>125800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>46500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>187500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>73300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>521300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>34800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E24" s="3">
         <v>14600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>30600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>25800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>13700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>24700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>19300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>28400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>14900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-16200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>110900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-90300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-8800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>16900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-16300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>9600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>39000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>17600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>17800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-32100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>163300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>12400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>139100</v>
+      </c>
+      <c r="E26" s="3">
         <v>169500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>147800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>140700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>103600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>223100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>143400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>129900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>81500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>96700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>82700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>56000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>83400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>204900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>199900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>130200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>51800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>198300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>76000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>86800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>28900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>169600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>105400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>358100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>22500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>139100</v>
+      </c>
+      <c r="E27" s="3">
         <v>169500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>147800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>140700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>103600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>223100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>143400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>129900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>81500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>96700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>82700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>56000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>83400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>204900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>199900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>130200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>51800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>198300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>76000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>86800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>28900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>169600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>105400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>358100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>22500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,168 +2607,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-45900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3700</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
-        <v>-8400</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="I32" s="3">
         <v>-22700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4900</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-4600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>20100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-20300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-36500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-29500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>47500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>56900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>9700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>4600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-179600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>6300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>139100</v>
+      </c>
+      <c r="E33" s="3">
         <v>169500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>147800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>140700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>103600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>223100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>143400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>129900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>81500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>96700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>82700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>56000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>83400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>204900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>199900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>130200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>51800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>198300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>76000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>86800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>28900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>169600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>105400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>358100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>22500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>139100</v>
+      </c>
+      <c r="E35" s="3">
         <v>169500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>147800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>140700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>103600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>223100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>143400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>129900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>81500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>96700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>82700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>56000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>83400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>204900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>199900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>130200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>51800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>198300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>76000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>86800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>28900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>169600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>105400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>358100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>22500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,728 +3091,756 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>495400</v>
+      </c>
+      <c r="E41" s="3">
         <v>526900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>420100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>380300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>395700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>634300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>722600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>636100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>702100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>458100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>424100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>240200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>823100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1055300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>819200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>726000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>508200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>504000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>413900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>605800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>284000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>422000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>164300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>118100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>171200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>201300</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>433700</v>
+      </c>
+      <c r="E42" s="3">
         <v>393600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>375600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>216300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>276400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>403600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>167700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>56300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>64300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>393700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>260000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>218000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>837500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>922000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>665600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>653600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>299700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>405200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>294700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>50300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>7000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>120900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>146700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>87400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>140900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>146900</v>
       </c>
     </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1047600</v>
+      </c>
+      <c r="E43" s="3">
         <v>938900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1020200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1001700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1073200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1083800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1020000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>952500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>915100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>829300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>816200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>958900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>898400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>955400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>875900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>867400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>843400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>948600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>956400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>849600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>835500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>923500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>785800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>661200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>670700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>648700</v>
       </c>
     </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>57500</v>
+      </c>
+      <c r="E44" s="3">
         <v>47500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>70200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>74900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>80700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>68400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>83200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>77700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>59500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>42400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>51400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>56100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>45700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>40900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>46600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>43700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>56300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>48300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>40300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>40100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>47900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>37500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>39600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>37800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>40200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>34300</v>
       </c>
     </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>111700</v>
+      </c>
+      <c r="E45" s="3">
         <v>95100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>105700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>110600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>112600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>111100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>103300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>102500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>91300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>139300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>174200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>279700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>192100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>134300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>132600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>170200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>172100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>131600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>164900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>101300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>108500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>57500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>121800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>152000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>206800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>91300</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2260900</v>
+      </c>
+      <c r="E46" s="3">
         <v>2047400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2066300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1872900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2060500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2350300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2169900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1924800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1955800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1862800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1725900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1752900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2796900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3107900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2539900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2460900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1879800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2037500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1870100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1647200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1283000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1561500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1258200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1056500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1229800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1122400</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>237200</v>
+      </c>
+      <c r="E47" s="3">
         <v>312700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>292800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>281000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>330100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>346300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>330900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>347400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>303100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>576000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>637900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>683700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>698500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>693400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>411600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>334300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>367500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>444200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>410400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>665000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>603700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>609100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>786100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>766800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>294700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4039500</v>
+      </c>
+      <c r="E48" s="3">
         <v>3705800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4145800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4085600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4545300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4641600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4553300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4811700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4629200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4072900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4268300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4739300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3963300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3695400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3515000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3373600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3450400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3542300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3380900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3415200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3190900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3253000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3129600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2907800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2970000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2096500</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2566900</v>
+      </c>
+      <c r="E49" s="3">
         <v>2384900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2720700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2717100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3059400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3197400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3135700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3304700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3204000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2950500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2946800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3155600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2179800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2136500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1459200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1444800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1650300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1766600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1755400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1826000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1703000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1785700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1846400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1791600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1947200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1998900</v>
       </c>
     </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,88 +4002,94 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>449200</v>
+      </c>
+      <c r="E52" s="3">
         <v>425800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>522500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>498500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>505200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>510200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>651400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>805600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>728200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>676000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>525300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>552700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>442800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>422300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>931700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>878600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>344500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>361100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>333500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>295600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>270900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>243100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>278500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>276200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>448900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>461900</v>
       </c>
     </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4168,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9847200</v>
+      </c>
+      <c r="E54" s="3">
         <v>9107200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10015400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9733200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10833300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11388400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11207800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11553300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11176600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10138300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10104100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10884200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10081300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10055500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8857300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8492200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7692600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8151800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7750300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7849100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7051500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7452400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7298800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6798900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6890500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5980300</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,488 +4315,507 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>790600</v>
+      </c>
+      <c r="E57" s="3">
         <v>806300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>671000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>657300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>780000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>950500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>771700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>757200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>762900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>761600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>766200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>818400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>618900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>659500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>534400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>501500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>497900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>612300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>423900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>407700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>470400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>724600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>548300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>512000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>707700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>809000</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>334200</v>
+      </c>
+      <c r="E58" s="3">
         <v>319800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>404800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>402400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>519900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>633900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>839000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>887000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>767500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>633000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>369800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>390000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>277400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>365000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>359000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>509600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>630200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>537000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>543200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>513900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>363300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>416900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>432400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>233000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>249900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>661600</v>
+      </c>
+      <c r="E59" s="3">
         <v>262000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>324000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>381700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>533300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>362800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>506000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>497600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>561400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>963100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>771900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>730500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>900400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1117300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>482200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>462100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>350500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>475400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>332200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>307800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>229800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>357800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>383300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>256100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>261700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>345900</v>
       </c>
     </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2569800</v>
+      </c>
+      <c r="E60" s="3">
         <v>2074000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2135000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2117900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2546700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2655000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2747000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2750300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2640200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2357700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1907900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1938900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1796700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2141800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1375500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1473300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1478600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1624700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1299200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1229400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1063500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1499300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1364000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1001100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1219300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1324000</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2420700</v>
+      </c>
+      <c r="E61" s="3">
         <v>2204300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2467900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2403200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2598700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2669200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2653700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2823500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2816500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2566500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2847800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3116100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2431100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2240600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2043100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1939900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1417100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1561600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1494800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1638000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1534300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1395000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1393500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1461300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1503800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>505100</v>
       </c>
     </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>495900</v>
+      </c>
+      <c r="E62" s="3">
         <v>468800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>536300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>516200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>575800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>573500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>559600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>593200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>610100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>649500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>674800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>752300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>643300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>605500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>475800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>475600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>407100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>428600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>427700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>479400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>421400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>415000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>459000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>451600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>440000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>446900</v>
       </c>
     </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5060,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5581800</v>
+      </c>
+      <c r="E66" s="3">
         <v>4838000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5244700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5144300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5843700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6026900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6087000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6300600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6196700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5573600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5430500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5807300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4871000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4987900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3894400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3888700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3302800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3614900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3221800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3346700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3019200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3309300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3216600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2914000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3163100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2276100</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5506,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1851800</v>
+      </c>
+      <c r="E72" s="3">
         <v>2030700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2235000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2098600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2227000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2506000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2347700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2371300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2237100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2079500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2119200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2311700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2368000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2277700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2179300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1930100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1803500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1831900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1835100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2161300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2204900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2251400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2160900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2071600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1811200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1788100</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +5838,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4265400</v>
+      </c>
+      <c r="E76" s="3">
         <v>4269200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4770700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4588900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4989600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5361600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5120900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5252700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4979900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4564700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4673600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5076900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5210200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5067600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4962900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4603400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4389800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4536900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4528500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4502400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4032300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4143200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4082200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3884900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3727500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3704200</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>139100</v>
+      </c>
+      <c r="E81" s="3">
         <v>169500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>147800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>140700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>103600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>223100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>143400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>129900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>81500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>96700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>82700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>56000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>83400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>204900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>199900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>130200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>51800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>198300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>76000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>86800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>28900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>169600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>105400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>358100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>22500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,88 +6208,92 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>254400</v>
+      </c>
+      <c r="E83" s="3">
         <v>261100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>253800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>283000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>255300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>135300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>260700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>233500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>205100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>334000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>347400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>338600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>287700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>289800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>282800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>275700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>267100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>269800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>270800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>543500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>251500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>195800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>269500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>229800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>249700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>190500</v>
       </c>
     </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6704,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>435300</v>
+      </c>
+      <c r="E89" s="3">
         <v>731000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>638700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>483900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>328100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>999300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>697700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>441300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>387000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>629400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>641600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>267500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>230200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>630400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>558400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>432300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>364700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>723800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>426300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>549100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>87000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>666100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>394600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>187500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>55400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>546400</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,88 +6820,92 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-233600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-222200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-164600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-166600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-270100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-266200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-199900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-192000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-254500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1375200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-977600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1049600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1328000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2157400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-896500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-175400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-247700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-286500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-165600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-310800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-161400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-246500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-173300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-167300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-121700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-256800</v>
       </c>
     </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,88 +7067,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-232400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-274500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-321000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-139800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-145900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-594600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-309200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-176900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>118300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-396300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-268300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-828100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-170900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-470600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-166300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-518500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-159800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-395400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-408500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-231700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-50600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-222900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-226400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-121600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-114600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-291500</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,88 +7183,92 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>116900</v>
+      </c>
+      <c r="E96" s="3">
         <v>221200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>14800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>112800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>128600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>86300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>57200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>169200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>129300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-47800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-49200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-38500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-97700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-42700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-59800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-9300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-91000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-108700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-5700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-112000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-101300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-67300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-64200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,88 +7513,94 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-275900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-299500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-285300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-321300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-400200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-514100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-279900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-365700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-306500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-187600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-200400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>30700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-311300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>74500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-328000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>286200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-178500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-240200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-202700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-161800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-160300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-183000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-129100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-109800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>29200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-175900</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7379,8 +7628,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7430,84 +7679,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-73000</v>
+      </c>
+      <c r="E102" s="3">
         <v>157100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>32400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>22800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-218000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-109400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>108500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-101200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>198800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>45500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>202700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-562000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-252000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>234300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>64100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>199900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>26400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>88200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-184800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>155600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-123900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>260200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>39200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-43900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-30000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>79000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TIMB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TIMB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>TIMB</t>
   </si>
@@ -656,378 +656,391 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1211300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1115100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1072100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1178800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1135300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1215300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1293200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1212500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1216000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1113900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1046800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1036700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1075900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>972100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>968700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>908700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>853300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>811900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>915500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>854600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1616400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>752500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>847100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>813600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>754800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>784200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>834100</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>566600</v>
+      </c>
+      <c r="E9" s="3">
         <v>531000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>495700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>543500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>525100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>581700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>600400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>568400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>608200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>555300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>658400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>668500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>697000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>611500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>563900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>546100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>522400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>499800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>414300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>399500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1122400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>350200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>307400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>366300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>329200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>366300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>367900</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>644700</v>
+      </c>
+      <c r="E10" s="3">
         <v>584100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>576500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>635300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>610200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>633700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>692800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>644100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>607800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>558600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>388500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>368200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>378900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>360600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>404800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>362500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>331000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>312100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>501200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>455100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>494000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>402400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>539800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>447200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>425600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>417900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>466200</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1057,8 +1070,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1140,8 +1154,11 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,174 +1240,183 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>200</v>
+      </c>
+      <c r="E14" s="3">
         <v>10300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>18500</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>16700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-36400</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>41200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>10000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>7000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>6700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>13900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>9400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>11700</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>38400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>11800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>10700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>17400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>40300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>16500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>203900</v>
+      </c>
+      <c r="E15" s="3">
         <v>191400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>172500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>208700</v>
       </c>
-      <c r="G15" s="3">
-        <v>178700</v>
-      </c>
       <c r="H15" s="3">
+        <v>193200</v>
+      </c>
+      <c r="I15" s="3">
         <v>209000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>194800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>213200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>205800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>177600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>32800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>34700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>37500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>40200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>41000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>42200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>40700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>41400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>43800</v>
       </c>
-      <c r="V15" s="3" t="s">
+      <c r="W15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>48900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>44300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>43900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>48900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>44800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>45900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1443,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>922100</v>
+      </c>
+      <c r="E17" s="3">
         <v>874800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>802800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>913300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>883600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>972300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>993600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>963500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>995800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>938400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>872300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>896000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>929100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>829200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>616500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>756600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>724900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>701100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>724800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>721600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1388200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>660600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>616100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>690200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>372700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>700300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>683600</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>289100</v>
+      </c>
+      <c r="E18" s="3">
         <v>240300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>269300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>265500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>251700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>243100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>299700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>249000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>220200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>175500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>174500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>140800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>146800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>142900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>352200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>152100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>128400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>110900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>190700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>133000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>228100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>92000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>231000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>123400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>382100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>84000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>150500</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,423 +1647,439 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E20" s="3">
         <v>45900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3700</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>32300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>22700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4900</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>4600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-20100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>20300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>36500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>29500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-47500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-56900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-9700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>179600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-6300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>478700</v>
+      </c>
+      <c r="E21" s="3">
         <v>385800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>438200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>470500</v>
       </c>
-      <c r="G21" s="3">
-        <v>430400</v>
-      </c>
       <c r="H21" s="3">
+        <v>444900</v>
+      </c>
+      <c r="I21" s="3">
         <v>419700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>471800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>458500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>421000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>353100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>513100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>491000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>465200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>438000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>662400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>440200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>440600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>373400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>490000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>356300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>714700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>333700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>427400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>388300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>791500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>327300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>344400</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>144800</v>
+      </c>
+      <c r="E22" s="3">
         <v>110400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>98300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>121300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>119100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>117200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>121600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>135000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>153700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>83200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>67500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>77100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>67900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>58300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>56700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>47900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>43500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>37600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>38200</v>
       </c>
-      <c r="V22" s="3" t="s">
+      <c r="W22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>45400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>35700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>44100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>45500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>40300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>42800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>215400</v>
+      </c>
+      <c r="E23" s="3">
         <v>121000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>184100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>178500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>166500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>117200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>247800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>162700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>127100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>109800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>111600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>66500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>58800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>91900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>315800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>109600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>121400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>68700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>182000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>85500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>125800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>46500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>187500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>73300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>521300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>34800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-18100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>30600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>25800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>13700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>24700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>19300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>28400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-16200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>110900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-90300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-8800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>16900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-16300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>9600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>39000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>17600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>17800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-32100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>163300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>12400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E26" s="3">
         <v>139100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>169500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>147800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>140700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>103600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>223100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>143400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>129900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>81500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>96700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>82700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>56000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>83400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>204900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>199900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>130200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>51800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>198300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>76000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>86800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>28900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>169600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>105400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>358100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>22500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E27" s="3">
         <v>139100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>169500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>147800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>140700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>103600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>223100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>143400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>129900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>81500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>96700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>82700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>56000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>83400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>204900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>199900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>130200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>51800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>198300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>76000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>86800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>28900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>169600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>105400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>358100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>22500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,174 +2677,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-45900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3700</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-32300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-22700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4900</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-4600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>20100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-20300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-36500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-29500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>47500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>56900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>9700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>4600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-179600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>6300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E33" s="3">
         <v>139100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>169500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>147800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>140700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>103600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>223100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>143400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>129900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>81500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>96700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>82700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>56000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>83400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>204900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>199900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>130200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>51800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>198300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>76000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>86800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>28900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>169600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>105400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>358100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>22500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E35" s="3">
         <v>139100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>169500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>147800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>140700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>103600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>223100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>143400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>129900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>81500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>96700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>82700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>56000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>83400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>204900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>199900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>130200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>51800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>198300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>76000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>86800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>28900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>169600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>105400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>358100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>22500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,755 +3178,783 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>549600</v>
+      </c>
+      <c r="E41" s="3">
         <v>495400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>526900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>420100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>380300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>395700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>634300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>722600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>636100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>702100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>458100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>424100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>240200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>823100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1055300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>819200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>726000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>508200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>504000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>413900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>605800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>284000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>422000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>164300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>118100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>171200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>201300</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>455000</v>
+      </c>
+      <c r="E42" s="3">
         <v>433700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>393600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>375600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>216300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>276400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>403600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>167700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>56300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>64300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>393700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>260000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>218000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>837500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>922000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>665600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>653600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>299700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>405200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>294700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>50300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>7000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>120900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>146700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>87400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>140900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>146900</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1165400</v>
+      </c>
+      <c r="E43" s="3">
         <v>1047600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>938900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1020200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1001700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1073200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1083800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1020000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>952500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>915100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>829300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>816200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>958900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>898400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>955400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>875900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>867400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>843400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>948600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>956400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>849600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>835500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>923500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>785800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>661200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>670700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>648700</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>65700</v>
+      </c>
+      <c r="E44" s="3">
         <v>57500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>47500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>70200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>74900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>80700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>68400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>83200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>77700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>59500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>42400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>51400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>56100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>45700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>40900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>46600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>43700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>56300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>48300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>40300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>40100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>47900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>37500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>39600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>37800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>40200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>34300</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>129300</v>
+      </c>
+      <c r="E45" s="3">
         <v>111700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>95100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>105700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>110600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>112600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>111100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>103300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>102500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>91300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>139300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>174200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>279700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>192100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>134300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>132600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>170200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>172100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>131600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>164900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>101300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>108500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>57500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>121800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>152000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>206800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>91300</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2469400</v>
+      </c>
+      <c r="E46" s="3">
         <v>2260900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2047400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2066300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1872900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2060500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2350300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2169900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1924800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1955800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1862800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1725900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1752900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2796900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3107900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2539900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2460900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1879800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2037500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1870100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1647200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1283000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1561500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1258200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1056500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1229800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1122400</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>237200</v>
+        <v>306500</v>
       </c>
       <c r="E47" s="3">
+        <v>285100</v>
+      </c>
+      <c r="F47" s="3">
         <v>312700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>292800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>281000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>330100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>346300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>330900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>347400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>303100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>576000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>637900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>683700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>698500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>693400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>411600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>334300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>367500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>444200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>410400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>665000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>603700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>609100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>786100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>766800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>294700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4285800</v>
+      </c>
+      <c r="E48" s="3">
         <v>4039500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3705800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4145800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4085600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4545300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4641600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4553300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4811700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4629200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4072900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4268300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4739300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3963300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3695400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3515000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3373600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3450400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3542300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3380900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3415200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3190900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3253000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3129600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2907800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2970000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2096500</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2666000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2566900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2384900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2720700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2717100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3059400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3197400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3135700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3304700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3204000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2950500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2946800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3155600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2179800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2136500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1459200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1444800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1650300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1766600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1755400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1826000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1703000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1785700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1846400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1791600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1947200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1998900</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,91 +4122,97 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>449200</v>
+        <v>431800</v>
       </c>
       <c r="E52" s="3">
+        <v>401300</v>
+      </c>
+      <c r="F52" s="3">
         <v>425800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>522500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>498500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>505200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>510200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>651400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>805600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>728200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>676000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>525300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>552700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>442800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>422300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>931700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>878600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>344500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>361100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>333500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>295600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>270900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>243100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>278500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>276200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>448900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>461900</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4294,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10452700</v>
+      </c>
+      <c r="E54" s="3">
         <v>9847200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9107200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10015400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9733200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10833300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11388400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11207800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11553300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11176600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10138300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10104100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10884200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10081300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10055500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8857300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8492200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7692600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8151800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7750300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7849100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7051500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7452400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7298800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6798900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6890500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5980300</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,506 +4446,525 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>830000</v>
+      </c>
+      <c r="E57" s="3">
         <v>790600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>806300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>671000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>657300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>780000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>950500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>771700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>757200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>762900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>761600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>766200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>818400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>618900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>659500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>534400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>501500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>497900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>612300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>423900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>407700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>470400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>724600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>548300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>512000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>707700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>809000</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>467700</v>
+      </c>
+      <c r="E58" s="3">
         <v>334200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>319800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>404800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>402400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>519900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>633900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>839000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>887000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>767500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>633000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>369800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>390000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>277400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>365000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>359000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>509600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>630200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>537000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>543200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>513900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>363300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>416900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>432400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>233000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>249900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>587700</v>
+      </c>
+      <c r="E59" s="3">
         <v>661600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>262000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>324000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>381700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>533300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>362800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>506000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>497600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>561400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>963100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>771900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>730500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>900400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1117300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>482200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>462100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>350500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>475400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>332200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>307800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>229800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>357800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>383300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>256100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>261700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>345900</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2726800</v>
+      </c>
+      <c r="E60" s="3">
         <v>2569800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2074000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2135000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2117900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2546700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2655000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2747000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2750300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2640200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2357700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1907900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1938900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1796700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2141800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1375500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1473300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1478600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1624700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1299200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1229400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1063500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1499300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1364000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1001100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1219300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1324000</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2509800</v>
+      </c>
+      <c r="E61" s="3">
         <v>2420700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2204300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2467900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2403200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2598700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2669200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2653700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2823500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2816500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2566500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2847800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3116100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2431100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2240600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2043100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1939900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1417100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1561600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1494800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1638000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1534300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1395000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1393500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1461300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1503800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>505100</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>507200</v>
+      </c>
+      <c r="E62" s="3">
         <v>495900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>468800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>536300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>516200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>575800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>573500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>559600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>593200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>610100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>649500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>674800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>752300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>643300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>605500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>475800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>475600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>407100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>428600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>427700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>479400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>421400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>415000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>459000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>451600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>440000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>446900</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,91 +5218,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5841500</v>
+      </c>
+      <c r="E66" s="3">
         <v>5581800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4838000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5244700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5144300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5843700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6026900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6087000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6300600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6196700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5573600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5430500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5807300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4871000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4987900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3894400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3888700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3302800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3614900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3221800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3346700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3019200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3309300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3216600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2914000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3163100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2276100</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,91 +5680,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2072500</v>
+      </c>
+      <c r="E72" s="3">
         <v>1851800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2030700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2235000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2098600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2227000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2506000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2347700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2371300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2237100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2079500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2119200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2311700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2368000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2277700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2179300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1930100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1803500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1831900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1835100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2161300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2204900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2251400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2160900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2071600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1811200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1788100</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,91 +6024,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4611200</v>
+      </c>
+      <c r="E76" s="3">
         <v>4265400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4269200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4770700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4588900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4989600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5361600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5120900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5252700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4979900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4564700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4673600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5076900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5210200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5067600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4962900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4603400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4389800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4536900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4528500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4502400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4032300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4143200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4082200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3884900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3727500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3704200</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E81" s="3">
         <v>139100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>169500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>147800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>140700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>103600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>223100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>143400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>129900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>81500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>96700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>82700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>56000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>83400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>204900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>199900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>130200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>51800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>198300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>76000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>86800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>28900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>169600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>105400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>358100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>22500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,91 +6407,95 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>229400</v>
+      </c>
+      <c r="E83" s="3">
         <v>254400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>261100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>253800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>283000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>255300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>135300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>260700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>233500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>205100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>334000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>347400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>338600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>287700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>289800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>282800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>275700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>267100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>269800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>270800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>543500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>251500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>195800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>269500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>229800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>249700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>190500</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6921,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>545200</v>
+      </c>
+      <c r="E89" s="3">
         <v>435300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>731000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>638700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>483900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>328100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>999300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>697700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>441300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>387000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>629400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>641600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>267500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>230200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>630400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>558400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>432300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>364700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>723800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>426300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>549100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>87000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>666100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>394600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>187500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>55400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>546400</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,91 +7041,95 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-161900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-233600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-222200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-164600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-166600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-270100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-266200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-199900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-192000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-254500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1375200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-977600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1049600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1328000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2157400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-896500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-175400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-247700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-286500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-165600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-310800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-161400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-246500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-173300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-167300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-121700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-256800</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,91 +7297,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-146900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-232400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-274500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-321000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-139800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-145900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-594600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-309200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-176900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>118300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-396300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-268300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-828100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-170900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-470600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-166300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-518500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-159800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-395400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-408500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-231700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-50600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-222900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-226400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-121600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-114600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-291500</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,91 +7417,95 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>175500</v>
+      </c>
+      <c r="E96" s="3">
         <v>116900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>221200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>14800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>112800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>128600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>86300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>57200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>169200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>129300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-47800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-49200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-38500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-97700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-42700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-59800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-9300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-91000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-108700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-5700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-112000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-101300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-67300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-64200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,91 +7759,97 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-370000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-275900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-299500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-285300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-321300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-400200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-514100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-279900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-365700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-306500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-187600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-200400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>30700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-311300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>74500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-328000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>286200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-178500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-240200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-202700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-161800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-160300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-183000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-129100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-109800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>29200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-175900</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7631,8 +7880,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7682,87 +7931,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-73000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>157100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>32400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>22800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-218000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-109400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>108500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-101200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>198800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>45500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>202700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-562000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-252000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>234300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>64100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>199900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>26400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>88200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-184800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>155600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-123900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>260200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>39200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-43900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-30000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>79000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TIMB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TIMB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>TIMB</t>
   </si>
@@ -656,404 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1256400</v>
+      </c>
+      <c r="E8" s="3">
         <v>1259200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1211300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1115100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1072100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1178800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1135300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1215300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1293200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1212500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1216000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1113900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1046800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1036700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1075900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>972100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>968700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>908700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>853300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>811900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>915500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>854600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1616400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>752500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>847100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>813600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>754800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>784200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>834100</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>557300</v>
+      </c>
+      <c r="E9" s="3">
         <v>567700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>566600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>531000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>495700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>543500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>525100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>581700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>600400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>568400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>608200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>555300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>658400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>668500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>697000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>611500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>563900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>546100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>522400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>499800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>414300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>399500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1122400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>350200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>307400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>366300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>329200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>366300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>367900</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>699000</v>
+      </c>
+      <c r="E10" s="3">
         <v>691500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>644700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>584100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>576500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>635300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>610200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>633700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>692800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>644100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>607800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>558600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>388500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>368200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>378900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>360600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>404800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>362500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>331000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>312100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>501200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>455100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>494000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>402400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>539800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>447200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>425600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>417900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>466200</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1085,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1174,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,186 +1279,195 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>200</v>
+        <v>23700</v>
       </c>
       <c r="E14" s="3">
         <v>200</v>
       </c>
       <c r="F14" s="3">
+        <v>200</v>
+      </c>
+      <c r="G14" s="3">
         <v>10300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>18500</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>16700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-36400</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>41200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>6700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>4600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>10000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>7000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>6700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>13900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>9400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>11700</v>
       </c>
-      <c r="X14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>38400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>11800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>10700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>17400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>40300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>16500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>197900</v>
+      </c>
+      <c r="E15" s="3">
         <v>208200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>203900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>191400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>172500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>208700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>193200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>209000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>194800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>213200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>205800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>177600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>32800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>34700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>37500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>40200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>41000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>42200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>40700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>41400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>43800</v>
       </c>
-      <c r="X15" s="3" t="s">
+      <c r="Y15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>48900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>44300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>43900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>48900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>44800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>45900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>910300</v>
+      </c>
+      <c r="E17" s="3">
         <v>941800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>922100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>874800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>802800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>913300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>883600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>972300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>993600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>963500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>995800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>938400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>872300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>896000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>929100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>829200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>616500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>756600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>724900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>701100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>724800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>721600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1388200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>660600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>616100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>690200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>372700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>700300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>683600</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>346100</v>
+      </c>
+      <c r="E18" s="3">
         <v>317500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>289100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>240300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>269300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>265500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>251700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>243100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>299700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>249000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>220200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>175500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>174500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>140800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>146800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>142900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>352200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>152100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>128400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>110900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>190700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>133000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>228100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>92000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>231000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>123400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>382100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>84000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>150500</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,453 +1714,469 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E20" s="3">
         <v>4800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>14300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>45900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2700</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>32300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>22700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4900</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>4600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-20100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>7400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>20300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>5400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>36500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>29500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-47500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-56900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-9700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>179600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-6300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>548400</v>
+      </c>
+      <c r="E21" s="3">
         <v>520900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>478700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>385800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>438200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>471500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>444900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>419700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>471800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>458500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>421000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>353100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>513100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>491000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>465200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>438000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>662400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>440200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>440600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>373400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>490000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>356300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>714700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>333700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>427400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>388300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>791500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>327300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>344400</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>122300</v>
+      </c>
+      <c r="E22" s="3">
         <v>165900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>144800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>110400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>98300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>128600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>119100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>117200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>121600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>135000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>153700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>83200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>67500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>77100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>67900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>58300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>56700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>47900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>43500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>37600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>38200</v>
       </c>
-      <c r="X22" s="3" t="s">
+      <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>45400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>35700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>44100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>45500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>40300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>42800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>267200</v>
+      </c>
+      <c r="E23" s="3">
         <v>229000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>215400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>121000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>184100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>178500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>166500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>117200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>247800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>162700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>127100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>109800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>111600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>66500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>58800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>91900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>315800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>109600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>121400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>68700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>182000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>85500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>125800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>46500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>187500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>73300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>521300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>34800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E24" s="3">
         <v>2400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>36400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-18100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>14600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>30600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>25800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>13700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>24700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>19300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>28400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>14900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-16200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>110900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-90300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-8800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>16900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-16300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>9600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>39000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>17600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>17800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-32100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>163300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>12400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>241700</v>
+      </c>
+      <c r="E26" s="3">
         <v>226600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>179000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>139100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>169500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>147800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>140700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>103600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>223100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>143400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>129900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>81500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>96700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>82700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>56000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>83400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>204900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>199900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>130200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>51800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>198300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>76000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>86800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>28900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>169600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>105400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>358100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>22500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>241700</v>
+      </c>
+      <c r="E27" s="3">
         <v>226600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>179000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>139100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>169500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>147800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>140700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>103600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>223100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>143400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>129900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>81500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>96700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>82700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>56000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>83400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>204900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>199900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>130200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>51800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>198300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>76000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>86800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>28900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>169600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>105400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>358100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>22500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2572,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,186 +2816,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-14300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-45900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2700</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-32300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-22700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4900</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-4600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>20100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-7400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-20300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-5400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-36500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-29500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>47500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>56900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>9700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>4600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-179600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>6300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>241700</v>
+      </c>
+      <c r="E33" s="3">
         <v>226600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>179000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>139100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>169500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>147800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>140700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>103600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>223100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>143400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>129900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>81500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>96700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>82700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>56000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>83400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>204900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>199900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>130200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>51800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>198300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>76000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>86800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>28900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>169600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>105400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>358100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>22500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>241700</v>
+      </c>
+      <c r="E35" s="3">
         <v>226600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>179000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>139100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>169500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>147800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>140700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>103600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>223100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>143400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>129900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>81500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>96700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>82700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>56000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>83400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>204900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>199900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>130200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>51800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>198300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>76000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>86800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>28900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>169600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>105400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>358100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>22500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,809 +3351,837 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>655500</v>
+      </c>
+      <c r="E41" s="3">
         <v>689300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>549600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>495400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>526900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>420100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>380300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>395700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>634300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>722600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>636100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>702100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>458100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>424100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>240200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>823100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1055300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>819200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>726000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>508200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>504000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>413900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>605800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>284000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>422000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>164300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>118100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>171200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>201300</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>412900</v>
+      </c>
+      <c r="E42" s="3">
         <v>535700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>455000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>433700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>393600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>375600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>216300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>276400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>403600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>167700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>56300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>64300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>393700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>260000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>218000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>837500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>922000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>665600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>653600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>299700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>405200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>294700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>50300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>7000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>120900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>146700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>87400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>140900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>146900</v>
       </c>
     </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1115400</v>
+      </c>
+      <c r="E43" s="3">
         <v>1140100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1165400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1047600</v>
       </c>
-      <c r="G43" s="3">
-        <v>938900</v>
-      </c>
       <c r="H43" s="3">
+        <v>932800</v>
+      </c>
+      <c r="I43" s="3">
         <v>1020200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1001700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1073200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1083800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1020000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>952500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>915100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>829300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>816200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>958900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>898400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>955400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>875900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>867400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>843400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>948600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>956400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>849600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>835500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>923500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>785800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>661200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>670700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>648700</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>64900</v>
+      </c>
+      <c r="E44" s="3">
         <v>66300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>65700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>57500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>47500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>70200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>74900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>80700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>68400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>83200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>77700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>59500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>42400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>51400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>56100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>45700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>40900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>46600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>43700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>56300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>48300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>40300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>40100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>47900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>37500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>39600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>37800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>40200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>34300</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>136100</v>
+      </c>
+      <c r="E45" s="3">
         <v>128300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>129300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>111700</v>
       </c>
-      <c r="G45" s="3">
-        <v>95100</v>
-      </c>
       <c r="H45" s="3">
+        <v>101300</v>
+      </c>
+      <c r="I45" s="3">
         <v>105700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>110600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>112600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>111100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>103300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>102500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>91300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>139300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>174200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>279700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>192100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>134300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>132600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>170200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>172100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>131600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>164900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>101300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>108500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>57500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>121800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>152000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>206800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>91300</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2444500</v>
+      </c>
+      <c r="E46" s="3">
         <v>2643100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2469400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2260900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2047400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2066300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1872900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2060500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2350300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2169900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1924800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1955800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1862800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1725900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1752900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2796900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3107900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2539900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2460900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1879800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2037500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1870100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1647200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1283000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1561500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1258200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1056500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1229800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1122400</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>295100</v>
+      </c>
+      <c r="E47" s="3">
         <v>306700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>306500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>285100</v>
       </c>
-      <c r="G47" s="3">
-        <v>312700</v>
-      </c>
       <c r="H47" s="3">
+        <v>258000</v>
+      </c>
+      <c r="I47" s="3">
         <v>292800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>281000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>330100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>346300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>330900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>347400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>303100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>576000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>637900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>683700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>698500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>693400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>411600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>334300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>367500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>444200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>410400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>665000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>603700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>609100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>786100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>766800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>294700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4225000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4355000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4285800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4039500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3705800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4145800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4085600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4545300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4641600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4553300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4811700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4629200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4072900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4268300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4739300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3963300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3695400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3515000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3373600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3450400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3542300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3380900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3415200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3190900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3253000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3129600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2907800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2970000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2096500</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2631200</v>
+      </c>
+      <c r="E49" s="3">
         <v>2704500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2666000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2566900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2384900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2720700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2717100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3059400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3197400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3135700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3304700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3204000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2950500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2946800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3155600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2179800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2136500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1459200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1444800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1650300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1766600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1755400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1826000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1703000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1785700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1846400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1791600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1947200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1998900</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,97 +4361,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>434300</v>
+      </c>
+      <c r="E52" s="3">
         <v>444300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>431800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>401300</v>
       </c>
-      <c r="G52" s="3">
-        <v>425800</v>
-      </c>
       <c r="H52" s="3">
+        <v>480500</v>
+      </c>
+      <c r="I52" s="3">
         <v>522500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>498500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>505200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>510200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>651400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>805600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>728200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>676000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>525300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>552700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>442800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>422300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>931700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>878600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>344500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>361100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>333500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>295600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>270900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>243100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>278500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>276200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>448900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>461900</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10337500</v>
+      </c>
+      <c r="E54" s="3">
         <v>10765100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10452700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9847200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9107200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10015400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9733200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10833300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11388400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11207800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11553300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11176600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10138300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10104100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10884200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10081300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10055500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8857300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8492200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7692600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>8151800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7750300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7849100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7051500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7452400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7298800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6798900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6890500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5980300</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,542 +4707,561 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>933000</v>
+      </c>
+      <c r="E57" s="3">
         <v>792100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>830000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>790600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>806300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>671000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>657300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>780000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>950500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>771700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>757200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>762900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>761600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>766200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>818400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>618900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>659500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>534400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>501500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>497900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>612300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>423900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>407700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>470400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>724600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>548300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>512000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>707700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>809000</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>477200</v>
+      </c>
+      <c r="E58" s="3">
         <v>480500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>467700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>334200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>319800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>404800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>402400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>519900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>633900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>839000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>887000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>767500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>633000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>369800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>390000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>277400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>365000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>359000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>509600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>630200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>537000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>543200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>513900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>363300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>416900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>432400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>233000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>249900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>402500</v>
+      </c>
+      <c r="E59" s="3">
         <v>544900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>587700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>661600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>262000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>324000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>381700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>533300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>362800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>506000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>497600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>561400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>963100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>771900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>730500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>900400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1117300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>482200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>462100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>350500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>475400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>332200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>307800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>229800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>357800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>383300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>256100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>261700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>345900</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2759800</v>
+      </c>
+      <c r="E60" s="3">
         <v>2754300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2726800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2569800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2074000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2135000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2117900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2546700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2655000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2747000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2750300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2640200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2357700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1907900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1938900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1796700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2141800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1375500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1473300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1478600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1624700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1299200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1229400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1063500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1499300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1364000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1001100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1219300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1324000</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2526300</v>
+      </c>
+      <c r="E61" s="3">
         <v>2589300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2509800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2420700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2204300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2467900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2403200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2598700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2669200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2653700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2823500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2816500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2566500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2847800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3116100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2431100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2240600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2043100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1939900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1417100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1561600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1494800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1638000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1534300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1395000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1393500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1461300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1503800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>505100</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>605500</v>
+      </c>
+      <c r="E62" s="3">
         <v>593400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>507200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>495900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>468800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>536300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>516200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>575800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>573500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>559600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>593200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>610100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>649500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>674800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>752300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>643300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>605500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>475800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>475600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>407100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>428600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>427700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>479400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>421400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>415000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>459000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>451600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>440000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>446900</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5984300</v>
+      </c>
+      <c r="E66" s="3">
         <v>6034100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5841500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5581800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4838000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5244700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5144300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5843700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6026900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6087000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6300600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6196700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5573600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5430500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5807300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4871000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4987900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3894400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3888700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3302800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3614900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3221800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3346700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3019200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3309300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3216600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2914000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3163100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2276100</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5768,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1850500</v>
+      </c>
+      <c r="E72" s="3">
         <v>2194800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2072500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1851800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2030700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2235000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2098600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2227000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2506000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2347700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2371300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2237100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2079500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2119200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2311700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2368000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2277700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2179300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1930100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1803500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1831900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1835100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2161300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2204900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2251400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2160900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2071600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1811200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1788100</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4353200</v>
+      </c>
+      <c r="E76" s="3">
         <v>4731000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4611200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4265400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4269200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4770700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4588900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4989600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5361600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5120900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5252700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4979900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4564700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4673600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5076900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5210200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5067600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4962900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4603400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4389800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4536900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4528500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4502400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4032300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4143200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4082200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3884900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3727500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3704200</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>241700</v>
+      </c>
+      <c r="E81" s="3">
         <v>226600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>179000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>139100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>169500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>147800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>140700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>103600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>223100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>143400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>129900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>81500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>96700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>82700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>56000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>83400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>204900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>199900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>130200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>51800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>198300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>76000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>86800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>28900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>169600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>105400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>358100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>22500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,97 +6804,101 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>201700</v>
+      </c>
+      <c r="E83" s="3">
         <v>241100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>229400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>254400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>261100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>253800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>283000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>255300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>135300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>260700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>233500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>205100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>334000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>347400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>338600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>287700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>289800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>282800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>275700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>267100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>269800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>270800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>543500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>251500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>195800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>269500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>229800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>249700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>190500</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>775300</v>
+      </c>
+      <c r="E89" s="3">
         <v>694800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>545200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>435300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>731000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>638700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>483900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>328100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>999300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>697700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>441300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>387000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>629400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>641600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>267500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>230200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>630400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>558400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>432300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>364700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>723800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>426300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>549100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>87000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>666100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>394600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>187500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>55400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>546400</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,97 +7482,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-244500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-182700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-161900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-233600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-222200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-164600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-166600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-270100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-266200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-199900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-192000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-254500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1375200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-977600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1049600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1328000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2157400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-896500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-175400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-247700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-286500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-165600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-310800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-161400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-246500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-173300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-167300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-121700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-256800</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,97 +7756,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-233300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-146900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-232400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-274500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-321000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-139800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-145900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-594600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-309200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-176900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>118300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-396300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-268300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-828100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-170900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-470600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-166300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-518500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-159800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-395400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-408500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-231700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-50600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-222900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-226400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-121600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-114600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-291500</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,97 +7884,101 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>658200</v>
+      </c>
+      <c r="E96" s="3">
         <v>20300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>175500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>116900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>221200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>14800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>112800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>128600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>86300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>57200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>169200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>129300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-47800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-49200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-38500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-97700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-42700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-59800</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-9300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-91000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-108700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-112000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-101300</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-67300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-11800</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-64200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,97 +8250,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-753400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-334100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-370000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-275900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-299500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-285300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-321300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-400200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-514100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-279900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-365700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-306500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-187600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-200400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>30700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-311300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>74500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-328000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>286200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-178500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-240200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-202700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-161800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-160300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-183000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-129100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-109800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>29200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-175900</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8135,8 +8383,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -8186,93 +8434,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E102" s="3">
         <v>127400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>28300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-73000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>157100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>32400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>22800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-218000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-109400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>108500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-101200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>198800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>45500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>202700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-562000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-252000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>234300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>64100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>199900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>26400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>88200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-184800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>155600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-123900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>260200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>39200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-43900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-30000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>79000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TIMB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TIMB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
   <si>
     <t>TIMB</t>
   </si>
@@ -656,416 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1304700</v>
+      </c>
+      <c r="E8" s="3">
         <v>1256400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1259200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1211300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1115100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1072100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1178800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1135300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1215300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1293200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1212500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1216000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1113900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1046800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1036700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1075900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>972100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>968700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>908700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>853300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>811900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>915500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>854600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1616400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>752500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>847100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>813600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>754800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>784200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>834100</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>621500</v>
+      </c>
+      <c r="E9" s="3">
         <v>557300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>567700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>566600</v>
       </c>
-      <c r="G9" s="3">
-        <v>531000</v>
-      </c>
       <c r="H9" s="3">
+        <v>537900</v>
+      </c>
+      <c r="I9" s="3">
         <v>495700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>543500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>525100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>581700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>600400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>568400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>608200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>555300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>658400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>668500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>697000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>611500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>563900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>546100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>522400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>499800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>414300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>399500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1122400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>350200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>307400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>366300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>329200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>366300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>367900</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>683200</v>
+      </c>
+      <c r="E10" s="3">
         <v>699000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>691500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>644700</v>
       </c>
-      <c r="G10" s="3">
-        <v>584100</v>
-      </c>
       <c r="H10" s="3">
+        <v>577200</v>
+      </c>
+      <c r="I10" s="3">
         <v>576500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>635300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>610200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>633700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>692800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>644100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>607800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>558600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>388500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>368200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>378900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>360600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>404800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>362500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>331000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>312100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>501200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>455100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>494000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>402400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>539800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>447200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>425600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>417900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>466200</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,192 +1299,201 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E14" s="3">
         <v>23700</v>
-      </c>
-      <c r="E14" s="3">
-        <v>200</v>
       </c>
       <c r="F14" s="3">
         <v>200</v>
       </c>
       <c r="G14" s="3">
+        <v>200</v>
+      </c>
+      <c r="H14" s="3">
         <v>10300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>18500</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>16700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-36400</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>41200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>6900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>6700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>4600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>10000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>7000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>6700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>13900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>9400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>11700</v>
       </c>
-      <c r="Y14" s="3" t="s">
+      <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>38400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>11800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>10700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>17400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>40300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>16500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>197200</v>
+      </c>
+      <c r="E15" s="3">
         <v>197900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>208200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>203900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>191400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>172500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>208700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>193200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>209000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>194800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>213200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>205800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>177600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>32800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>34700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>37500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>40200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>41000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>42200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>40700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>41400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>43800</v>
       </c>
-      <c r="Y15" s="3" t="s">
+      <c r="Z15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>48900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>44300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>43900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>48900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>44800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>45900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>987500</v>
+      </c>
+      <c r="E17" s="3">
         <v>910300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>941800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>922100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>874800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>802800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>913300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>883600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>972300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>993600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>963500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>995800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>938400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>872300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>896000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>929100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>829200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>616500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>756600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>724900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>701100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>724800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>721600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1388200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>660600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>616100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>690200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>372700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>700300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>683600</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>317100</v>
+      </c>
+      <c r="E18" s="3">
         <v>346100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>317500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>289100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>240300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>269300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>265500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>251700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>243100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>299700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>249000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>220200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>175500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>174500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>140800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>146800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>142900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>352200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>152100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>128400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>110900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>190700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>133000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>228100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>92000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>231000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>123400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>382100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>84000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>150500</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,468 +1748,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>14300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>45900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2700</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>32300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>22700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4900</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>4600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-20100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>7400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>20300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>5400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>36500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-4600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>29500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-47500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-56900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>179600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-6300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>484000</v>
+      </c>
+      <c r="E21" s="3">
         <v>548400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>520900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>478700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>385800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>438200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>471500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>444900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>419700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>471800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>458500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>421000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>353100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>513100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>491000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>465200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>438000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>662400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>440200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>440600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>373400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>490000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>356300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>714700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>333700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>427400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>388300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>791500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>327300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>344400</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>137400</v>
+      </c>
+      <c r="E22" s="3">
         <v>122300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>165900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>144800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>110400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>98300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>128600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>119100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>117200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>121600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>135000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>153700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>83200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>67500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>77100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>67900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>58300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>56700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>47900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>43500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>37600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>38200</v>
       </c>
-      <c r="Y22" s="3" t="s">
+      <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>45400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>35700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>44100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>45500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>40300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>42800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>188800</v>
+      </c>
+      <c r="E23" s="3">
         <v>267200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>229000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>215400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>121000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>184100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>178500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>166500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>117200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>247800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>162700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>127100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>109800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>111600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>66500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>58800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>91900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>315800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>109600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>121400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>68700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>182000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>85500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>125800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>46500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>187500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>73300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>521300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>34800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E24" s="3">
         <v>25500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>36400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-18100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>14600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>30600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>25800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>13700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>24700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>19300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>28400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>14900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-16200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>8500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>110900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-90300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-8800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>16900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-16300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>9600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>39000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>17600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>17800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-32100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>163300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>12400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>156600</v>
+      </c>
+      <c r="E26" s="3">
         <v>241700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>226600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>179000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>139100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>169500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>147800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>140700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>103600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>223100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>143400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>129900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>81500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>96700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>82700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>56000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>83400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>204900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>199900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>130200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>51800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>198300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>76000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>86800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>28900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>169600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>105400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>358100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>22500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>156600</v>
+      </c>
+      <c r="E27" s="3">
         <v>241700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>226600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>179000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>139100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>169500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>147800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>140700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>103600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>223100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>143400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>129900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>81500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>96700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>82700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>56000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>83400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>204900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>199900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>130200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>51800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>198300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>76000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>86800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>28900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>169600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>105400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>358100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>22500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2886,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-30300</v>
+      </c>
+      <c r="E32" s="3">
         <v>4400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-14300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-45900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2700</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-32300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-22700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4900</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>20100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-7400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-20300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-5400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-36500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>4600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-29500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>47500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>56900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>9700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>4600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-179600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>6300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>156600</v>
+      </c>
+      <c r="E33" s="3">
         <v>241700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>226600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>179000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>139100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>169500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>147800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>140700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>103600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>223100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>143400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>129900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>81500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>96700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>82700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>56000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>83400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>204900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>199900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>130200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>51800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>198300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>76000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>86800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>28900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>169600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>105400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>358100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>22500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>156600</v>
+      </c>
+      <c r="E35" s="3">
         <v>241700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>226600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>179000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>139100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>169500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>147800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>140700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>103600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>223100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>143400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>129900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>81500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>96700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>82700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>56000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>83400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>204900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>199900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>130200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>51800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>198300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>76000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>86800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>28900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>169600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>105400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>358100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>22500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,836 +3438,864 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>770900</v>
+      </c>
+      <c r="E41" s="3">
         <v>655500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>689300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>549600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>495400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>526900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>420100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>380300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>395700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>634300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>722600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>636100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>702100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>458100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>424100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>240200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>823100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1055300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>819200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>726000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>508200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>504000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>413900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>605800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>284000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>422000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>164300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>118100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>171200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>201300</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>354500</v>
+      </c>
+      <c r="E42" s="3">
         <v>412900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>535700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>455000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>433700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>393600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>375600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>216300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>276400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>403600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>167700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>56300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>64300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>393700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>260000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>218000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>837500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>922000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>665600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>653600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>299700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>405200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>294700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>50300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>7000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>120900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>146700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>87400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>140900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>146900</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1219500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1115400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1140100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1165400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1047600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>932800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1020200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1001700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1073200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1083800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1020000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>952500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>915100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>829300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>816200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>958900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>898400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>955400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>875900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>867400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>843400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>948600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>956400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>849600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>835500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>923500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>785800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>661200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>670700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>648700</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>74300</v>
+      </c>
+      <c r="E44" s="3">
         <v>64900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>66300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>65700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>57500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>47500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>70200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>74900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>80700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>68400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>83200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>77700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>59500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>42400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>51400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>56100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>45700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>40900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>46600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>43700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>56300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>48300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>40300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>40100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>47900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>37500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>39600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>37800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>40200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>34300</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>137800</v>
+      </c>
+      <c r="E45" s="3">
         <v>136100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>128300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>129300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>111700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>101300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>105700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>110600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>112600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>111100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>103300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>102500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>91300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>139300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>174200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>279700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>192100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>134300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>132600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>170200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>172100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>131600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>164900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>101300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>108500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>57500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>121800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>152000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>206800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>91300</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2700200</v>
+      </c>
+      <c r="E46" s="3">
         <v>2444500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2643100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2469400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2260900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2047400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2066300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1872900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2060500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2350300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2169900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1924800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1955800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1862800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1725900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1752900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2796900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3107900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2539900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2460900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1879800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2037500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1870100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1647200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1283000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1561500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1258200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1056500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1229800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1122400</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>305600</v>
+      </c>
+      <c r="E47" s="3">
         <v>295100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>306700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>306500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>285100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>258000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>292800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>281000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>330100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>346300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>330900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>347400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>303100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>576000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>637900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>683700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>698500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>693400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>411600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>334300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>367500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>444200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>410400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>665000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>603700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>609100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>786100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>766800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>294700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4474700</v>
+      </c>
+      <c r="E48" s="3">
         <v>4225000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4355000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4285800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4039500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3705800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4145800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4085600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4545300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4641600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4553300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4811700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4629200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4072900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4268300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4739300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3963300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3695400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3515000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3373600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3450400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3542300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3380900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3415200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3190900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3253000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3129600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2907800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2970000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2096500</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2808300</v>
+      </c>
+      <c r="E49" s="3">
         <v>2631200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2704500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2666000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2566900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2384900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2720700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2717100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3059400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3197400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3135700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3304700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3204000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2950500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2946800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3155600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2179800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2136500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1459200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1444800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1650300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1766600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1755400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1826000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1703000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1785700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1846400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1791600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1947200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1998900</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4481,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>462800</v>
+      </c>
+      <c r="E52" s="3">
         <v>434300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>444300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>431800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>401300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>480500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>522500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>498500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>505200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>510200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>651400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>805600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>728200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>676000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>525300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>552700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>442800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>422300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>931700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>878600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>344500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>361100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>333500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>295600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>270900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>243100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>278500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>276200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>448900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>461900</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11079000</v>
+      </c>
+      <c r="E54" s="3">
         <v>10337500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10765100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10452700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9847200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9107200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10015400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9733200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10833300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11388400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11207800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11553300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11176600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10138300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10104100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10884200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10081300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10055500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8857300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>8492200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7692600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>8151800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7750300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7849100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7051500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7452400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7298800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6798900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6890500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5980300</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4838,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>992800</v>
+      </c>
+      <c r="E57" s="3">
         <v>933000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>792100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>830000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>790600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>806300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>671000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>657300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>780000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>950500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>771700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>757200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>762900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>761600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>766200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>818400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>618900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>659500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>534400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>501500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>497900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>612300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>423900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>407700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>470400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>724600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>548300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>512000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>707700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>809000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>502900</v>
+      </c>
+      <c r="E58" s="3">
         <v>477200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>480500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>467700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>334200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>319800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>404800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>402400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>519900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>633900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>839000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>887000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>767500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>633000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>369800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>390000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>277400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>365000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>359000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>509600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>630200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>537000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>543200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>513900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>363300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>416900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>432400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>233000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>249900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>401500</v>
+      </c>
+      <c r="E59" s="3">
         <v>402500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>544900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>587700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>661600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>262000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>324000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>381700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>533300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>362800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>506000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>497600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>561400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>963100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>771900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>730500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>900400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1117300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>482200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>462100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>350500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>475400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>332200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>307800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>229800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>357800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>383300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>256100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>261700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>345900</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2948400</v>
+      </c>
+      <c r="E60" s="3">
         <v>2759800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2754300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2726800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2569800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2074000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2135000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2117900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2546700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2655000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2747000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2750300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2640200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2357700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1907900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1938900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1796700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2141800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1375500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1473300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1478600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1624700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1299200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1229400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1063500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1499300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1364000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1001100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1219300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1324000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2706000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2526300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2589300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2509800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2420700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2204300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2467900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2403200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2598700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2669200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2653700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2823500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2816500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2566500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2847800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3116100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2431100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2240600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2043100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1939900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1417100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1561600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1494800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1638000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1534300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1395000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1393500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1461300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1503800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>505100</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>663600</v>
+      </c>
+      <c r="E62" s="3">
         <v>605500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>593400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>507200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>495900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>468800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>536300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>516200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>575800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>573500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>559600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>593200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>610100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>649500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>674800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>752300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>643300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>605500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>475800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>475600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>407100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>428600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>427700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>479400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>421400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>415000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>459000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>451600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>440000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>446900</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5691,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6397900</v>
+      </c>
+      <c r="E66" s="3">
         <v>5984300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6034100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5841500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5581800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4838000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5244700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5144300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5843700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6026900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6087000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6300600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6196700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5573600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5430500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5807300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4871000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4987900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3894400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3888700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3302800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3614900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3221800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3346700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3019200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3309300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3216600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2914000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3163100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2276100</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6201,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2037800</v>
+      </c>
+      <c r="E72" s="3">
         <v>1850500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2194800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2072500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1851800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2030700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2235000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2098600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2227000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2506000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2347700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2371300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2237100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2079500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2119200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2311700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2368000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2277700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2179300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1930100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1803500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1831900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1835100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2161300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2204900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2251400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2160900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2071600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1811200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1788100</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4681100</v>
+      </c>
+      <c r="E76" s="3">
         <v>4353200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4731000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4611200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4265400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4269200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4770700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4588900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4989600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5361600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5120900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5252700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4979900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4564700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4673600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5076900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5210200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5067600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4962900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4603400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4389800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4536900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4528500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4502400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4032300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4143200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4082200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3884900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3727500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3704200</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>156600</v>
+      </c>
+      <c r="E81" s="3">
         <v>241700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>226600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>179000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>139100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>169500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>147800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>140700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>103600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>223100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>143400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>129900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>81500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>96700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>82700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>56000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>83400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>204900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>199900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>130200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>51800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>198300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>76000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>86800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>28900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>169600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>105400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>358100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>22500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7003,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>220900</v>
+      </c>
+      <c r="E83" s="3">
         <v>201700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>241100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>229400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>254400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>261100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>253800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>283000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>255300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>135300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>260700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>233500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>205100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>334000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>347400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>338600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>287700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>289800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>282800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>275700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>267100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>269800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>270800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>543500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>251500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>195800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>269500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>229800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>249700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>190500</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>511100</v>
+      </c>
+      <c r="E89" s="3">
         <v>775300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>694800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>545200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>435300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>731000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>638700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>483900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>328100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>999300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>697700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>441300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>387000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>629400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>641600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>267500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>230200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>630400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>558400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>432300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>364700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>723800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>426300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>549100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>87000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>666100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>394600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>187500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>55400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>546400</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7703,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-259500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-244500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-182700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-161900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-233600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-222200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-164600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-166600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-270100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-266200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-199900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-192000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-254500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1375200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-977600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1049600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1328000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2157400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-896500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-175400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-247700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-286500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-165600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-310800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-161400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-246500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-173300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-167300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-121700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-256800</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7986,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-173400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-33400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-233300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-146900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-232400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-274500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-321000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-139800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-145900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-594600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-309200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-176900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>118300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-396300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-268300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-828100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-170900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-470600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-166300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-518500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-159800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-395400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-408500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-231700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-50600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-222900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-226400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-121600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-114600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-291500</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,100 +8118,104 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>91700</v>
+      </c>
+      <c r="E96" s="3">
         <v>658200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>20300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>175500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>116900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>221200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>14800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>112800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>128600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>86300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>57200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>169200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>129300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-47800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-49200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-38500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-97700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-42700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-59800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-9300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-91000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-108700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-112000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-101300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-67300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-11800</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-64200</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,100 +8496,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-258800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-753400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-334100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-370000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-275900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-299500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-285300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-321300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-400200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-514100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-279900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-365700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-306500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-187600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-200400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>30700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-311300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>74500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-328000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>286200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-178500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-240200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-202700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-161800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-160300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-183000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-129100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-109800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>29200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-175900</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8386,8 +8635,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8437,96 +8686,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>78900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>127400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>28300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-73000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>157100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>32400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>22800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-218000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-109400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>108500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-101200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>198800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>45500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>202700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-562000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-252000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>234300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>64100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>199900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>26400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>88200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-184800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>155600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-123900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>260200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>39200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-43900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-30000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>79000</v>
       </c>
     </row>
